--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -5,16 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6A19C2-775B-4B86-A162-9338EC2D89DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4592B3AA-29A2-46EF-B599-9D8452B5F1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$230</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1082,7 +1085,7 @@
         <v>36</v>
       </c>
       <c r="D40">
-        <v>1000</v>
+        <v>-1</v>
       </c>
       <c r="E40">
         <v>1</v>
@@ -1422,7 +1425,7 @@
         <v>20</v>
       </c>
       <c r="D60">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -1932,7 +1935,7 @@
         <v>30</v>
       </c>
       <c r="D90">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -2612,7 +2615,7 @@
         <v>30</v>
       </c>
       <c r="D130">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="E130">
         <v>1</v>
@@ -4312,13 +4315,14 @@
         <v>100</v>
       </c>
       <c r="D230">
-        <v>300</v>
+        <v>-1</v>
       </c>
       <c r="E230">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:E230" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4592B3AA-29A2-46EF-B599-9D8452B5F1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632DBC8E-69DD-4096-BAA8-2469652CB8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -413,7 +413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E230"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.5" bestFit="1" customWidth="1"/>
@@ -2632,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="D131">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -2649,7 +2649,7 @@
         <v>2</v>
       </c>
       <c r="D132">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E132">
         <v>1</v>
@@ -2666,7 +2666,7 @@
         <v>3</v>
       </c>
       <c r="D133">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E133">
         <v>1</v>
@@ -2683,7 +2683,7 @@
         <v>4</v>
       </c>
       <c r="D134">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E134">
         <v>1</v>
@@ -2700,7 +2700,7 @@
         <v>5</v>
       </c>
       <c r="D135">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E135">
         <v>1</v>
@@ -2717,7 +2717,7 @@
         <v>6</v>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E136">
         <v>1</v>
@@ -2734,7 +2734,7 @@
         <v>7</v>
       </c>
       <c r="D137">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E137">
         <v>1</v>
@@ -2751,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="D138">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -2768,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="D139">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E139">
         <v>1</v>
@@ -2785,1544 +2785,13 @@
         <v>10</v>
       </c>
       <c r="D140">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="E140">
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A141">
-        <v>990011</v>
-      </c>
-      <c r="B141">
-        <v>99</v>
-      </c>
-      <c r="C141">
-        <v>11</v>
-      </c>
-      <c r="D141">
-        <v>200</v>
-      </c>
-      <c r="E141">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A142">
-        <v>990012</v>
-      </c>
-      <c r="B142">
-        <v>99</v>
-      </c>
-      <c r="C142">
-        <v>12</v>
-      </c>
-      <c r="D142">
-        <v>300</v>
-      </c>
-      <c r="E142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A143">
-        <v>990013</v>
-      </c>
-      <c r="B143">
-        <v>99</v>
-      </c>
-      <c r="C143">
-        <v>13</v>
-      </c>
-      <c r="D143">
-        <v>300</v>
-      </c>
-      <c r="E143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A144">
-        <v>990014</v>
-      </c>
-      <c r="B144">
-        <v>99</v>
-      </c>
-      <c r="C144">
-        <v>14</v>
-      </c>
-      <c r="D144">
-        <v>300</v>
-      </c>
-      <c r="E144">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A145">
-        <v>990015</v>
-      </c>
-      <c r="B145">
-        <v>99</v>
-      </c>
-      <c r="C145">
-        <v>15</v>
-      </c>
-      <c r="D145">
-        <v>300</v>
-      </c>
-      <c r="E145">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A146">
-        <v>990016</v>
-      </c>
-      <c r="B146">
-        <v>99</v>
-      </c>
-      <c r="C146">
-        <v>16</v>
-      </c>
-      <c r="D146">
-        <v>300</v>
-      </c>
-      <c r="E146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A147">
-        <v>990017</v>
-      </c>
-      <c r="B147">
-        <v>99</v>
-      </c>
-      <c r="C147">
-        <v>17</v>
-      </c>
-      <c r="D147">
-        <v>300</v>
-      </c>
-      <c r="E147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A148">
-        <v>990018</v>
-      </c>
-      <c r="B148">
-        <v>99</v>
-      </c>
-      <c r="C148">
-        <v>18</v>
-      </c>
-      <c r="D148">
-        <v>300</v>
-      </c>
-      <c r="E148">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A149">
-        <v>990019</v>
-      </c>
-      <c r="B149">
-        <v>99</v>
-      </c>
-      <c r="C149">
-        <v>19</v>
-      </c>
-      <c r="D149">
-        <v>300</v>
-      </c>
-      <c r="E149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A150">
-        <v>990020</v>
-      </c>
-      <c r="B150">
-        <v>99</v>
-      </c>
-      <c r="C150">
-        <v>20</v>
-      </c>
-      <c r="D150">
-        <v>300</v>
-      </c>
-      <c r="E150">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A151">
-        <v>990021</v>
-      </c>
-      <c r="B151">
-        <v>99</v>
-      </c>
-      <c r="C151">
-        <v>21</v>
-      </c>
-      <c r="D151">
-        <v>300</v>
-      </c>
-      <c r="E151">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A152">
-        <v>990022</v>
-      </c>
-      <c r="B152">
-        <v>99</v>
-      </c>
-      <c r="C152">
-        <v>22</v>
-      </c>
-      <c r="D152">
-        <v>300</v>
-      </c>
-      <c r="E152">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A153">
-        <v>990023</v>
-      </c>
-      <c r="B153">
-        <v>99</v>
-      </c>
-      <c r="C153">
-        <v>23</v>
-      </c>
-      <c r="D153">
-        <v>300</v>
-      </c>
-      <c r="E153">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A154">
-        <v>990024</v>
-      </c>
-      <c r="B154">
-        <v>99</v>
-      </c>
-      <c r="C154">
-        <v>24</v>
-      </c>
-      <c r="D154">
-        <v>300</v>
-      </c>
-      <c r="E154">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A155">
-        <v>990025</v>
-      </c>
-      <c r="B155">
-        <v>99</v>
-      </c>
-      <c r="C155">
-        <v>25</v>
-      </c>
-      <c r="D155">
-        <v>300</v>
-      </c>
-      <c r="E155">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A156">
-        <v>990026</v>
-      </c>
-      <c r="B156">
-        <v>99</v>
-      </c>
-      <c r="C156">
-        <v>26</v>
-      </c>
-      <c r="D156">
-        <v>300</v>
-      </c>
-      <c r="E156">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A157">
-        <v>990027</v>
-      </c>
-      <c r="B157">
-        <v>99</v>
-      </c>
-      <c r="C157">
-        <v>27</v>
-      </c>
-      <c r="D157">
-        <v>300</v>
-      </c>
-      <c r="E157">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A158">
-        <v>990028</v>
-      </c>
-      <c r="B158">
-        <v>99</v>
-      </c>
-      <c r="C158">
-        <v>28</v>
-      </c>
-      <c r="D158">
-        <v>300</v>
-      </c>
-      <c r="E158">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A159">
-        <v>990029</v>
-      </c>
-      <c r="B159">
-        <v>99</v>
-      </c>
-      <c r="C159">
-        <v>29</v>
-      </c>
-      <c r="D159">
-        <v>300</v>
-      </c>
-      <c r="E159">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A160">
-        <v>990030</v>
-      </c>
-      <c r="B160">
-        <v>99</v>
-      </c>
-      <c r="C160">
-        <v>30</v>
-      </c>
-      <c r="D160">
-        <v>300</v>
-      </c>
-      <c r="E160">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A161">
-        <v>990031</v>
-      </c>
-      <c r="B161">
-        <v>99</v>
-      </c>
-      <c r="C161">
-        <v>31</v>
-      </c>
-      <c r="D161">
-        <v>300</v>
-      </c>
-      <c r="E161">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A162">
-        <v>990032</v>
-      </c>
-      <c r="B162">
-        <v>99</v>
-      </c>
-      <c r="C162">
-        <v>32</v>
-      </c>
-      <c r="D162">
-        <v>300</v>
-      </c>
-      <c r="E162">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A163">
-        <v>990033</v>
-      </c>
-      <c r="B163">
-        <v>99</v>
-      </c>
-      <c r="C163">
-        <v>33</v>
-      </c>
-      <c r="D163">
-        <v>300</v>
-      </c>
-      <c r="E163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A164">
-        <v>990034</v>
-      </c>
-      <c r="B164">
-        <v>99</v>
-      </c>
-      <c r="C164">
-        <v>34</v>
-      </c>
-      <c r="D164">
-        <v>300</v>
-      </c>
-      <c r="E164">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A165">
-        <v>990035</v>
-      </c>
-      <c r="B165">
-        <v>99</v>
-      </c>
-      <c r="C165">
-        <v>35</v>
-      </c>
-      <c r="D165">
-        <v>300</v>
-      </c>
-      <c r="E165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A166">
-        <v>990036</v>
-      </c>
-      <c r="B166">
-        <v>99</v>
-      </c>
-      <c r="C166">
-        <v>36</v>
-      </c>
-      <c r="D166">
-        <v>300</v>
-      </c>
-      <c r="E166">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A167">
-        <v>990037</v>
-      </c>
-      <c r="B167">
-        <v>99</v>
-      </c>
-      <c r="C167">
-        <v>37</v>
-      </c>
-      <c r="D167">
-        <v>300</v>
-      </c>
-      <c r="E167">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A168">
-        <v>990038</v>
-      </c>
-      <c r="B168">
-        <v>99</v>
-      </c>
-      <c r="C168">
-        <v>38</v>
-      </c>
-      <c r="D168">
-        <v>300</v>
-      </c>
-      <c r="E168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A169">
-        <v>990039</v>
-      </c>
-      <c r="B169">
-        <v>99</v>
-      </c>
-      <c r="C169">
-        <v>39</v>
-      </c>
-      <c r="D169">
-        <v>300</v>
-      </c>
-      <c r="E169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A170">
-        <v>990040</v>
-      </c>
-      <c r="B170">
-        <v>99</v>
-      </c>
-      <c r="C170">
-        <v>40</v>
-      </c>
-      <c r="D170">
-        <v>300</v>
-      </c>
-      <c r="E170">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A171">
-        <v>990041</v>
-      </c>
-      <c r="B171">
-        <v>99</v>
-      </c>
-      <c r="C171">
-        <v>41</v>
-      </c>
-      <c r="D171">
-        <v>300</v>
-      </c>
-      <c r="E171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A172">
-        <v>990042</v>
-      </c>
-      <c r="B172">
-        <v>99</v>
-      </c>
-      <c r="C172">
-        <v>42</v>
-      </c>
-      <c r="D172">
-        <v>300</v>
-      </c>
-      <c r="E172">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A173">
-        <v>990043</v>
-      </c>
-      <c r="B173">
-        <v>99</v>
-      </c>
-      <c r="C173">
-        <v>43</v>
-      </c>
-      <c r="D173">
-        <v>300</v>
-      </c>
-      <c r="E173">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A174">
-        <v>990044</v>
-      </c>
-      <c r="B174">
-        <v>99</v>
-      </c>
-      <c r="C174">
-        <v>44</v>
-      </c>
-      <c r="D174">
-        <v>300</v>
-      </c>
-      <c r="E174">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A175">
-        <v>990045</v>
-      </c>
-      <c r="B175">
-        <v>99</v>
-      </c>
-      <c r="C175">
-        <v>45</v>
-      </c>
-      <c r="D175">
-        <v>300</v>
-      </c>
-      <c r="E175">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A176">
-        <v>990046</v>
-      </c>
-      <c r="B176">
-        <v>99</v>
-      </c>
-      <c r="C176">
-        <v>46</v>
-      </c>
-      <c r="D176">
-        <v>300</v>
-      </c>
-      <c r="E176">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A177">
-        <v>990047</v>
-      </c>
-      <c r="B177">
-        <v>99</v>
-      </c>
-      <c r="C177">
-        <v>47</v>
-      </c>
-      <c r="D177">
-        <v>300</v>
-      </c>
-      <c r="E177">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A178">
-        <v>990048</v>
-      </c>
-      <c r="B178">
-        <v>99</v>
-      </c>
-      <c r="C178">
-        <v>48</v>
-      </c>
-      <c r="D178">
-        <v>300</v>
-      </c>
-      <c r="E178">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A179">
-        <v>990049</v>
-      </c>
-      <c r="B179">
-        <v>99</v>
-      </c>
-      <c r="C179">
-        <v>49</v>
-      </c>
-      <c r="D179">
-        <v>300</v>
-      </c>
-      <c r="E179">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A180">
-        <v>990050</v>
-      </c>
-      <c r="B180">
-        <v>99</v>
-      </c>
-      <c r="C180">
-        <v>50</v>
-      </c>
-      <c r="D180">
-        <v>300</v>
-      </c>
-      <c r="E180">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A181">
-        <v>990051</v>
-      </c>
-      <c r="B181">
-        <v>99</v>
-      </c>
-      <c r="C181">
-        <v>51</v>
-      </c>
-      <c r="D181">
-        <v>300</v>
-      </c>
-      <c r="E181">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A182">
-        <v>990052</v>
-      </c>
-      <c r="B182">
-        <v>99</v>
-      </c>
-      <c r="C182">
-        <v>52</v>
-      </c>
-      <c r="D182">
-        <v>300</v>
-      </c>
-      <c r="E182">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A183">
-        <v>990053</v>
-      </c>
-      <c r="B183">
-        <v>99</v>
-      </c>
-      <c r="C183">
-        <v>53</v>
-      </c>
-      <c r="D183">
-        <v>300</v>
-      </c>
-      <c r="E183">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A184">
-        <v>990054</v>
-      </c>
-      <c r="B184">
-        <v>99</v>
-      </c>
-      <c r="C184">
-        <v>54</v>
-      </c>
-      <c r="D184">
-        <v>300</v>
-      </c>
-      <c r="E184">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A185">
-        <v>990055</v>
-      </c>
-      <c r="B185">
-        <v>99</v>
-      </c>
-      <c r="C185">
-        <v>55</v>
-      </c>
-      <c r="D185">
-        <v>300</v>
-      </c>
-      <c r="E185">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A186">
-        <v>990056</v>
-      </c>
-      <c r="B186">
-        <v>99</v>
-      </c>
-      <c r="C186">
-        <v>56</v>
-      </c>
-      <c r="D186">
-        <v>300</v>
-      </c>
-      <c r="E186">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A187">
-        <v>990057</v>
-      </c>
-      <c r="B187">
-        <v>99</v>
-      </c>
-      <c r="C187">
-        <v>57</v>
-      </c>
-      <c r="D187">
-        <v>300</v>
-      </c>
-      <c r="E187">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A188">
-        <v>990058</v>
-      </c>
-      <c r="B188">
-        <v>99</v>
-      </c>
-      <c r="C188">
-        <v>58</v>
-      </c>
-      <c r="D188">
-        <v>300</v>
-      </c>
-      <c r="E188">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A189">
-        <v>990059</v>
-      </c>
-      <c r="B189">
-        <v>99</v>
-      </c>
-      <c r="C189">
-        <v>59</v>
-      </c>
-      <c r="D189">
-        <v>300</v>
-      </c>
-      <c r="E189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A190">
-        <v>990060</v>
-      </c>
-      <c r="B190">
-        <v>99</v>
-      </c>
-      <c r="C190">
-        <v>60</v>
-      </c>
-      <c r="D190">
-        <v>300</v>
-      </c>
-      <c r="E190">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A191">
-        <v>990061</v>
-      </c>
-      <c r="B191">
-        <v>99</v>
-      </c>
-      <c r="C191">
-        <v>61</v>
-      </c>
-      <c r="D191">
-        <v>300</v>
-      </c>
-      <c r="E191">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A192">
-        <v>990062</v>
-      </c>
-      <c r="B192">
-        <v>99</v>
-      </c>
-      <c r="C192">
-        <v>62</v>
-      </c>
-      <c r="D192">
-        <v>300</v>
-      </c>
-      <c r="E192">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A193">
-        <v>990063</v>
-      </c>
-      <c r="B193">
-        <v>99</v>
-      </c>
-      <c r="C193">
-        <v>63</v>
-      </c>
-      <c r="D193">
-        <v>300</v>
-      </c>
-      <c r="E193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A194">
-        <v>990064</v>
-      </c>
-      <c r="B194">
-        <v>99</v>
-      </c>
-      <c r="C194">
-        <v>64</v>
-      </c>
-      <c r="D194">
-        <v>300</v>
-      </c>
-      <c r="E194">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A195">
-        <v>990065</v>
-      </c>
-      <c r="B195">
-        <v>99</v>
-      </c>
-      <c r="C195">
-        <v>65</v>
-      </c>
-      <c r="D195">
-        <v>300</v>
-      </c>
-      <c r="E195">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A196">
-        <v>990066</v>
-      </c>
-      <c r="B196">
-        <v>99</v>
-      </c>
-      <c r="C196">
-        <v>66</v>
-      </c>
-      <c r="D196">
-        <v>300</v>
-      </c>
-      <c r="E196">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A197">
-        <v>990067</v>
-      </c>
-      <c r="B197">
-        <v>99</v>
-      </c>
-      <c r="C197">
-        <v>67</v>
-      </c>
-      <c r="D197">
-        <v>300</v>
-      </c>
-      <c r="E197">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A198">
-        <v>990068</v>
-      </c>
-      <c r="B198">
-        <v>99</v>
-      </c>
-      <c r="C198">
-        <v>68</v>
-      </c>
-      <c r="D198">
-        <v>300</v>
-      </c>
-      <c r="E198">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A199">
-        <v>990069</v>
-      </c>
-      <c r="B199">
-        <v>99</v>
-      </c>
-      <c r="C199">
-        <v>69</v>
-      </c>
-      <c r="D199">
-        <v>300</v>
-      </c>
-      <c r="E199">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A200">
-        <v>990070</v>
-      </c>
-      <c r="B200">
-        <v>99</v>
-      </c>
-      <c r="C200">
-        <v>70</v>
-      </c>
-      <c r="D200">
-        <v>300</v>
-      </c>
-      <c r="E200">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A201">
-        <v>990071</v>
-      </c>
-      <c r="B201">
-        <v>99</v>
-      </c>
-      <c r="C201">
-        <v>71</v>
-      </c>
-      <c r="D201">
-        <v>300</v>
-      </c>
-      <c r="E201">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A202">
-        <v>990072</v>
-      </c>
-      <c r="B202">
-        <v>99</v>
-      </c>
-      <c r="C202">
-        <v>72</v>
-      </c>
-      <c r="D202">
-        <v>300</v>
-      </c>
-      <c r="E202">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A203">
-        <v>990073</v>
-      </c>
-      <c r="B203">
-        <v>99</v>
-      </c>
-      <c r="C203">
-        <v>73</v>
-      </c>
-      <c r="D203">
-        <v>300</v>
-      </c>
-      <c r="E203">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A204">
-        <v>990074</v>
-      </c>
-      <c r="B204">
-        <v>99</v>
-      </c>
-      <c r="C204">
-        <v>74</v>
-      </c>
-      <c r="D204">
-        <v>300</v>
-      </c>
-      <c r="E204">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A205">
-        <v>990075</v>
-      </c>
-      <c r="B205">
-        <v>99</v>
-      </c>
-      <c r="C205">
-        <v>75</v>
-      </c>
-      <c r="D205">
-        <v>300</v>
-      </c>
-      <c r="E205">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A206">
-        <v>990076</v>
-      </c>
-      <c r="B206">
-        <v>99</v>
-      </c>
-      <c r="C206">
-        <v>76</v>
-      </c>
-      <c r="D206">
-        <v>300</v>
-      </c>
-      <c r="E206">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A207">
-        <v>990077</v>
-      </c>
-      <c r="B207">
-        <v>99</v>
-      </c>
-      <c r="C207">
-        <v>77</v>
-      </c>
-      <c r="D207">
-        <v>300</v>
-      </c>
-      <c r="E207">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A208">
-        <v>990078</v>
-      </c>
-      <c r="B208">
-        <v>99</v>
-      </c>
-      <c r="C208">
-        <v>78</v>
-      </c>
-      <c r="D208">
-        <v>300</v>
-      </c>
-      <c r="E208">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A209">
-        <v>990079</v>
-      </c>
-      <c r="B209">
-        <v>99</v>
-      </c>
-      <c r="C209">
-        <v>79</v>
-      </c>
-      <c r="D209">
-        <v>300</v>
-      </c>
-      <c r="E209">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A210">
-        <v>990080</v>
-      </c>
-      <c r="B210">
-        <v>99</v>
-      </c>
-      <c r="C210">
-        <v>80</v>
-      </c>
-      <c r="D210">
-        <v>300</v>
-      </c>
-      <c r="E210">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A211">
-        <v>990081</v>
-      </c>
-      <c r="B211">
-        <v>99</v>
-      </c>
-      <c r="C211">
-        <v>81</v>
-      </c>
-      <c r="D211">
-        <v>300</v>
-      </c>
-      <c r="E211">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A212">
-        <v>990082</v>
-      </c>
-      <c r="B212">
-        <v>99</v>
-      </c>
-      <c r="C212">
-        <v>82</v>
-      </c>
-      <c r="D212">
-        <v>300</v>
-      </c>
-      <c r="E212">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A213">
-        <v>990083</v>
-      </c>
-      <c r="B213">
-        <v>99</v>
-      </c>
-      <c r="C213">
-        <v>83</v>
-      </c>
-      <c r="D213">
-        <v>300</v>
-      </c>
-      <c r="E213">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A214">
-        <v>990084</v>
-      </c>
-      <c r="B214">
-        <v>99</v>
-      </c>
-      <c r="C214">
-        <v>84</v>
-      </c>
-      <c r="D214">
-        <v>300</v>
-      </c>
-      <c r="E214">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A215">
-        <v>990085</v>
-      </c>
-      <c r="B215">
-        <v>99</v>
-      </c>
-      <c r="C215">
-        <v>85</v>
-      </c>
-      <c r="D215">
-        <v>300</v>
-      </c>
-      <c r="E215">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A216">
-        <v>990086</v>
-      </c>
-      <c r="B216">
-        <v>99</v>
-      </c>
-      <c r="C216">
-        <v>86</v>
-      </c>
-      <c r="D216">
-        <v>300</v>
-      </c>
-      <c r="E216">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A217">
-        <v>990087</v>
-      </c>
-      <c r="B217">
-        <v>99</v>
-      </c>
-      <c r="C217">
-        <v>87</v>
-      </c>
-      <c r="D217">
-        <v>300</v>
-      </c>
-      <c r="E217">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A218">
-        <v>990088</v>
-      </c>
-      <c r="B218">
-        <v>99</v>
-      </c>
-      <c r="C218">
-        <v>88</v>
-      </c>
-      <c r="D218">
-        <v>300</v>
-      </c>
-      <c r="E218">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A219">
-        <v>990089</v>
-      </c>
-      <c r="B219">
-        <v>99</v>
-      </c>
-      <c r="C219">
-        <v>89</v>
-      </c>
-      <c r="D219">
-        <v>300</v>
-      </c>
-      <c r="E219">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A220">
-        <v>990090</v>
-      </c>
-      <c r="B220">
-        <v>99</v>
-      </c>
-      <c r="C220">
-        <v>90</v>
-      </c>
-      <c r="D220">
-        <v>300</v>
-      </c>
-      <c r="E220">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A221">
-        <v>990091</v>
-      </c>
-      <c r="B221">
-        <v>99</v>
-      </c>
-      <c r="C221">
-        <v>91</v>
-      </c>
-      <c r="D221">
-        <v>300</v>
-      </c>
-      <c r="E221">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A222">
-        <v>990092</v>
-      </c>
-      <c r="B222">
-        <v>99</v>
-      </c>
-      <c r="C222">
-        <v>92</v>
-      </c>
-      <c r="D222">
-        <v>300</v>
-      </c>
-      <c r="E222">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A223">
-        <v>990093</v>
-      </c>
-      <c r="B223">
-        <v>99</v>
-      </c>
-      <c r="C223">
-        <v>93</v>
-      </c>
-      <c r="D223">
-        <v>300</v>
-      </c>
-      <c r="E223">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A224">
-        <v>990094</v>
-      </c>
-      <c r="B224">
-        <v>99</v>
-      </c>
-      <c r="C224">
-        <v>94</v>
-      </c>
-      <c r="D224">
-        <v>300</v>
-      </c>
-      <c r="E224">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A225">
-        <v>990095</v>
-      </c>
-      <c r="B225">
-        <v>99</v>
-      </c>
-      <c r="C225">
-        <v>95</v>
-      </c>
-      <c r="D225">
-        <v>300</v>
-      </c>
-      <c r="E225">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A226">
-        <v>990096</v>
-      </c>
-      <c r="B226">
-        <v>99</v>
-      </c>
-      <c r="C226">
-        <v>96</v>
-      </c>
-      <c r="D226">
-        <v>300</v>
-      </c>
-      <c r="E226">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A227">
-        <v>990097</v>
-      </c>
-      <c r="B227">
-        <v>99</v>
-      </c>
-      <c r="C227">
-        <v>97</v>
-      </c>
-      <c r="D227">
-        <v>300</v>
-      </c>
-      <c r="E227">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A228">
-        <v>990098</v>
-      </c>
-      <c r="B228">
-        <v>99</v>
-      </c>
-      <c r="C228">
-        <v>98</v>
-      </c>
-      <c r="D228">
-        <v>300</v>
-      </c>
-      <c r="E228">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A229">
-        <v>990099</v>
-      </c>
-      <c r="B229">
-        <v>99</v>
-      </c>
-      <c r="C229">
-        <v>99</v>
-      </c>
-      <c r="D229">
-        <v>300</v>
-      </c>
-      <c r="E229">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A230">
-        <v>990100</v>
-      </c>
-      <c r="B230">
-        <v>99</v>
-      </c>
-      <c r="C230">
-        <v>100</v>
-      </c>
-      <c r="D230">
-        <v>-1</v>
-      </c>
-      <c r="E230">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:E230" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632DBC8E-69DD-4096-BAA8-2469652CB8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C40D998-A502-49D8-880E-0F22E1D9E7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2751,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="D138">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -2768,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="D139">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E139">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C40D998-A502-49D8-880E-0F22E1D9E7D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{632DBC8E-69DD-4096-BAA8-2469652CB8D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2751,7 +2751,7 @@
         <v>8</v>
       </c>
       <c r="D138">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E138">
         <v>1</v>
@@ -2768,7 +2768,7 @@
         <v>9</v>
       </c>
       <c r="D139">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E139">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F0B137-3209-4D3D-85A5-B38B3CD860AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD1DDB9-E03B-44F0-8A00-353B0074B9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
@@ -3027,7 +3027,7 @@
         <v>1</v>
       </c>
       <c r="F130" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
@@ -3141,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="D136" s="1">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
@@ -3161,7 +3161,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="1">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="1">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>
@@ -3221,12 +3221,217 @@
         <v>10</v>
       </c>
       <c r="D140" s="1">
+        <v>53</v>
+      </c>
+      <c r="E140" s="1">
+        <v>1</v>
+      </c>
+      <c r="F140" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A141" s="1">
+        <v>990011</v>
+      </c>
+      <c r="B141" s="1">
+        <v>99</v>
+      </c>
+      <c r="C141" s="1">
+        <v>11</v>
+      </c>
+      <c r="D141" s="1">
+        <v>19</v>
+      </c>
+      <c r="E141" s="1">
+        <v>1</v>
+      </c>
+      <c r="F141" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A142" s="1">
+        <v>990012</v>
+      </c>
+      <c r="B142" s="1">
+        <v>99</v>
+      </c>
+      <c r="C142" s="1">
+        <v>12</v>
+      </c>
+      <c r="D142" s="1">
+        <v>27</v>
+      </c>
+      <c r="E142" s="1">
+        <v>1</v>
+      </c>
+      <c r="F142" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A143" s="1">
+        <v>990013</v>
+      </c>
+      <c r="B143" s="1">
+        <v>99</v>
+      </c>
+      <c r="C143" s="1">
+        <v>13</v>
+      </c>
+      <c r="D143" s="1">
+        <v>41</v>
+      </c>
+      <c r="E143" s="1">
+        <v>1</v>
+      </c>
+      <c r="F143" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A144" s="1">
+        <v>990014</v>
+      </c>
+      <c r="B144" s="1">
+        <v>99</v>
+      </c>
+      <c r="C144" s="1">
+        <v>14</v>
+      </c>
+      <c r="D144" s="1">
+        <v>53</v>
+      </c>
+      <c r="E144" s="1">
+        <v>1</v>
+      </c>
+      <c r="F144" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A145" s="1">
+        <v>990015</v>
+      </c>
+      <c r="B145" s="1">
+        <v>99</v>
+      </c>
+      <c r="C145" s="1">
+        <v>15</v>
+      </c>
+      <c r="D145" s="1">
+        <v>67</v>
+      </c>
+      <c r="E145" s="1">
+        <v>1</v>
+      </c>
+      <c r="F145" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A146" s="1">
+        <v>990016</v>
+      </c>
+      <c r="B146" s="1">
+        <v>99</v>
+      </c>
+      <c r="C146" s="1">
+        <v>16</v>
+      </c>
+      <c r="D146" s="1">
+        <v>27</v>
+      </c>
+      <c r="E146" s="1">
+        <v>1</v>
+      </c>
+      <c r="F146" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A147" s="1">
+        <v>990017</v>
+      </c>
+      <c r="B147" s="1">
+        <v>99</v>
+      </c>
+      <c r="C147" s="1">
+        <v>17</v>
+      </c>
+      <c r="D147" s="1">
+        <v>41</v>
+      </c>
+      <c r="E147" s="1">
+        <v>1</v>
+      </c>
+      <c r="F147" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A148" s="1">
+        <v>990018</v>
+      </c>
+      <c r="B148" s="1">
+        <v>99</v>
+      </c>
+      <c r="C148" s="1">
+        <v>18</v>
+      </c>
+      <c r="D148" s="1">
+        <v>53</v>
+      </c>
+      <c r="E148" s="1">
+        <v>1</v>
+      </c>
+      <c r="F148" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A149" s="1">
+        <v>990019</v>
+      </c>
+      <c r="B149" s="1">
+        <v>99</v>
+      </c>
+      <c r="C149" s="1">
+        <v>19</v>
+      </c>
+      <c r="D149" s="1">
+        <v>67</v>
+      </c>
+      <c r="E149" s="1">
+        <v>1</v>
+      </c>
+      <c r="F149" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A150" s="1">
+        <v>990020</v>
+      </c>
+      <c r="B150" s="1">
+        <v>99</v>
+      </c>
+      <c r="C150" s="1">
+        <v>20</v>
+      </c>
+      <c r="D150" s="1">
         <v>-1</v>
       </c>
-      <c r="E140" s="1">
-        <v>1</v>
-      </c>
-      <c r="F140" s="1">
+      <c r="E150" s="1">
+        <v>1</v>
+      </c>
+      <c r="F150" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="F151" s="1">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD1DDB9-E03B-44F0-8A00-353B0074B9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18350" windowHeight="6880"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -20,9 +14,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,85 +33,68 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>paipaiworld_config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S_C</t>
+  </si>
+  <si>
+    <t>INT_S</t>
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energy_id</t>
+  </si>
+  <si>
+    <t>energy_level</t>
+  </si>
+  <si>
+    <t>max_energy</t>
+  </si>
+  <si>
+    <t>energy_select</t>
+  </si>
+  <si>
+    <t>energy_item_select</t>
+  </si>
+  <si>
+    <t>序号（能力id*10000+等级</t>
+  </si>
+  <si>
+    <t>能力id</t>
   </si>
   <si>
     <t>等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_energy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>升到下一级需要的能量点数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_select</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>提升到当前等级时可以选择能力的次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_level</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号（能力id*10000+等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>能力id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_item_select</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>提升到当前等级时，可以使用道具触发的选择能力次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -126,19 +102,355 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -146,25 +458,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -213,7 +811,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -248,7 +846,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -422,95 +1020,90 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F151"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="50.5" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>10001</v>
       </c>
@@ -530,7 +1123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>10002</v>
       </c>
@@ -550,7 +1143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>10003</v>
       </c>
@@ -570,7 +1163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>10004</v>
       </c>
@@ -590,7 +1183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>10005</v>
       </c>
@@ -610,7 +1203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>10006</v>
       </c>
@@ -630,7 +1223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>10007</v>
       </c>
@@ -650,7 +1243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>10008</v>
       </c>
@@ -670,7 +1263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>10009</v>
       </c>
@@ -690,7 +1283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>10010</v>
       </c>
@@ -710,7 +1303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>10011</v>
       </c>
@@ -730,7 +1323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>10012</v>
       </c>
@@ -750,7 +1343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>10013</v>
       </c>
@@ -770,7 +1363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>10014</v>
       </c>
@@ -790,7 +1383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>10015</v>
       </c>
@@ -810,7 +1403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>10016</v>
       </c>
@@ -830,7 +1423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>10017</v>
       </c>
@@ -850,7 +1443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>10018</v>
       </c>
@@ -870,7 +1463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>10019</v>
       </c>
@@ -890,7 +1483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>10020</v>
       </c>
@@ -910,7 +1503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>10021</v>
       </c>
@@ -930,7 +1523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>10022</v>
       </c>
@@ -950,7 +1543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>10023</v>
       </c>
@@ -970,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>10024</v>
       </c>
@@ -990,7 +1583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>10025</v>
       </c>
@@ -1010,7 +1603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>10026</v>
       </c>
@@ -1030,7 +1623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>10027</v>
       </c>
@@ -1050,7 +1643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>10028</v>
       </c>
@@ -1070,7 +1663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>10029</v>
       </c>
@@ -1090,7 +1683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:6">
       <c r="A34" s="1">
         <v>10030</v>
       </c>
@@ -1110,7 +1703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:6">
       <c r="A35" s="1">
         <v>10031</v>
       </c>
@@ -1130,7 +1723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6">
       <c r="A36" s="1">
         <v>10032</v>
       </c>
@@ -1150,7 +1743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6">
       <c r="A37" s="1">
         <v>10033</v>
       </c>
@@ -1170,7 +1763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:6">
       <c r="A38" s="1">
         <v>10034</v>
       </c>
@@ -1190,7 +1783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="A39" s="1">
         <v>10035</v>
       </c>
@@ -1210,7 +1803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6">
       <c r="A40" s="1">
         <v>10036</v>
       </c>
@@ -1230,7 +1823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="A41" s="1">
         <v>20001</v>
       </c>
@@ -1250,7 +1843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="A42" s="1">
         <v>20002</v>
       </c>
@@ -1270,7 +1863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6">
       <c r="A43" s="1">
         <v>20003</v>
       </c>
@@ -1290,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="A44" s="1">
         <v>20004</v>
       </c>
@@ -1310,7 +1903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="A45" s="1">
         <v>20005</v>
       </c>
@@ -1330,7 +1923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:6">
       <c r="A46" s="1">
         <v>20006</v>
       </c>
@@ -1350,7 +1943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="A47" s="1">
         <v>20007</v>
       </c>
@@ -1370,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="A48" s="1">
         <v>20008</v>
       </c>
@@ -1390,7 +1983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:6">
       <c r="A49" s="1">
         <v>20009</v>
       </c>
@@ -1410,7 +2003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:6">
       <c r="A50" s="1">
         <v>20010</v>
       </c>
@@ -1430,7 +2023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:6">
       <c r="A51" s="1">
         <v>20011</v>
       </c>
@@ -1450,7 +2043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:6">
       <c r="A52" s="1">
         <v>20012</v>
       </c>
@@ -1470,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:6">
       <c r="A53" s="1">
         <v>20013</v>
       </c>
@@ -1490,7 +2083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:6">
       <c r="A54" s="1">
         <v>20014</v>
       </c>
@@ -1510,7 +2103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:6">
       <c r="A55" s="1">
         <v>20015</v>
       </c>
@@ -1530,7 +2123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:6">
       <c r="A56" s="1">
         <v>20016</v>
       </c>
@@ -1550,7 +2143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:6">
       <c r="A57" s="1">
         <v>20017</v>
       </c>
@@ -1570,7 +2163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:6">
       <c r="A58" s="1">
         <v>20018</v>
       </c>
@@ -1590,7 +2183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:6">
       <c r="A59" s="1">
         <v>20019</v>
       </c>
@@ -1610,7 +2203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:6">
       <c r="A60" s="1">
         <v>20020</v>
       </c>
@@ -1630,7 +2223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:6">
       <c r="A61" s="1">
         <v>30001</v>
       </c>
@@ -1650,7 +2243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:6">
       <c r="A62" s="1">
         <v>30002</v>
       </c>
@@ -1670,7 +2263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:6">
       <c r="A63" s="1">
         <v>30003</v>
       </c>
@@ -1690,7 +2283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:6">
       <c r="A64" s="1">
         <v>30004</v>
       </c>
@@ -1710,7 +2303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="A65" s="1">
         <v>30005</v>
       </c>
@@ -1730,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="A66" s="1">
         <v>30006</v>
       </c>
@@ -1750,7 +2343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="A67" s="1">
         <v>30007</v>
       </c>
@@ -1770,7 +2363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="A68" s="1">
         <v>30008</v>
       </c>
@@ -1790,7 +2383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="A69" s="1">
         <v>30009</v>
       </c>
@@ -1810,7 +2403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="A70" s="1">
         <v>30010</v>
       </c>
@@ -1830,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:6">
       <c r="A71" s="1">
         <v>30011</v>
       </c>
@@ -1850,7 +2443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="1">
         <v>30012</v>
       </c>
@@ -1870,7 +2463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="1">
         <v>30013</v>
       </c>
@@ -1890,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="A74" s="1">
         <v>30014</v>
       </c>
@@ -1910,7 +2503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="1">
         <v>30015</v>
       </c>
@@ -1930,7 +2523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="1">
         <v>30016</v>
       </c>
@@ -1950,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="1">
         <v>30017</v>
       </c>
@@ -1970,7 +2563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="A78" s="1">
         <v>30018</v>
       </c>
@@ -1990,7 +2583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="1">
         <v>30019</v>
       </c>
@@ -2010,7 +2603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="1">
         <v>30020</v>
       </c>
@@ -2030,7 +2623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="1">
         <v>30021</v>
       </c>
@@ -2050,7 +2643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="1">
         <v>30022</v>
       </c>
@@ -2070,7 +2663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="1">
         <v>30023</v>
       </c>
@@ -2090,7 +2683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="1">
         <v>30024</v>
       </c>
@@ -2110,7 +2703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="1">
         <v>30025</v>
       </c>
@@ -2130,7 +2723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="1">
         <v>30026</v>
       </c>
@@ -2150,7 +2743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="1">
         <v>30027</v>
       </c>
@@ -2170,7 +2763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="1">
         <v>30028</v>
       </c>
@@ -2190,7 +2783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="1">
         <v>30029</v>
       </c>
@@ -2210,7 +2803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="1">
         <v>30030</v>
       </c>
@@ -2230,7 +2823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="1">
         <v>40001</v>
       </c>
@@ -2250,7 +2843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="1">
         <v>40002</v>
       </c>
@@ -2270,7 +2863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="A93" s="1">
         <v>40003</v>
       </c>
@@ -2290,7 +2883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="A94" s="1">
         <v>40004</v>
       </c>
@@ -2310,7 +2903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="1">
         <v>40005</v>
       </c>
@@ -2330,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="1">
         <v>40006</v>
       </c>
@@ -2350,7 +2943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:6">
       <c r="A97" s="1">
         <v>40007</v>
       </c>
@@ -2370,7 +2963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:6">
       <c r="A98" s="1">
         <v>40008</v>
       </c>
@@ -2390,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:6">
       <c r="A99" s="1">
         <v>40009</v>
       </c>
@@ -2410,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:6">
       <c r="A100" s="1">
         <v>40010</v>
       </c>
@@ -2430,7 +3023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:6">
       <c r="A101" s="1">
         <v>40011</v>
       </c>
@@ -2450,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:6">
       <c r="A102" s="1">
         <v>40012</v>
       </c>
@@ -2470,7 +3063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:6">
       <c r="A103" s="1">
         <v>40013</v>
       </c>
@@ -2490,7 +3083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:6">
       <c r="A104" s="1">
         <v>40014</v>
       </c>
@@ -2510,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:6">
       <c r="A105" s="1">
         <v>40015</v>
       </c>
@@ -2530,7 +3123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:6">
       <c r="A106" s="1">
         <v>40016</v>
       </c>
@@ -2550,7 +3143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:6">
       <c r="A107" s="1">
         <v>40017</v>
       </c>
@@ -2570,7 +3163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:6">
       <c r="A108" s="1">
         <v>40018</v>
       </c>
@@ -2590,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:6">
       <c r="A109" s="1">
         <v>40019</v>
       </c>
@@ -2610,7 +3203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:6">
       <c r="A110" s="1">
         <v>40020</v>
       </c>
@@ -2630,7 +3223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:6">
       <c r="A111" s="1">
         <v>40021</v>
       </c>
@@ -2650,7 +3243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:6">
       <c r="A112" s="1">
         <v>40022</v>
       </c>
@@ -2670,7 +3263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="A113" s="1">
         <v>40023</v>
       </c>
@@ -2690,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="A114" s="1">
         <v>40024</v>
       </c>
@@ -2710,7 +3303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:6">
       <c r="A115" s="1">
         <v>40025</v>
       </c>
@@ -2730,7 +3323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:6">
       <c r="A116" s="1">
         <v>40026</v>
       </c>
@@ -2750,7 +3343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:6">
       <c r="A117" s="1">
         <v>40027</v>
       </c>
@@ -2770,7 +3363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6">
       <c r="A118" s="1">
         <v>40028</v>
       </c>
@@ -2790,7 +3383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="A119" s="1">
         <v>40029</v>
       </c>
@@ -2810,7 +3403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:6">
       <c r="A120" s="1">
         <v>40030</v>
       </c>
@@ -2830,7 +3423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="A121" s="1">
         <v>40031</v>
       </c>
@@ -2850,7 +3443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="A122" s="1">
         <v>40032</v>
       </c>
@@ -2870,7 +3463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="A123" s="1">
         <v>40033</v>
       </c>
@@ -2890,7 +3483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="A124" s="1">
         <v>40034</v>
       </c>
@@ -2910,7 +3503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="A125" s="1">
         <v>40035</v>
       </c>
@@ -2930,7 +3523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="A126" s="1">
         <v>40036</v>
       </c>
@@ -2950,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="A127" s="1">
         <v>40037</v>
       </c>
@@ -2970,7 +3563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="A128" s="1">
         <v>40038</v>
       </c>
@@ -2990,7 +3583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="A129" s="1">
         <v>40039</v>
       </c>
@@ -3010,7 +3603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="A130" s="1">
         <v>40040</v>
       </c>
@@ -3030,7 +3623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:6">
       <c r="A131" s="1">
         <v>990001</v>
       </c>
@@ -3047,10 +3640,10 @@
         <v>0</v>
       </c>
       <c r="F131" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" s="1">
         <v>990002</v>
       </c>
@@ -3067,10 +3660,10 @@
         <v>1</v>
       </c>
       <c r="F132" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" s="1">
         <v>990003</v>
       </c>
@@ -3084,13 +3677,13 @@
         <v>14</v>
       </c>
       <c r="E133" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F133" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="1">
         <v>990004</v>
       </c>
@@ -3110,7 +3703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="A135" s="1">
         <v>990005</v>
       </c>
@@ -3130,7 +3723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="A136" s="1">
         <v>990006</v>
       </c>
@@ -3150,7 +3743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="A137" s="1">
         <v>990007</v>
       </c>
@@ -3170,7 +3763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="A138" s="1">
         <v>990008</v>
       </c>
@@ -3190,7 +3783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:6">
       <c r="A139" s="1">
         <v>990009</v>
       </c>
@@ -3210,7 +3803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="A140" s="1">
         <v>990010</v>
       </c>
@@ -3230,7 +3823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="A141" s="1">
         <v>990011</v>
       </c>
@@ -3250,7 +3843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="A142" s="1">
         <v>990012</v>
       </c>
@@ -3270,7 +3863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="A143" s="1">
         <v>990013</v>
       </c>
@@ -3290,7 +3883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="A144" s="1">
         <v>990014</v>
       </c>
@@ -3310,7 +3903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="A145" s="1">
         <v>990015</v>
       </c>
@@ -3330,7 +3923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:6">
       <c r="A146" s="1">
         <v>990016</v>
       </c>
@@ -3350,7 +3943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:6">
       <c r="A147" s="1">
         <v>990017</v>
       </c>
@@ -3370,7 +3963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:6">
       <c r="A148" s="1">
         <v>990018</v>
       </c>
@@ -3390,7 +3983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:6">
       <c r="A149" s="1">
         <v>990019</v>
       </c>
@@ -3410,7 +4003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:6">
       <c r="A150" s="1">
         <v>990020</v>
       </c>
@@ -3430,13 +4023,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="151" spans="6:6">
       <c r="F151" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD1DDB9-E03B-44F0-8A00-353B0074B9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6880"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -14,6 +20,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -21,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,68 +40,85 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>paipaiworld_config</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>order</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_energy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升到下一级需要的能量点数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energy_select</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升到当前等级时可以选择能力的次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_S_C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energy_level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energy_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>序号（能力id*10000+等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能力id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energy_item_select</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升到当前等级时，可以使用道具触发的选择能力次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_S</t>
-  </si>
-  <si>
-    <t>order</t>
-  </si>
-  <si>
-    <t>energy_id</t>
-  </si>
-  <si>
-    <t>energy_level</t>
-  </si>
-  <si>
-    <t>max_energy</t>
-  </si>
-  <si>
-    <t>energy_select</t>
-  </si>
-  <si>
-    <t>energy_item_select</t>
-  </si>
-  <si>
-    <t>序号（能力id*10000+等级</t>
-  </si>
-  <si>
-    <t>能力id</t>
-  </si>
-  <si>
-    <t>等级</t>
-  </si>
-  <si>
-    <t>升到下一级需要的能量点数</t>
-  </si>
-  <si>
-    <t>提升到当前等级时可以选择能力的次数</t>
-  </si>
-  <si>
-    <t>提升到当前等级时，可以使用道具触发的选择能力次数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -102,355 +126,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -458,311 +146,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -811,7 +213,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -846,7 +248,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -1020,90 +422,95 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F151"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="25.125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="35.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="50.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="50.5" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>10001</v>
       </c>
@@ -1123,7 +530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>10002</v>
       </c>
@@ -1143,7 +550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>10003</v>
       </c>
@@ -1163,7 +570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>10004</v>
       </c>
@@ -1183,7 +590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>10005</v>
       </c>
@@ -1203,7 +610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>10006</v>
       </c>
@@ -1223,7 +630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>10007</v>
       </c>
@@ -1243,7 +650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>10008</v>
       </c>
@@ -1263,7 +670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>10009</v>
       </c>
@@ -1283,7 +690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10010</v>
       </c>
@@ -1303,7 +710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>10011</v>
       </c>
@@ -1323,7 +730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>10012</v>
       </c>
@@ -1343,7 +750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>10013</v>
       </c>
@@ -1363,7 +770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>10014</v>
       </c>
@@ -1383,7 +790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>10015</v>
       </c>
@@ -1403,7 +810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>10016</v>
       </c>
@@ -1423,7 +830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>10017</v>
       </c>
@@ -1443,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>10018</v>
       </c>
@@ -1463,7 +870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>10019</v>
       </c>
@@ -1483,7 +890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>10020</v>
       </c>
@@ -1503,7 +910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>10021</v>
       </c>
@@ -1523,7 +930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>10022</v>
       </c>
@@ -1543,7 +950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>10023</v>
       </c>
@@ -1563,7 +970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>10024</v>
       </c>
@@ -1583,7 +990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>10025</v>
       </c>
@@ -1603,7 +1010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>10026</v>
       </c>
@@ -1623,7 +1030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>10027</v>
       </c>
@@ -1643,7 +1050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>10028</v>
       </c>
@@ -1663,7 +1070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>10029</v>
       </c>
@@ -1683,7 +1090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>10030</v>
       </c>
@@ -1703,7 +1110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>10031</v>
       </c>
@@ -1723,7 +1130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>10032</v>
       </c>
@@ -1743,7 +1150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>10033</v>
       </c>
@@ -1763,7 +1170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>10034</v>
       </c>
@@ -1783,7 +1190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>10035</v>
       </c>
@@ -1803,7 +1210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>10036</v>
       </c>
@@ -1823,7 +1230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>20001</v>
       </c>
@@ -1843,7 +1250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>20002</v>
       </c>
@@ -1863,7 +1270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>20003</v>
       </c>
@@ -1883,7 +1290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>20004</v>
       </c>
@@ -1903,7 +1310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>20005</v>
       </c>
@@ -1923,7 +1330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>20006</v>
       </c>
@@ -1943,7 +1350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>20007</v>
       </c>
@@ -1963,7 +1370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>20008</v>
       </c>
@@ -1983,7 +1390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>20009</v>
       </c>
@@ -2003,7 +1410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>20010</v>
       </c>
@@ -2023,7 +1430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>20011</v>
       </c>
@@ -2043,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>20012</v>
       </c>
@@ -2063,7 +1470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>20013</v>
       </c>
@@ -2083,7 +1490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>20014</v>
       </c>
@@ -2103,7 +1510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>20015</v>
       </c>
@@ -2123,7 +1530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>20016</v>
       </c>
@@ -2143,7 +1550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>20017</v>
       </c>
@@ -2163,7 +1570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>20018</v>
       </c>
@@ -2183,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>20019</v>
       </c>
@@ -2203,7 +1610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>20020</v>
       </c>
@@ -2223,7 +1630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>30001</v>
       </c>
@@ -2243,7 +1650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>30002</v>
       </c>
@@ -2263,7 +1670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>30003</v>
       </c>
@@ -2283,7 +1690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>30004</v>
       </c>
@@ -2303,7 +1710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>30005</v>
       </c>
@@ -2323,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>30006</v>
       </c>
@@ -2343,7 +1750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>30007</v>
       </c>
@@ -2363,7 +1770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>30008</v>
       </c>
@@ -2383,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>30009</v>
       </c>
@@ -2403,7 +1810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>30010</v>
       </c>
@@ -2423,7 +1830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>30011</v>
       </c>
@@ -2443,7 +1850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>30012</v>
       </c>
@@ -2463,7 +1870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>30013</v>
       </c>
@@ -2483,7 +1890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>30014</v>
       </c>
@@ -2503,7 +1910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>30015</v>
       </c>
@@ -2523,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>30016</v>
       </c>
@@ -2543,7 +1950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>30017</v>
       </c>
@@ -2563,7 +1970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>30018</v>
       </c>
@@ -2583,7 +1990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>30019</v>
       </c>
@@ -2603,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>30020</v>
       </c>
@@ -2623,7 +2030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>30021</v>
       </c>
@@ -2643,7 +2050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>30022</v>
       </c>
@@ -2663,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>30023</v>
       </c>
@@ -2683,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>30024</v>
       </c>
@@ -2703,7 +2110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>30025</v>
       </c>
@@ -2723,7 +2130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>30026</v>
       </c>
@@ -2743,7 +2150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>30027</v>
       </c>
@@ -2763,7 +2170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>30028</v>
       </c>
@@ -2783,7 +2190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>30029</v>
       </c>
@@ -2803,7 +2210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>30030</v>
       </c>
@@ -2823,7 +2230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>40001</v>
       </c>
@@ -2843,7 +2250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>40002</v>
       </c>
@@ -2863,7 +2270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>40003</v>
       </c>
@@ -2883,7 +2290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>40004</v>
       </c>
@@ -2903,7 +2310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>40005</v>
       </c>
@@ -2923,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>40006</v>
       </c>
@@ -2943,7 +2350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>40007</v>
       </c>
@@ -2963,7 +2370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>40008</v>
       </c>
@@ -2983,7 +2390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>40009</v>
       </c>
@@ -3003,7 +2410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>40010</v>
       </c>
@@ -3023,7 +2430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>40011</v>
       </c>
@@ -3043,7 +2450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>40012</v>
       </c>
@@ -3063,7 +2470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>40013</v>
       </c>
@@ -3083,7 +2490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>40014</v>
       </c>
@@ -3103,7 +2510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>40015</v>
       </c>
@@ -3123,7 +2530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>40016</v>
       </c>
@@ -3143,7 +2550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>40017</v>
       </c>
@@ -3163,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>40018</v>
       </c>
@@ -3183,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>40019</v>
       </c>
@@ -3203,7 +2610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>40020</v>
       </c>
@@ -3223,7 +2630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>40021</v>
       </c>
@@ -3243,7 +2650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>40022</v>
       </c>
@@ -3263,7 +2670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>40023</v>
       </c>
@@ -3283,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>40024</v>
       </c>
@@ -3303,7 +2710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>40025</v>
       </c>
@@ -3323,7 +2730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>40026</v>
       </c>
@@ -3343,7 +2750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>40027</v>
       </c>
@@ -3363,7 +2770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>40028</v>
       </c>
@@ -3383,7 +2790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>40029</v>
       </c>
@@ -3403,7 +2810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>40030</v>
       </c>
@@ -3423,7 +2830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>40031</v>
       </c>
@@ -3443,7 +2850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>40032</v>
       </c>
@@ -3463,7 +2870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>40033</v>
       </c>
@@ -3483,7 +2890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>40034</v>
       </c>
@@ -3503,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>40035</v>
       </c>
@@ -3523,7 +2930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>40036</v>
       </c>
@@ -3543,7 +2950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>40037</v>
       </c>
@@ -3563,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>40038</v>
       </c>
@@ -3583,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>40039</v>
       </c>
@@ -3603,7 +3010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>40040</v>
       </c>
@@ -3623,7 +3030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>990001</v>
       </c>
@@ -3640,10 +3047,10 @@
         <v>0</v>
       </c>
       <c r="F131" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>990002</v>
       </c>
@@ -3660,10 +3067,10 @@
         <v>1</v>
       </c>
       <c r="F132" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>990003</v>
       </c>
@@ -3677,13 +3084,13 @@
         <v>14</v>
       </c>
       <c r="E133" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F133" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>990004</v>
       </c>
@@ -3703,7 +3110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>990005</v>
       </c>
@@ -3723,7 +3130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>990006</v>
       </c>
@@ -3743,7 +3150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>990007</v>
       </c>
@@ -3763,7 +3170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>990008</v>
       </c>
@@ -3783,7 +3190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>990009</v>
       </c>
@@ -3803,7 +3210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>990010</v>
       </c>
@@ -3823,7 +3230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>990011</v>
       </c>
@@ -3843,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>990012</v>
       </c>
@@ -3863,7 +3270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>990013</v>
       </c>
@@ -3883,7 +3290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>990014</v>
       </c>
@@ -3903,7 +3310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>990015</v>
       </c>
@@ -3923,7 +3330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>990016</v>
       </c>
@@ -3943,7 +3350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>990017</v>
       </c>
@@ -3963,7 +3370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>990018</v>
       </c>
@@ -3983,7 +3390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>990019</v>
       </c>
@@ -4003,7 +3410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>990020</v>
       </c>
@@ -4023,13 +3430,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="6:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="F151" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD1DDB9-E03B-44F0-8A00-353B0074B9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8C20D1-914D-4A0E-98B7-5DAFA72D9B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$219</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F140"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.15">
@@ -3061,7 +3061,7 @@
         <v>2</v>
       </c>
       <c r="D132" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -3081,7 +3081,7 @@
         <v>3</v>
       </c>
       <c r="D133" s="1">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="D134" s="1">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -3121,7 +3121,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="1">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -3141,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="D136" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
@@ -3161,7 +3161,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="1">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>
@@ -3221,217 +3221,12 @@
         <v>10</v>
       </c>
       <c r="D140" s="1">
-        <v>53</v>
+        <v>-1</v>
       </c>
       <c r="E140" s="1">
         <v>1</v>
       </c>
       <c r="F140" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A141" s="1">
-        <v>990011</v>
-      </c>
-      <c r="B141" s="1">
-        <v>99</v>
-      </c>
-      <c r="C141" s="1">
-        <v>11</v>
-      </c>
-      <c r="D141" s="1">
-        <v>19</v>
-      </c>
-      <c r="E141" s="1">
-        <v>1</v>
-      </c>
-      <c r="F141" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A142" s="1">
-        <v>990012</v>
-      </c>
-      <c r="B142" s="1">
-        <v>99</v>
-      </c>
-      <c r="C142" s="1">
-        <v>12</v>
-      </c>
-      <c r="D142" s="1">
-        <v>27</v>
-      </c>
-      <c r="E142" s="1">
-        <v>1</v>
-      </c>
-      <c r="F142" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A143" s="1">
-        <v>990013</v>
-      </c>
-      <c r="B143" s="1">
-        <v>99</v>
-      </c>
-      <c r="C143" s="1">
-        <v>13</v>
-      </c>
-      <c r="D143" s="1">
-        <v>41</v>
-      </c>
-      <c r="E143" s="1">
-        <v>1</v>
-      </c>
-      <c r="F143" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A144" s="1">
-        <v>990014</v>
-      </c>
-      <c r="B144" s="1">
-        <v>99</v>
-      </c>
-      <c r="C144" s="1">
-        <v>14</v>
-      </c>
-      <c r="D144" s="1">
-        <v>53</v>
-      </c>
-      <c r="E144" s="1">
-        <v>1</v>
-      </c>
-      <c r="F144" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A145" s="1">
-        <v>990015</v>
-      </c>
-      <c r="B145" s="1">
-        <v>99</v>
-      </c>
-      <c r="C145" s="1">
-        <v>15</v>
-      </c>
-      <c r="D145" s="1">
-        <v>67</v>
-      </c>
-      <c r="E145" s="1">
-        <v>1</v>
-      </c>
-      <c r="F145" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A146" s="1">
-        <v>990016</v>
-      </c>
-      <c r="B146" s="1">
-        <v>99</v>
-      </c>
-      <c r="C146" s="1">
-        <v>16</v>
-      </c>
-      <c r="D146" s="1">
-        <v>27</v>
-      </c>
-      <c r="E146" s="1">
-        <v>1</v>
-      </c>
-      <c r="F146" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A147" s="1">
-        <v>990017</v>
-      </c>
-      <c r="B147" s="1">
-        <v>99</v>
-      </c>
-      <c r="C147" s="1">
-        <v>17</v>
-      </c>
-      <c r="D147" s="1">
-        <v>41</v>
-      </c>
-      <c r="E147" s="1">
-        <v>1</v>
-      </c>
-      <c r="F147" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A148" s="1">
-        <v>990018</v>
-      </c>
-      <c r="B148" s="1">
-        <v>99</v>
-      </c>
-      <c r="C148" s="1">
-        <v>18</v>
-      </c>
-      <c r="D148" s="1">
-        <v>53</v>
-      </c>
-      <c r="E148" s="1">
-        <v>1</v>
-      </c>
-      <c r="F148" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A149" s="1">
-        <v>990019</v>
-      </c>
-      <c r="B149" s="1">
-        <v>99</v>
-      </c>
-      <c r="C149" s="1">
-        <v>19</v>
-      </c>
-      <c r="D149" s="1">
-        <v>67</v>
-      </c>
-      <c r="E149" s="1">
-        <v>1</v>
-      </c>
-      <c r="F149" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A150" s="1">
-        <v>990020</v>
-      </c>
-      <c r="B150" s="1">
-        <v>99</v>
-      </c>
-      <c r="C150" s="1">
-        <v>20</v>
-      </c>
-      <c r="D150" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E150" s="1">
-        <v>1</v>
-      </c>
-      <c r="F150" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="F151" s="1">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8C20D1-914D-4A0E-98B7-5DAFA72D9B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B684E0-C9E7-48A1-A70F-AFC10197BEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3161,7 +3161,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="1">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="1">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B684E0-C9E7-48A1-A70F-AFC10197BEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8C20D1-914D-4A0E-98B7-5DAFA72D9B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3161,7 +3161,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="1">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64B684E0-C9E7-48A1-A70F-AFC10197BEE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E833B7D8-D170-4D15-980E-B9A787A4E485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="D134" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -3121,7 +3121,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E833B7D8-D170-4D15-980E-B9A787A4E485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A7E336-8B4E-4129-B28F-891F6BDBD340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3141,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="D136" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
@@ -3161,7 +3161,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="1">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A7E336-8B4E-4129-B28F-891F6BDBD340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D83668-876C-461C-98DC-90D3DB7A3D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F140"/>
+  <dimension ref="A1:F200"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
@@ -3230,6 +3230,1206 @@
         <v>1</v>
       </c>
     </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A141" s="1">
+        <v>1000001</v>
+      </c>
+      <c r="B141" s="1">
+        <v>100</v>
+      </c>
+      <c r="C141" s="1">
+        <v>1</v>
+      </c>
+      <c r="D141" s="1">
+        <v>2</v>
+      </c>
+      <c r="E141" s="1">
+        <v>0</v>
+      </c>
+      <c r="F141" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A142" s="1">
+        <v>1000002</v>
+      </c>
+      <c r="B142" s="1">
+        <v>100</v>
+      </c>
+      <c r="C142" s="1">
+        <v>2</v>
+      </c>
+      <c r="D142" s="1">
+        <v>2</v>
+      </c>
+      <c r="E142" s="1">
+        <v>1</v>
+      </c>
+      <c r="F142" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A143" s="1">
+        <v>1000003</v>
+      </c>
+      <c r="B143" s="1">
+        <v>100</v>
+      </c>
+      <c r="C143" s="1">
+        <v>3</v>
+      </c>
+      <c r="D143" s="1">
+        <v>2</v>
+      </c>
+      <c r="E143" s="1">
+        <v>1</v>
+      </c>
+      <c r="F143" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A144" s="1">
+        <v>1000004</v>
+      </c>
+      <c r="B144" s="1">
+        <v>100</v>
+      </c>
+      <c r="C144" s="1">
+        <v>4</v>
+      </c>
+      <c r="D144" s="1">
+        <v>2</v>
+      </c>
+      <c r="E144" s="1">
+        <v>1</v>
+      </c>
+      <c r="F144" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A145" s="1">
+        <v>1000005</v>
+      </c>
+      <c r="B145" s="1">
+        <v>100</v>
+      </c>
+      <c r="C145" s="1">
+        <v>5</v>
+      </c>
+      <c r="D145" s="1">
+        <v>2</v>
+      </c>
+      <c r="E145" s="1">
+        <v>1</v>
+      </c>
+      <c r="F145" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A146" s="1">
+        <v>1000006</v>
+      </c>
+      <c r="B146" s="1">
+        <v>100</v>
+      </c>
+      <c r="C146" s="1">
+        <v>6</v>
+      </c>
+      <c r="D146" s="1">
+        <v>2</v>
+      </c>
+      <c r="E146" s="1">
+        <v>1</v>
+      </c>
+      <c r="F146" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A147" s="1">
+        <v>1000007</v>
+      </c>
+      <c r="B147" s="1">
+        <v>100</v>
+      </c>
+      <c r="C147" s="1">
+        <v>7</v>
+      </c>
+      <c r="D147" s="1">
+        <v>2</v>
+      </c>
+      <c r="E147" s="1">
+        <v>1</v>
+      </c>
+      <c r="F147" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A148" s="1">
+        <v>1000008</v>
+      </c>
+      <c r="B148" s="1">
+        <v>100</v>
+      </c>
+      <c r="C148" s="1">
+        <v>8</v>
+      </c>
+      <c r="D148" s="1">
+        <v>2</v>
+      </c>
+      <c r="E148" s="1">
+        <v>1</v>
+      </c>
+      <c r="F148" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A149" s="1">
+        <v>1000009</v>
+      </c>
+      <c r="B149" s="1">
+        <v>100</v>
+      </c>
+      <c r="C149" s="1">
+        <v>9</v>
+      </c>
+      <c r="D149" s="1">
+        <v>2</v>
+      </c>
+      <c r="E149" s="1">
+        <v>1</v>
+      </c>
+      <c r="F149" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A150" s="1">
+        <v>1000010</v>
+      </c>
+      <c r="B150" s="1">
+        <v>100</v>
+      </c>
+      <c r="C150" s="1">
+        <v>10</v>
+      </c>
+      <c r="D150" s="1">
+        <v>2</v>
+      </c>
+      <c r="E150" s="1">
+        <v>1</v>
+      </c>
+      <c r="F150" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A151" s="1">
+        <v>1000011</v>
+      </c>
+      <c r="B151" s="1">
+        <v>100</v>
+      </c>
+      <c r="C151" s="1">
+        <v>11</v>
+      </c>
+      <c r="D151" s="1">
+        <v>2</v>
+      </c>
+      <c r="E151" s="1">
+        <v>1</v>
+      </c>
+      <c r="F151" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A152" s="1">
+        <v>1000012</v>
+      </c>
+      <c r="B152" s="1">
+        <v>100</v>
+      </c>
+      <c r="C152" s="1">
+        <v>12</v>
+      </c>
+      <c r="D152" s="1">
+        <v>2</v>
+      </c>
+      <c r="E152" s="1">
+        <v>1</v>
+      </c>
+      <c r="F152" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A153" s="1">
+        <v>1000013</v>
+      </c>
+      <c r="B153" s="1">
+        <v>100</v>
+      </c>
+      <c r="C153" s="1">
+        <v>13</v>
+      </c>
+      <c r="D153" s="1">
+        <v>2</v>
+      </c>
+      <c r="E153" s="1">
+        <v>1</v>
+      </c>
+      <c r="F153" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A154" s="1">
+        <v>1000014</v>
+      </c>
+      <c r="B154" s="1">
+        <v>100</v>
+      </c>
+      <c r="C154" s="1">
+        <v>14</v>
+      </c>
+      <c r="D154" s="1">
+        <v>2</v>
+      </c>
+      <c r="E154" s="1">
+        <v>1</v>
+      </c>
+      <c r="F154" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A155" s="1">
+        <v>1000015</v>
+      </c>
+      <c r="B155" s="1">
+        <v>100</v>
+      </c>
+      <c r="C155" s="1">
+        <v>15</v>
+      </c>
+      <c r="D155" s="1">
+        <v>2</v>
+      </c>
+      <c r="E155" s="1">
+        <v>1</v>
+      </c>
+      <c r="F155" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A156" s="1">
+        <v>1000016</v>
+      </c>
+      <c r="B156" s="1">
+        <v>100</v>
+      </c>
+      <c r="C156" s="1">
+        <v>16</v>
+      </c>
+      <c r="D156" s="1">
+        <v>2</v>
+      </c>
+      <c r="E156" s="1">
+        <v>1</v>
+      </c>
+      <c r="F156" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A157" s="1">
+        <v>1000017</v>
+      </c>
+      <c r="B157" s="1">
+        <v>100</v>
+      </c>
+      <c r="C157" s="1">
+        <v>17</v>
+      </c>
+      <c r="D157" s="1">
+        <v>2</v>
+      </c>
+      <c r="E157" s="1">
+        <v>1</v>
+      </c>
+      <c r="F157" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A158" s="1">
+        <v>1000018</v>
+      </c>
+      <c r="B158" s="1">
+        <v>100</v>
+      </c>
+      <c r="C158" s="1">
+        <v>18</v>
+      </c>
+      <c r="D158" s="1">
+        <v>2</v>
+      </c>
+      <c r="E158" s="1">
+        <v>1</v>
+      </c>
+      <c r="F158" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A159" s="1">
+        <v>1000019</v>
+      </c>
+      <c r="B159" s="1">
+        <v>100</v>
+      </c>
+      <c r="C159" s="1">
+        <v>19</v>
+      </c>
+      <c r="D159" s="1">
+        <v>2</v>
+      </c>
+      <c r="E159" s="1">
+        <v>1</v>
+      </c>
+      <c r="F159" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A160" s="1">
+        <v>1000020</v>
+      </c>
+      <c r="B160" s="1">
+        <v>100</v>
+      </c>
+      <c r="C160" s="1">
+        <v>20</v>
+      </c>
+      <c r="D160" s="1">
+        <v>2</v>
+      </c>
+      <c r="E160" s="1">
+        <v>1</v>
+      </c>
+      <c r="F160" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A161" s="1">
+        <v>1000021</v>
+      </c>
+      <c r="B161" s="1">
+        <v>100</v>
+      </c>
+      <c r="C161" s="1">
+        <v>21</v>
+      </c>
+      <c r="D161" s="1">
+        <v>2</v>
+      </c>
+      <c r="E161" s="1">
+        <v>1</v>
+      </c>
+      <c r="F161" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A162" s="1">
+        <v>1000022</v>
+      </c>
+      <c r="B162" s="1">
+        <v>100</v>
+      </c>
+      <c r="C162" s="1">
+        <v>22</v>
+      </c>
+      <c r="D162" s="1">
+        <v>2</v>
+      </c>
+      <c r="E162" s="1">
+        <v>1</v>
+      </c>
+      <c r="F162" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A163" s="1">
+        <v>1000023</v>
+      </c>
+      <c r="B163" s="1">
+        <v>100</v>
+      </c>
+      <c r="C163" s="1">
+        <v>23</v>
+      </c>
+      <c r="D163" s="1">
+        <v>2</v>
+      </c>
+      <c r="E163" s="1">
+        <v>1</v>
+      </c>
+      <c r="F163" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A164" s="1">
+        <v>1000024</v>
+      </c>
+      <c r="B164" s="1">
+        <v>100</v>
+      </c>
+      <c r="C164" s="1">
+        <v>24</v>
+      </c>
+      <c r="D164" s="1">
+        <v>2</v>
+      </c>
+      <c r="E164" s="1">
+        <v>1</v>
+      </c>
+      <c r="F164" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A165" s="1">
+        <v>1000025</v>
+      </c>
+      <c r="B165" s="1">
+        <v>100</v>
+      </c>
+      <c r="C165" s="1">
+        <v>25</v>
+      </c>
+      <c r="D165" s="1">
+        <v>2</v>
+      </c>
+      <c r="E165" s="1">
+        <v>1</v>
+      </c>
+      <c r="F165" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A166" s="1">
+        <v>1000026</v>
+      </c>
+      <c r="B166" s="1">
+        <v>100</v>
+      </c>
+      <c r="C166" s="1">
+        <v>26</v>
+      </c>
+      <c r="D166" s="1">
+        <v>2</v>
+      </c>
+      <c r="E166" s="1">
+        <v>1</v>
+      </c>
+      <c r="F166" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A167" s="1">
+        <v>1000027</v>
+      </c>
+      <c r="B167" s="1">
+        <v>100</v>
+      </c>
+      <c r="C167" s="1">
+        <v>27</v>
+      </c>
+      <c r="D167" s="1">
+        <v>2</v>
+      </c>
+      <c r="E167" s="1">
+        <v>1</v>
+      </c>
+      <c r="F167" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A168" s="1">
+        <v>1000028</v>
+      </c>
+      <c r="B168" s="1">
+        <v>100</v>
+      </c>
+      <c r="C168" s="1">
+        <v>28</v>
+      </c>
+      <c r="D168" s="1">
+        <v>2</v>
+      </c>
+      <c r="E168" s="1">
+        <v>1</v>
+      </c>
+      <c r="F168" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A169" s="1">
+        <v>1000029</v>
+      </c>
+      <c r="B169" s="1">
+        <v>100</v>
+      </c>
+      <c r="C169" s="1">
+        <v>29</v>
+      </c>
+      <c r="D169" s="1">
+        <v>2</v>
+      </c>
+      <c r="E169" s="1">
+        <v>1</v>
+      </c>
+      <c r="F169" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A170" s="1">
+        <v>1000030</v>
+      </c>
+      <c r="B170" s="1">
+        <v>100</v>
+      </c>
+      <c r="C170" s="1">
+        <v>30</v>
+      </c>
+      <c r="D170" s="1">
+        <v>2</v>
+      </c>
+      <c r="E170" s="1">
+        <v>1</v>
+      </c>
+      <c r="F170" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A171" s="1">
+        <v>1000031</v>
+      </c>
+      <c r="B171" s="1">
+        <v>100</v>
+      </c>
+      <c r="C171" s="1">
+        <v>31</v>
+      </c>
+      <c r="D171" s="1">
+        <v>2</v>
+      </c>
+      <c r="E171" s="1">
+        <v>1</v>
+      </c>
+      <c r="F171" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A172" s="1">
+        <v>1000032</v>
+      </c>
+      <c r="B172" s="1">
+        <v>100</v>
+      </c>
+      <c r="C172" s="1">
+        <v>32</v>
+      </c>
+      <c r="D172" s="1">
+        <v>2</v>
+      </c>
+      <c r="E172" s="1">
+        <v>1</v>
+      </c>
+      <c r="F172" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A173" s="1">
+        <v>1000033</v>
+      </c>
+      <c r="B173" s="1">
+        <v>100</v>
+      </c>
+      <c r="C173" s="1">
+        <v>33</v>
+      </c>
+      <c r="D173" s="1">
+        <v>2</v>
+      </c>
+      <c r="E173" s="1">
+        <v>1</v>
+      </c>
+      <c r="F173" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A174" s="1">
+        <v>1000034</v>
+      </c>
+      <c r="B174" s="1">
+        <v>100</v>
+      </c>
+      <c r="C174" s="1">
+        <v>34</v>
+      </c>
+      <c r="D174" s="1">
+        <v>2</v>
+      </c>
+      <c r="E174" s="1">
+        <v>1</v>
+      </c>
+      <c r="F174" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A175" s="1">
+        <v>1000035</v>
+      </c>
+      <c r="B175" s="1">
+        <v>100</v>
+      </c>
+      <c r="C175" s="1">
+        <v>35</v>
+      </c>
+      <c r="D175" s="1">
+        <v>2</v>
+      </c>
+      <c r="E175" s="1">
+        <v>1</v>
+      </c>
+      <c r="F175" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A176" s="1">
+        <v>1000036</v>
+      </c>
+      <c r="B176" s="1">
+        <v>100</v>
+      </c>
+      <c r="C176" s="1">
+        <v>36</v>
+      </c>
+      <c r="D176" s="1">
+        <v>2</v>
+      </c>
+      <c r="E176" s="1">
+        <v>1</v>
+      </c>
+      <c r="F176" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A177" s="1">
+        <v>1000037</v>
+      </c>
+      <c r="B177" s="1">
+        <v>100</v>
+      </c>
+      <c r="C177" s="1">
+        <v>37</v>
+      </c>
+      <c r="D177" s="1">
+        <v>2</v>
+      </c>
+      <c r="E177" s="1">
+        <v>1</v>
+      </c>
+      <c r="F177" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A178" s="1">
+        <v>1000038</v>
+      </c>
+      <c r="B178" s="1">
+        <v>100</v>
+      </c>
+      <c r="C178" s="1">
+        <v>38</v>
+      </c>
+      <c r="D178" s="1">
+        <v>2</v>
+      </c>
+      <c r="E178" s="1">
+        <v>1</v>
+      </c>
+      <c r="F178" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A179" s="1">
+        <v>1000039</v>
+      </c>
+      <c r="B179" s="1">
+        <v>100</v>
+      </c>
+      <c r="C179" s="1">
+        <v>39</v>
+      </c>
+      <c r="D179" s="1">
+        <v>2</v>
+      </c>
+      <c r="E179" s="1">
+        <v>1</v>
+      </c>
+      <c r="F179" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A180" s="1">
+        <v>1000040</v>
+      </c>
+      <c r="B180" s="1">
+        <v>100</v>
+      </c>
+      <c r="C180" s="1">
+        <v>40</v>
+      </c>
+      <c r="D180" s="1">
+        <v>2</v>
+      </c>
+      <c r="E180" s="1">
+        <v>1</v>
+      </c>
+      <c r="F180" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A181" s="1">
+        <v>1000041</v>
+      </c>
+      <c r="B181" s="1">
+        <v>100</v>
+      </c>
+      <c r="C181" s="1">
+        <v>41</v>
+      </c>
+      <c r="D181" s="1">
+        <v>2</v>
+      </c>
+      <c r="E181" s="1">
+        <v>1</v>
+      </c>
+      <c r="F181" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A182" s="1">
+        <v>1000042</v>
+      </c>
+      <c r="B182" s="1">
+        <v>100</v>
+      </c>
+      <c r="C182" s="1">
+        <v>42</v>
+      </c>
+      <c r="D182" s="1">
+        <v>2</v>
+      </c>
+      <c r="E182" s="1">
+        <v>1</v>
+      </c>
+      <c r="F182" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A183" s="1">
+        <v>1000043</v>
+      </c>
+      <c r="B183" s="1">
+        <v>100</v>
+      </c>
+      <c r="C183" s="1">
+        <v>43</v>
+      </c>
+      <c r="D183" s="1">
+        <v>2</v>
+      </c>
+      <c r="E183" s="1">
+        <v>1</v>
+      </c>
+      <c r="F183" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A184" s="1">
+        <v>1000044</v>
+      </c>
+      <c r="B184" s="1">
+        <v>100</v>
+      </c>
+      <c r="C184" s="1">
+        <v>44</v>
+      </c>
+      <c r="D184" s="1">
+        <v>2</v>
+      </c>
+      <c r="E184" s="1">
+        <v>1</v>
+      </c>
+      <c r="F184" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A185" s="1">
+        <v>1000045</v>
+      </c>
+      <c r="B185" s="1">
+        <v>100</v>
+      </c>
+      <c r="C185" s="1">
+        <v>45</v>
+      </c>
+      <c r="D185" s="1">
+        <v>2</v>
+      </c>
+      <c r="E185" s="1">
+        <v>1</v>
+      </c>
+      <c r="F185" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A186" s="1">
+        <v>1000046</v>
+      </c>
+      <c r="B186" s="1">
+        <v>100</v>
+      </c>
+      <c r="C186" s="1">
+        <v>46</v>
+      </c>
+      <c r="D186" s="1">
+        <v>2</v>
+      </c>
+      <c r="E186" s="1">
+        <v>1</v>
+      </c>
+      <c r="F186" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A187" s="1">
+        <v>1000047</v>
+      </c>
+      <c r="B187" s="1">
+        <v>100</v>
+      </c>
+      <c r="C187" s="1">
+        <v>47</v>
+      </c>
+      <c r="D187" s="1">
+        <v>2</v>
+      </c>
+      <c r="E187" s="1">
+        <v>1</v>
+      </c>
+      <c r="F187" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A188" s="1">
+        <v>1000048</v>
+      </c>
+      <c r="B188" s="1">
+        <v>100</v>
+      </c>
+      <c r="C188" s="1">
+        <v>48</v>
+      </c>
+      <c r="D188" s="1">
+        <v>2</v>
+      </c>
+      <c r="E188" s="1">
+        <v>1</v>
+      </c>
+      <c r="F188" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A189" s="1">
+        <v>1000049</v>
+      </c>
+      <c r="B189" s="1">
+        <v>100</v>
+      </c>
+      <c r="C189" s="1">
+        <v>49</v>
+      </c>
+      <c r="D189" s="1">
+        <v>2</v>
+      </c>
+      <c r="E189" s="1">
+        <v>1</v>
+      </c>
+      <c r="F189" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A190" s="1">
+        <v>1000050</v>
+      </c>
+      <c r="B190" s="1">
+        <v>100</v>
+      </c>
+      <c r="C190" s="1">
+        <v>50</v>
+      </c>
+      <c r="D190" s="1">
+        <v>2</v>
+      </c>
+      <c r="E190" s="1">
+        <v>1</v>
+      </c>
+      <c r="F190" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A191" s="1">
+        <v>1000051</v>
+      </c>
+      <c r="B191" s="1">
+        <v>100</v>
+      </c>
+      <c r="C191" s="1">
+        <v>51</v>
+      </c>
+      <c r="D191" s="1">
+        <v>2</v>
+      </c>
+      <c r="E191" s="1">
+        <v>1</v>
+      </c>
+      <c r="F191" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A192" s="1">
+        <v>1000052</v>
+      </c>
+      <c r="B192" s="1">
+        <v>100</v>
+      </c>
+      <c r="C192" s="1">
+        <v>52</v>
+      </c>
+      <c r="D192" s="1">
+        <v>2</v>
+      </c>
+      <c r="E192" s="1">
+        <v>1</v>
+      </c>
+      <c r="F192" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A193" s="1">
+        <v>1000053</v>
+      </c>
+      <c r="B193" s="1">
+        <v>100</v>
+      </c>
+      <c r="C193" s="1">
+        <v>53</v>
+      </c>
+      <c r="D193" s="1">
+        <v>2</v>
+      </c>
+      <c r="E193" s="1">
+        <v>1</v>
+      </c>
+      <c r="F193" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A194" s="1">
+        <v>1000054</v>
+      </c>
+      <c r="B194" s="1">
+        <v>100</v>
+      </c>
+      <c r="C194" s="1">
+        <v>54</v>
+      </c>
+      <c r="D194" s="1">
+        <v>2</v>
+      </c>
+      <c r="E194" s="1">
+        <v>1</v>
+      </c>
+      <c r="F194" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A195" s="1">
+        <v>1000055</v>
+      </c>
+      <c r="B195" s="1">
+        <v>100</v>
+      </c>
+      <c r="C195" s="1">
+        <v>55</v>
+      </c>
+      <c r="D195" s="1">
+        <v>2</v>
+      </c>
+      <c r="E195" s="1">
+        <v>1</v>
+      </c>
+      <c r="F195" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A196" s="1">
+        <v>1000056</v>
+      </c>
+      <c r="B196" s="1">
+        <v>100</v>
+      </c>
+      <c r="C196" s="1">
+        <v>56</v>
+      </c>
+      <c r="D196" s="1">
+        <v>2</v>
+      </c>
+      <c r="E196" s="1">
+        <v>1</v>
+      </c>
+      <c r="F196" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A197" s="1">
+        <v>1000057</v>
+      </c>
+      <c r="B197" s="1">
+        <v>100</v>
+      </c>
+      <c r="C197" s="1">
+        <v>57</v>
+      </c>
+      <c r="D197" s="1">
+        <v>2</v>
+      </c>
+      <c r="E197" s="1">
+        <v>1</v>
+      </c>
+      <c r="F197" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A198" s="1">
+        <v>1000058</v>
+      </c>
+      <c r="B198" s="1">
+        <v>100</v>
+      </c>
+      <c r="C198" s="1">
+        <v>58</v>
+      </c>
+      <c r="D198" s="1">
+        <v>2</v>
+      </c>
+      <c r="E198" s="1">
+        <v>1</v>
+      </c>
+      <c r="F198" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A199" s="1">
+        <v>1000059</v>
+      </c>
+      <c r="B199" s="1">
+        <v>100</v>
+      </c>
+      <c r="C199" s="1">
+        <v>59</v>
+      </c>
+      <c r="D199" s="1">
+        <v>2</v>
+      </c>
+      <c r="E199" s="1">
+        <v>1</v>
+      </c>
+      <c r="F199" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A200" s="1">
+        <v>1000060</v>
+      </c>
+      <c r="B200" s="1">
+        <v>100</v>
+      </c>
+      <c r="C200" s="1">
+        <v>60</v>
+      </c>
+      <c r="D200" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E200" s="1">
+        <v>1</v>
+      </c>
+      <c r="F200" s="1">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D83668-876C-461C-98DC-90D3DB7A3D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD9CC1A-252A-4F29-A32D-9EB8F1B05899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$229</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F200"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
@@ -3061,7 +3061,7 @@
         <v>2</v>
       </c>
       <c r="D132" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -3081,7 +3081,7 @@
         <v>3</v>
       </c>
       <c r="D133" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -3101,7 +3101,7 @@
         <v>4</v>
       </c>
       <c r="D134" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -3121,7 +3121,7 @@
         <v>5</v>
       </c>
       <c r="D135" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -3141,7 +3141,7 @@
         <v>6</v>
       </c>
       <c r="D136" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
@@ -3161,7 +3161,7 @@
         <v>7</v>
       </c>
       <c r="D137" s="1">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -3181,7 +3181,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
@@ -3201,7 +3201,7 @@
         <v>9</v>
       </c>
       <c r="D139" s="1">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>
@@ -3221,7 +3221,7 @@
         <v>10</v>
       </c>
       <c r="D140" s="1">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="E140" s="1">
         <v>1</v>
@@ -3232,36 +3232,36 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>1000001</v>
+        <v>990011</v>
       </c>
       <c r="B141" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C141" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D141" s="1">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E141" s="1">
         <v>0</v>
       </c>
       <c r="F141" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>1000002</v>
+        <v>990012</v>
       </c>
       <c r="B142" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C142" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D142" s="1">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E142" s="1">
         <v>1</v>
@@ -3272,16 +3272,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>1000003</v>
+        <v>990013</v>
       </c>
       <c r="B143" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C143" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D143" s="1">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E143" s="1">
         <v>1</v>
@@ -3292,16 +3292,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>1000004</v>
+        <v>990014</v>
       </c>
       <c r="B144" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C144" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D144" s="1">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E144" s="1">
         <v>1</v>
@@ -3312,16 +3312,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>1000005</v>
+        <v>990015</v>
       </c>
       <c r="B145" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C145" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D145" s="1">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E145" s="1">
         <v>1</v>
@@ -3332,16 +3332,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>1000006</v>
+        <v>990016</v>
       </c>
       <c r="B146" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C146" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D146" s="1">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="E146" s="1">
         <v>1</v>
@@ -3352,16 +3352,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>1000007</v>
+        <v>990017</v>
       </c>
       <c r="B147" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C147" s="1">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D147" s="1">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E147" s="1">
         <v>1</v>
@@ -3372,16 +3372,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>1000008</v>
+        <v>990018</v>
       </c>
       <c r="B148" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C148" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D148" s="1">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E148" s="1">
         <v>1</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>1000009</v>
+        <v>990019</v>
       </c>
       <c r="B149" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C149" s="1">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D149" s="1">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="E149" s="1">
         <v>1</v>
@@ -3412,16 +3412,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>1000010</v>
+        <v>990020</v>
       </c>
       <c r="B150" s="1">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C150" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D150" s="1">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E150" s="1">
         <v>1</v>
@@ -3432,33 +3432,33 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>1000011</v>
+        <v>1000001</v>
       </c>
       <c r="B151" s="1">
         <v>100</v>
       </c>
       <c r="C151" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D151" s="1">
         <v>2</v>
       </c>
       <c r="E151" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>1000012</v>
+        <v>1000002</v>
       </c>
       <c r="B152" s="1">
         <v>100</v>
       </c>
       <c r="C152" s="1">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D152" s="1">
         <v>2</v>
@@ -3472,13 +3472,13 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>1000013</v>
+        <v>1000003</v>
       </c>
       <c r="B153" s="1">
         <v>100</v>
       </c>
       <c r="C153" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D153" s="1">
         <v>2</v>
@@ -3492,13 +3492,13 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>1000014</v>
+        <v>1000004</v>
       </c>
       <c r="B154" s="1">
         <v>100</v>
       </c>
       <c r="C154" s="1">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D154" s="1">
         <v>2</v>
@@ -3512,13 +3512,13 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>1000015</v>
+        <v>1000005</v>
       </c>
       <c r="B155" s="1">
         <v>100</v>
       </c>
       <c r="C155" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D155" s="1">
         <v>2</v>
@@ -3532,13 +3532,13 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>1000016</v>
+        <v>1000006</v>
       </c>
       <c r="B156" s="1">
         <v>100</v>
       </c>
       <c r="C156" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D156" s="1">
         <v>2</v>
@@ -3552,13 +3552,13 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>1000017</v>
+        <v>1000007</v>
       </c>
       <c r="B157" s="1">
         <v>100</v>
       </c>
       <c r="C157" s="1">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D157" s="1">
         <v>2</v>
@@ -3572,13 +3572,13 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>1000018</v>
+        <v>1000008</v>
       </c>
       <c r="B158" s="1">
         <v>100</v>
       </c>
       <c r="C158" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D158" s="1">
         <v>2</v>
@@ -3592,13 +3592,13 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>1000019</v>
+        <v>1000009</v>
       </c>
       <c r="B159" s="1">
         <v>100</v>
       </c>
       <c r="C159" s="1">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D159" s="1">
         <v>2</v>
@@ -3612,13 +3612,13 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>1000020</v>
+        <v>1000010</v>
       </c>
       <c r="B160" s="1">
         <v>100</v>
       </c>
       <c r="C160" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D160" s="1">
         <v>2</v>
@@ -3632,13 +3632,13 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>1000021</v>
+        <v>1000011</v>
       </c>
       <c r="B161" s="1">
         <v>100</v>
       </c>
       <c r="C161" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D161" s="1">
         <v>2</v>
@@ -3652,13 +3652,13 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>1000022</v>
+        <v>1000012</v>
       </c>
       <c r="B162" s="1">
         <v>100</v>
       </c>
       <c r="C162" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D162" s="1">
         <v>2</v>
@@ -3672,13 +3672,13 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>1000023</v>
+        <v>1000013</v>
       </c>
       <c r="B163" s="1">
         <v>100</v>
       </c>
       <c r="C163" s="1">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D163" s="1">
         <v>2</v>
@@ -3692,13 +3692,13 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>1000024</v>
+        <v>1000014</v>
       </c>
       <c r="B164" s="1">
         <v>100</v>
       </c>
       <c r="C164" s="1">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D164" s="1">
         <v>2</v>
@@ -3712,13 +3712,13 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>1000025</v>
+        <v>1000015</v>
       </c>
       <c r="B165" s="1">
         <v>100</v>
       </c>
       <c r="C165" s="1">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D165" s="1">
         <v>2</v>
@@ -3732,13 +3732,13 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>1000026</v>
+        <v>1000016</v>
       </c>
       <c r="B166" s="1">
         <v>100</v>
       </c>
       <c r="C166" s="1">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D166" s="1">
         <v>2</v>
@@ -3752,13 +3752,13 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>1000027</v>
+        <v>1000017</v>
       </c>
       <c r="B167" s="1">
         <v>100</v>
       </c>
       <c r="C167" s="1">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D167" s="1">
         <v>2</v>
@@ -3772,13 +3772,13 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>1000028</v>
+        <v>1000018</v>
       </c>
       <c r="B168" s="1">
         <v>100</v>
       </c>
       <c r="C168" s="1">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D168" s="1">
         <v>2</v>
@@ -3792,13 +3792,13 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>1000029</v>
+        <v>1000019</v>
       </c>
       <c r="B169" s="1">
         <v>100</v>
       </c>
       <c r="C169" s="1">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D169" s="1">
         <v>2</v>
@@ -3812,13 +3812,13 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>1000030</v>
+        <v>1000020</v>
       </c>
       <c r="B170" s="1">
         <v>100</v>
       </c>
       <c r="C170" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D170" s="1">
         <v>2</v>
@@ -3832,13 +3832,13 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>1000031</v>
+        <v>1000021</v>
       </c>
       <c r="B171" s="1">
         <v>100</v>
       </c>
       <c r="C171" s="1">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D171" s="1">
         <v>2</v>
@@ -3852,13 +3852,13 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>1000032</v>
+        <v>1000022</v>
       </c>
       <c r="B172" s="1">
         <v>100</v>
       </c>
       <c r="C172" s="1">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D172" s="1">
         <v>2</v>
@@ -3872,13 +3872,13 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>1000033</v>
+        <v>1000023</v>
       </c>
       <c r="B173" s="1">
         <v>100</v>
       </c>
       <c r="C173" s="1">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D173" s="1">
         <v>2</v>
@@ -3892,13 +3892,13 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>1000034</v>
+        <v>1000024</v>
       </c>
       <c r="B174" s="1">
         <v>100</v>
       </c>
       <c r="C174" s="1">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D174" s="1">
         <v>2</v>
@@ -3912,13 +3912,13 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>1000035</v>
+        <v>1000025</v>
       </c>
       <c r="B175" s="1">
         <v>100</v>
       </c>
       <c r="C175" s="1">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D175" s="1">
         <v>2</v>
@@ -3932,13 +3932,13 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>1000036</v>
+        <v>1000026</v>
       </c>
       <c r="B176" s="1">
         <v>100</v>
       </c>
       <c r="C176" s="1">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D176" s="1">
         <v>2</v>
@@ -3952,13 +3952,13 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>1000037</v>
+        <v>1000027</v>
       </c>
       <c r="B177" s="1">
         <v>100</v>
       </c>
       <c r="C177" s="1">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D177" s="1">
         <v>2</v>
@@ -3972,13 +3972,13 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>1000038</v>
+        <v>1000028</v>
       </c>
       <c r="B178" s="1">
         <v>100</v>
       </c>
       <c r="C178" s="1">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D178" s="1">
         <v>2</v>
@@ -3992,13 +3992,13 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>1000039</v>
+        <v>1000029</v>
       </c>
       <c r="B179" s="1">
         <v>100</v>
       </c>
       <c r="C179" s="1">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D179" s="1">
         <v>2</v>
@@ -4012,13 +4012,13 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>1000040</v>
+        <v>1000030</v>
       </c>
       <c r="B180" s="1">
         <v>100</v>
       </c>
       <c r="C180" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D180" s="1">
         <v>2</v>
@@ -4032,13 +4032,13 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>1000041</v>
+        <v>1000031</v>
       </c>
       <c r="B181" s="1">
         <v>100</v>
       </c>
       <c r="C181" s="1">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D181" s="1">
         <v>2</v>
@@ -4052,13 +4052,13 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>1000042</v>
+        <v>1000032</v>
       </c>
       <c r="B182" s="1">
         <v>100</v>
       </c>
       <c r="C182" s="1">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D182" s="1">
         <v>2</v>
@@ -4072,13 +4072,13 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>1000043</v>
+        <v>1000033</v>
       </c>
       <c r="B183" s="1">
         <v>100</v>
       </c>
       <c r="C183" s="1">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D183" s="1">
         <v>2</v>
@@ -4092,13 +4092,13 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>1000044</v>
+        <v>1000034</v>
       </c>
       <c r="B184" s="1">
         <v>100</v>
       </c>
       <c r="C184" s="1">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D184" s="1">
         <v>2</v>
@@ -4112,13 +4112,13 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>1000045</v>
+        <v>1000035</v>
       </c>
       <c r="B185" s="1">
         <v>100</v>
       </c>
       <c r="C185" s="1">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D185" s="1">
         <v>2</v>
@@ -4132,13 +4132,13 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>1000046</v>
+        <v>1000036</v>
       </c>
       <c r="B186" s="1">
         <v>100</v>
       </c>
       <c r="C186" s="1">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D186" s="1">
         <v>2</v>
@@ -4152,13 +4152,13 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>1000047</v>
+        <v>1000037</v>
       </c>
       <c r="B187" s="1">
         <v>100</v>
       </c>
       <c r="C187" s="1">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D187" s="1">
         <v>2</v>
@@ -4172,13 +4172,13 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>1000048</v>
+        <v>1000038</v>
       </c>
       <c r="B188" s="1">
         <v>100</v>
       </c>
       <c r="C188" s="1">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D188" s="1">
         <v>2</v>
@@ -4192,13 +4192,13 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>1000049</v>
+        <v>1000039</v>
       </c>
       <c r="B189" s="1">
         <v>100</v>
       </c>
       <c r="C189" s="1">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="D189" s="1">
         <v>2</v>
@@ -4212,13 +4212,13 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>1000050</v>
+        <v>1000040</v>
       </c>
       <c r="B190" s="1">
         <v>100</v>
       </c>
       <c r="C190" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D190" s="1">
         <v>2</v>
@@ -4232,13 +4232,13 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>1000051</v>
+        <v>1000041</v>
       </c>
       <c r="B191" s="1">
         <v>100</v>
       </c>
       <c r="C191" s="1">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D191" s="1">
         <v>2</v>
@@ -4252,13 +4252,13 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>1000052</v>
+        <v>1000042</v>
       </c>
       <c r="B192" s="1">
         <v>100</v>
       </c>
       <c r="C192" s="1">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="D192" s="1">
         <v>2</v>
@@ -4272,13 +4272,13 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>1000053</v>
+        <v>1000043</v>
       </c>
       <c r="B193" s="1">
         <v>100</v>
       </c>
       <c r="C193" s="1">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D193" s="1">
         <v>2</v>
@@ -4292,13 +4292,13 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>1000054</v>
+        <v>1000044</v>
       </c>
       <c r="B194" s="1">
         <v>100</v>
       </c>
       <c r="C194" s="1">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="D194" s="1">
         <v>2</v>
@@ -4312,13 +4312,13 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>1000055</v>
+        <v>1000045</v>
       </c>
       <c r="B195" s="1">
         <v>100</v>
       </c>
       <c r="C195" s="1">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="D195" s="1">
         <v>2</v>
@@ -4332,13 +4332,13 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>1000056</v>
+        <v>1000046</v>
       </c>
       <c r="B196" s="1">
         <v>100</v>
       </c>
       <c r="C196" s="1">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D196" s="1">
         <v>2</v>
@@ -4352,13 +4352,13 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>1000057</v>
+        <v>1000047</v>
       </c>
       <c r="B197" s="1">
         <v>100</v>
       </c>
       <c r="C197" s="1">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D197" s="1">
         <v>2</v>
@@ -4372,13 +4372,13 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>1000058</v>
+        <v>1000048</v>
       </c>
       <c r="B198" s="1">
         <v>100</v>
       </c>
       <c r="C198" s="1">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D198" s="1">
         <v>2</v>
@@ -4392,13 +4392,13 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>1000059</v>
+        <v>1000049</v>
       </c>
       <c r="B199" s="1">
         <v>100</v>
       </c>
       <c r="C199" s="1">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="D199" s="1">
         <v>2</v>
@@ -4412,21 +4412,221 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
+        <v>1000050</v>
+      </c>
+      <c r="B200" s="1">
+        <v>100</v>
+      </c>
+      <c r="C200" s="1">
+        <v>50</v>
+      </c>
+      <c r="D200" s="1">
+        <v>2</v>
+      </c>
+      <c r="E200" s="1">
+        <v>1</v>
+      </c>
+      <c r="F200" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A201" s="1">
+        <v>1000051</v>
+      </c>
+      <c r="B201" s="1">
+        <v>100</v>
+      </c>
+      <c r="C201" s="1">
+        <v>51</v>
+      </c>
+      <c r="D201" s="1">
+        <v>2</v>
+      </c>
+      <c r="E201" s="1">
+        <v>1</v>
+      </c>
+      <c r="F201" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A202" s="1">
+        <v>1000052</v>
+      </c>
+      <c r="B202" s="1">
+        <v>100</v>
+      </c>
+      <c r="C202" s="1">
+        <v>52</v>
+      </c>
+      <c r="D202" s="1">
+        <v>2</v>
+      </c>
+      <c r="E202" s="1">
+        <v>1</v>
+      </c>
+      <c r="F202" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A203" s="1">
+        <v>1000053</v>
+      </c>
+      <c r="B203" s="1">
+        <v>100</v>
+      </c>
+      <c r="C203" s="1">
+        <v>53</v>
+      </c>
+      <c r="D203" s="1">
+        <v>2</v>
+      </c>
+      <c r="E203" s="1">
+        <v>1</v>
+      </c>
+      <c r="F203" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A204" s="1">
+        <v>1000054</v>
+      </c>
+      <c r="B204" s="1">
+        <v>100</v>
+      </c>
+      <c r="C204" s="1">
+        <v>54</v>
+      </c>
+      <c r="D204" s="1">
+        <v>2</v>
+      </c>
+      <c r="E204" s="1">
+        <v>1</v>
+      </c>
+      <c r="F204" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A205" s="1">
+        <v>1000055</v>
+      </c>
+      <c r="B205" s="1">
+        <v>100</v>
+      </c>
+      <c r="C205" s="1">
+        <v>55</v>
+      </c>
+      <c r="D205" s="1">
+        <v>2</v>
+      </c>
+      <c r="E205" s="1">
+        <v>1</v>
+      </c>
+      <c r="F205" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A206" s="1">
+        <v>1000056</v>
+      </c>
+      <c r="B206" s="1">
+        <v>100</v>
+      </c>
+      <c r="C206" s="1">
+        <v>56</v>
+      </c>
+      <c r="D206" s="1">
+        <v>2</v>
+      </c>
+      <c r="E206" s="1">
+        <v>1</v>
+      </c>
+      <c r="F206" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A207" s="1">
+        <v>1000057</v>
+      </c>
+      <c r="B207" s="1">
+        <v>100</v>
+      </c>
+      <c r="C207" s="1">
+        <v>57</v>
+      </c>
+      <c r="D207" s="1">
+        <v>2</v>
+      </c>
+      <c r="E207" s="1">
+        <v>1</v>
+      </c>
+      <c r="F207" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A208" s="1">
+        <v>1000058</v>
+      </c>
+      <c r="B208" s="1">
+        <v>100</v>
+      </c>
+      <c r="C208" s="1">
+        <v>58</v>
+      </c>
+      <c r="D208" s="1">
+        <v>2</v>
+      </c>
+      <c r="E208" s="1">
+        <v>1</v>
+      </c>
+      <c r="F208" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A209" s="1">
+        <v>1000059</v>
+      </c>
+      <c r="B209" s="1">
+        <v>100</v>
+      </c>
+      <c r="C209" s="1">
+        <v>59</v>
+      </c>
+      <c r="D209" s="1">
+        <v>2</v>
+      </c>
+      <c r="E209" s="1">
+        <v>1</v>
+      </c>
+      <c r="F209" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A210" s="1">
         <v>1000060</v>
       </c>
-      <c r="B200" s="1">
-        <v>100</v>
-      </c>
-      <c r="C200" s="1">
+      <c r="B210" s="1">
+        <v>100</v>
+      </c>
+      <c r="C210" s="1">
         <v>60</v>
       </c>
-      <c r="D200" s="1">
+      <c r="D210" s="1">
         <v>-1</v>
       </c>
-      <c r="E200" s="1">
-        <v>1</v>
-      </c>
-      <c r="F200" s="1">
+      <c r="E210" s="1">
+        <v>1</v>
+      </c>
+      <c r="F210" s="1">
         <v>1</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACD9CC1A-252A-4F29-A32D-9EB8F1B05899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C70FD8-C5A9-4DCB-9369-31AA79A5BE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,6 +101,246 @@
   <si>
     <t>INT_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1101001</t>
+  </si>
+  <si>
+    <t>1101002</t>
+  </si>
+  <si>
+    <t>1101003</t>
+  </si>
+  <si>
+    <t>1101004</t>
+  </si>
+  <si>
+    <t>1101005</t>
+  </si>
+  <si>
+    <t>1101006</t>
+  </si>
+  <si>
+    <t>1101007</t>
+  </si>
+  <si>
+    <t>1101008</t>
+  </si>
+  <si>
+    <t>1101009</t>
+  </si>
+  <si>
+    <t>1101010</t>
+  </si>
+  <si>
+    <t>1101011</t>
+  </si>
+  <si>
+    <t>1101012</t>
+  </si>
+  <si>
+    <t>1101013</t>
+  </si>
+  <si>
+    <t>1101014</t>
+  </si>
+  <si>
+    <t>1101015</t>
+  </si>
+  <si>
+    <t>1101016</t>
+  </si>
+  <si>
+    <t>1101017</t>
+  </si>
+  <si>
+    <t>1101018</t>
+  </si>
+  <si>
+    <t>1101019</t>
+  </si>
+  <si>
+    <t>1101020</t>
+  </si>
+  <si>
+    <t>1102001</t>
+  </si>
+  <si>
+    <t>1102002</t>
+  </si>
+  <si>
+    <t>1102003</t>
+  </si>
+  <si>
+    <t>1102004</t>
+  </si>
+  <si>
+    <t>1102005</t>
+  </si>
+  <si>
+    <t>1102006</t>
+  </si>
+  <si>
+    <t>1102007</t>
+  </si>
+  <si>
+    <t>1102008</t>
+  </si>
+  <si>
+    <t>1102009</t>
+  </si>
+  <si>
+    <t>1102010</t>
+  </si>
+  <si>
+    <t>1102011</t>
+  </si>
+  <si>
+    <t>1102012</t>
+  </si>
+  <si>
+    <t>1102013</t>
+  </si>
+  <si>
+    <t>1102014</t>
+  </si>
+  <si>
+    <t>1102015</t>
+  </si>
+  <si>
+    <t>1102016</t>
+  </si>
+  <si>
+    <t>1102017</t>
+  </si>
+  <si>
+    <t>1102018</t>
+  </si>
+  <si>
+    <t>1102019</t>
+  </si>
+  <si>
+    <t>1102020</t>
+  </si>
+  <si>
+    <t>1103001</t>
+  </si>
+  <si>
+    <t>1103002</t>
+  </si>
+  <si>
+    <t>1103003</t>
+  </si>
+  <si>
+    <t>1103004</t>
+  </si>
+  <si>
+    <t>1103005</t>
+  </si>
+  <si>
+    <t>1103006</t>
+  </si>
+  <si>
+    <t>1103007</t>
+  </si>
+  <si>
+    <t>1103008</t>
+  </si>
+  <si>
+    <t>1103009</t>
+  </si>
+  <si>
+    <t>1103010</t>
+  </si>
+  <si>
+    <t>1103011</t>
+  </si>
+  <si>
+    <t>1103012</t>
+  </si>
+  <si>
+    <t>1103013</t>
+  </si>
+  <si>
+    <t>1103014</t>
+  </si>
+  <si>
+    <t>1103015</t>
+  </si>
+  <si>
+    <t>1103016</t>
+  </si>
+  <si>
+    <t>1103017</t>
+  </si>
+  <si>
+    <t>1103018</t>
+  </si>
+  <si>
+    <t>1103019</t>
+  </si>
+  <si>
+    <t>1103020</t>
+  </si>
+  <si>
+    <t>1104001</t>
+  </si>
+  <si>
+    <t>1104002</t>
+  </si>
+  <si>
+    <t>1104003</t>
+  </si>
+  <si>
+    <t>1104004</t>
+  </si>
+  <si>
+    <t>1104005</t>
+  </si>
+  <si>
+    <t>1104006</t>
+  </si>
+  <si>
+    <t>1104007</t>
+  </si>
+  <si>
+    <t>1104008</t>
+  </si>
+  <si>
+    <t>1104009</t>
+  </si>
+  <si>
+    <t>1104010</t>
+  </si>
+  <si>
+    <t>1104011</t>
+  </si>
+  <si>
+    <t>1104012</t>
+  </si>
+  <si>
+    <t>1104013</t>
+  </si>
+  <si>
+    <t>1104014</t>
+  </si>
+  <si>
+    <t>1104015</t>
+  </si>
+  <si>
+    <t>1104016</t>
+  </si>
+  <si>
+    <t>1104017</t>
+  </si>
+  <si>
+    <t>1104018</t>
+  </si>
+  <si>
+    <t>1104019</t>
+  </si>
+  <si>
+    <t>1104020</t>
   </si>
 </sst>
 </file>
@@ -433,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F210"/>
+  <dimension ref="A1:F290"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
@@ -4630,6 +4870,1606 @@
         <v>1</v>
       </c>
     </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A211" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B211" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C211" s="1">
+        <v>1</v>
+      </c>
+      <c r="D211" s="1">
+        <v>4</v>
+      </c>
+      <c r="E211" s="1">
+        <v>0</v>
+      </c>
+      <c r="F211" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A212" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B212" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C212" s="1">
+        <v>2</v>
+      </c>
+      <c r="D212" s="1">
+        <v>5</v>
+      </c>
+      <c r="E212" s="1">
+        <v>1</v>
+      </c>
+      <c r="F212" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A213" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B213" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C213" s="1">
+        <v>3</v>
+      </c>
+      <c r="D213" s="1">
+        <v>6</v>
+      </c>
+      <c r="E213" s="1">
+        <v>1</v>
+      </c>
+      <c r="F213" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A214" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B214" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C214" s="1">
+        <v>4</v>
+      </c>
+      <c r="D214" s="1">
+        <v>7</v>
+      </c>
+      <c r="E214" s="1">
+        <v>1</v>
+      </c>
+      <c r="F214" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A215" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B215" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C215" s="1">
+        <v>5</v>
+      </c>
+      <c r="D215" s="1">
+        <v>10</v>
+      </c>
+      <c r="E215" s="1">
+        <v>1</v>
+      </c>
+      <c r="F215" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A216" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B216" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C216" s="1">
+        <v>6</v>
+      </c>
+      <c r="D216" s="1">
+        <v>11</v>
+      </c>
+      <c r="E216" s="1">
+        <v>1</v>
+      </c>
+      <c r="F216" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A217" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B217" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C217" s="1">
+        <v>7</v>
+      </c>
+      <c r="D217" s="1">
+        <v>13</v>
+      </c>
+      <c r="E217" s="1">
+        <v>1</v>
+      </c>
+      <c r="F217" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A218" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B218" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C218" s="1">
+        <v>8</v>
+      </c>
+      <c r="D218" s="1">
+        <v>15</v>
+      </c>
+      <c r="E218" s="1">
+        <v>1</v>
+      </c>
+      <c r="F218" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A219" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B219" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C219" s="1">
+        <v>9</v>
+      </c>
+      <c r="D219" s="1">
+        <v>18</v>
+      </c>
+      <c r="E219" s="1">
+        <v>1</v>
+      </c>
+      <c r="F219" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A220" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B220" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C220" s="1">
+        <v>10</v>
+      </c>
+      <c r="D220" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E220" s="1">
+        <v>1</v>
+      </c>
+      <c r="F220" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A221" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B221" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C221" s="1">
+        <v>11</v>
+      </c>
+      <c r="D221" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E221" s="1">
+        <v>1</v>
+      </c>
+      <c r="F221" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A222" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B222" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C222" s="1">
+        <v>12</v>
+      </c>
+      <c r="D222" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E222" s="1">
+        <v>1</v>
+      </c>
+      <c r="F222" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A223" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B223" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C223" s="1">
+        <v>13</v>
+      </c>
+      <c r="D223" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E223" s="1">
+        <v>1</v>
+      </c>
+      <c r="F223" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A224" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B224" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C224" s="1">
+        <v>14</v>
+      </c>
+      <c r="D224" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E224" s="1">
+        <v>1</v>
+      </c>
+      <c r="F224" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A225" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B225" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C225" s="1">
+        <v>15</v>
+      </c>
+      <c r="D225" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E225" s="1">
+        <v>1</v>
+      </c>
+      <c r="F225" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A226" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B226" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C226" s="1">
+        <v>16</v>
+      </c>
+      <c r="D226" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E226" s="1">
+        <v>1</v>
+      </c>
+      <c r="F226" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A227" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B227" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C227" s="1">
+        <v>17</v>
+      </c>
+      <c r="D227" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E227" s="1">
+        <v>1</v>
+      </c>
+      <c r="F227" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A228" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B228" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C228" s="1">
+        <v>18</v>
+      </c>
+      <c r="D228" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E228" s="1">
+        <v>1</v>
+      </c>
+      <c r="F228" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A229" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B229" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C229" s="1">
+        <v>19</v>
+      </c>
+      <c r="D229" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E229" s="1">
+        <v>1</v>
+      </c>
+      <c r="F229" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A230" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B230" s="1">
+        <v>1101</v>
+      </c>
+      <c r="C230" s="1">
+        <v>20</v>
+      </c>
+      <c r="D230" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E230" s="1">
+        <v>1</v>
+      </c>
+      <c r="F230" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A231" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B231" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C231" s="1">
+        <v>1</v>
+      </c>
+      <c r="D231" s="1">
+        <v>4</v>
+      </c>
+      <c r="E231" s="1">
+        <v>0</v>
+      </c>
+      <c r="F231" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A232" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B232" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C232" s="1">
+        <v>2</v>
+      </c>
+      <c r="D232" s="1">
+        <v>5</v>
+      </c>
+      <c r="E232" s="1">
+        <v>1</v>
+      </c>
+      <c r="F232" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A233" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B233" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C233" s="1">
+        <v>3</v>
+      </c>
+      <c r="D233" s="1">
+        <v>6</v>
+      </c>
+      <c r="E233" s="1">
+        <v>1</v>
+      </c>
+      <c r="F233" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A234" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B234" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C234" s="1">
+        <v>4</v>
+      </c>
+      <c r="D234" s="1">
+        <v>7</v>
+      </c>
+      <c r="E234" s="1">
+        <v>1</v>
+      </c>
+      <c r="F234" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A235" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B235" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C235" s="1">
+        <v>5</v>
+      </c>
+      <c r="D235" s="1">
+        <v>10</v>
+      </c>
+      <c r="E235" s="1">
+        <v>1</v>
+      </c>
+      <c r="F235" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A236" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B236" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C236" s="1">
+        <v>6</v>
+      </c>
+      <c r="D236" s="1">
+        <v>11</v>
+      </c>
+      <c r="E236" s="1">
+        <v>1</v>
+      </c>
+      <c r="F236" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A237" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B237" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C237" s="1">
+        <v>7</v>
+      </c>
+      <c r="D237" s="1">
+        <v>13</v>
+      </c>
+      <c r="E237" s="1">
+        <v>1</v>
+      </c>
+      <c r="F237" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A238" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B238" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C238" s="1">
+        <v>8</v>
+      </c>
+      <c r="D238" s="1">
+        <v>15</v>
+      </c>
+      <c r="E238" s="1">
+        <v>1</v>
+      </c>
+      <c r="F238" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A239" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B239" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C239" s="1">
+        <v>9</v>
+      </c>
+      <c r="D239" s="1">
+        <v>18</v>
+      </c>
+      <c r="E239" s="1">
+        <v>1</v>
+      </c>
+      <c r="F239" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A240" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B240" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C240" s="1">
+        <v>10</v>
+      </c>
+      <c r="D240" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E240" s="1">
+        <v>1</v>
+      </c>
+      <c r="F240" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A241" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B241" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C241" s="1">
+        <v>11</v>
+      </c>
+      <c r="D241" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E241" s="1">
+        <v>1</v>
+      </c>
+      <c r="F241" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A242" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B242" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C242" s="1">
+        <v>12</v>
+      </c>
+      <c r="D242" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E242" s="1">
+        <v>1</v>
+      </c>
+      <c r="F242" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A243" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B243" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C243" s="1">
+        <v>13</v>
+      </c>
+      <c r="D243" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E243" s="1">
+        <v>1</v>
+      </c>
+      <c r="F243" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A244" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B244" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C244" s="1">
+        <v>14</v>
+      </c>
+      <c r="D244" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E244" s="1">
+        <v>1</v>
+      </c>
+      <c r="F244" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A245" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B245" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C245" s="1">
+        <v>15</v>
+      </c>
+      <c r="D245" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E245" s="1">
+        <v>1</v>
+      </c>
+      <c r="F245" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A246" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B246" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C246" s="1">
+        <v>16</v>
+      </c>
+      <c r="D246" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E246" s="1">
+        <v>1</v>
+      </c>
+      <c r="F246" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A247" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B247" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C247" s="1">
+        <v>17</v>
+      </c>
+      <c r="D247" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E247" s="1">
+        <v>1</v>
+      </c>
+      <c r="F247" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A248" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B248" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C248" s="1">
+        <v>18</v>
+      </c>
+      <c r="D248" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E248" s="1">
+        <v>1</v>
+      </c>
+      <c r="F248" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A249" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B249" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C249" s="1">
+        <v>19</v>
+      </c>
+      <c r="D249" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E249" s="1">
+        <v>1</v>
+      </c>
+      <c r="F249" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A250" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B250" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C250" s="1">
+        <v>20</v>
+      </c>
+      <c r="D250" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E250" s="1">
+        <v>1</v>
+      </c>
+      <c r="F250" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A251" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B251" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C251" s="1">
+        <v>1</v>
+      </c>
+      <c r="D251" s="1">
+        <v>4</v>
+      </c>
+      <c r="E251" s="1">
+        <v>0</v>
+      </c>
+      <c r="F251" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A252" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B252" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C252" s="1">
+        <v>2</v>
+      </c>
+      <c r="D252" s="1">
+        <v>6</v>
+      </c>
+      <c r="E252" s="1">
+        <v>1</v>
+      </c>
+      <c r="F252" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A253" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B253" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C253" s="1">
+        <v>3</v>
+      </c>
+      <c r="D253" s="1">
+        <v>8</v>
+      </c>
+      <c r="E253" s="1">
+        <v>1</v>
+      </c>
+      <c r="F253" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A254" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B254" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C254" s="1">
+        <v>4</v>
+      </c>
+      <c r="D254" s="1">
+        <v>11</v>
+      </c>
+      <c r="E254" s="1">
+        <v>1</v>
+      </c>
+      <c r="F254" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A255" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B255" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C255" s="1">
+        <v>5</v>
+      </c>
+      <c r="D255" s="1">
+        <v>14</v>
+      </c>
+      <c r="E255" s="1">
+        <v>1</v>
+      </c>
+      <c r="F255" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A256" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B256" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C256" s="1">
+        <v>6</v>
+      </c>
+      <c r="D256" s="1">
+        <v>17</v>
+      </c>
+      <c r="E256" s="1">
+        <v>1</v>
+      </c>
+      <c r="F256" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A257" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B257" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C257" s="1">
+        <v>7</v>
+      </c>
+      <c r="D257" s="1">
+        <v>19</v>
+      </c>
+      <c r="E257" s="1">
+        <v>1</v>
+      </c>
+      <c r="F257" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A258" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B258" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C258" s="1">
+        <v>8</v>
+      </c>
+      <c r="D258" s="1">
+        <v>21</v>
+      </c>
+      <c r="E258" s="1">
+        <v>1</v>
+      </c>
+      <c r="F258" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A259" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B259" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C259" s="1">
+        <v>9</v>
+      </c>
+      <c r="D259" s="1">
+        <v>27</v>
+      </c>
+      <c r="E259" s="1">
+        <v>1</v>
+      </c>
+      <c r="F259" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A260" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B260" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C260" s="1">
+        <v>10</v>
+      </c>
+      <c r="D260" s="1">
+        <v>29</v>
+      </c>
+      <c r="E260" s="1">
+        <v>1</v>
+      </c>
+      <c r="F260" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A261" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B261" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C261" s="1">
+        <v>11</v>
+      </c>
+      <c r="D261" s="1">
+        <v>35</v>
+      </c>
+      <c r="E261" s="1">
+        <v>1</v>
+      </c>
+      <c r="F261" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A262" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B262" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C262" s="1">
+        <v>12</v>
+      </c>
+      <c r="D262" s="1">
+        <v>39</v>
+      </c>
+      <c r="E262" s="1">
+        <v>1</v>
+      </c>
+      <c r="F262" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A263" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B263" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C263" s="1">
+        <v>13</v>
+      </c>
+      <c r="D263" s="1">
+        <v>39</v>
+      </c>
+      <c r="E263" s="1">
+        <v>1</v>
+      </c>
+      <c r="F263" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A264" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B264" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C264" s="1">
+        <v>14</v>
+      </c>
+      <c r="D264" s="1">
+        <v>39</v>
+      </c>
+      <c r="E264" s="1">
+        <v>1</v>
+      </c>
+      <c r="F264" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A265" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B265" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C265" s="1">
+        <v>15</v>
+      </c>
+      <c r="D265" s="1">
+        <v>39</v>
+      </c>
+      <c r="E265" s="1">
+        <v>1</v>
+      </c>
+      <c r="F265" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A266" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B266" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C266" s="1">
+        <v>16</v>
+      </c>
+      <c r="D266" s="1">
+        <v>46</v>
+      </c>
+      <c r="E266" s="1">
+        <v>1</v>
+      </c>
+      <c r="F266" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A267" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B267" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C267" s="1">
+        <v>17</v>
+      </c>
+      <c r="D267" s="1">
+        <v>48</v>
+      </c>
+      <c r="E267" s="1">
+        <v>1</v>
+      </c>
+      <c r="F267" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A268" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B268" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C268" s="1">
+        <v>18</v>
+      </c>
+      <c r="D268" s="1">
+        <v>48</v>
+      </c>
+      <c r="E268" s="1">
+        <v>1</v>
+      </c>
+      <c r="F268" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A269" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B269" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C269" s="1">
+        <v>19</v>
+      </c>
+      <c r="D269" s="1">
+        <v>48</v>
+      </c>
+      <c r="E269" s="1">
+        <v>1</v>
+      </c>
+      <c r="F269" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A270" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B270" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C270" s="1">
+        <v>20</v>
+      </c>
+      <c r="D270" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E270" s="1">
+        <v>1</v>
+      </c>
+      <c r="F270" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A271" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B271" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C271" s="1">
+        <v>1</v>
+      </c>
+      <c r="D271" s="1">
+        <v>4</v>
+      </c>
+      <c r="E271" s="1">
+        <v>0</v>
+      </c>
+      <c r="F271" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A272" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B272" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C272" s="1">
+        <v>2</v>
+      </c>
+      <c r="D272" s="1">
+        <v>6</v>
+      </c>
+      <c r="E272" s="1">
+        <v>1</v>
+      </c>
+      <c r="F272" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A273" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B273" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C273" s="1">
+        <v>3</v>
+      </c>
+      <c r="D273" s="1">
+        <v>8</v>
+      </c>
+      <c r="E273" s="1">
+        <v>1</v>
+      </c>
+      <c r="F273" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A274" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B274" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C274" s="1">
+        <v>4</v>
+      </c>
+      <c r="D274" s="1">
+        <v>11</v>
+      </c>
+      <c r="E274" s="1">
+        <v>1</v>
+      </c>
+      <c r="F274" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A275" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B275" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C275" s="1">
+        <v>5</v>
+      </c>
+      <c r="D275" s="1">
+        <v>14</v>
+      </c>
+      <c r="E275" s="1">
+        <v>1</v>
+      </c>
+      <c r="F275" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A276" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B276" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C276" s="1">
+        <v>6</v>
+      </c>
+      <c r="D276" s="1">
+        <v>17</v>
+      </c>
+      <c r="E276" s="1">
+        <v>1</v>
+      </c>
+      <c r="F276" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A277" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B277" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C277" s="1">
+        <v>7</v>
+      </c>
+      <c r="D277" s="1">
+        <v>19</v>
+      </c>
+      <c r="E277" s="1">
+        <v>1</v>
+      </c>
+      <c r="F277" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A278" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B278" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C278" s="1">
+        <v>8</v>
+      </c>
+      <c r="D278" s="1">
+        <v>21</v>
+      </c>
+      <c r="E278" s="1">
+        <v>1</v>
+      </c>
+      <c r="F278" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A279" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B279" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C279" s="1">
+        <v>9</v>
+      </c>
+      <c r="D279" s="1">
+        <v>27</v>
+      </c>
+      <c r="E279" s="1">
+        <v>1</v>
+      </c>
+      <c r="F279" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A280" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B280" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C280" s="1">
+        <v>10</v>
+      </c>
+      <c r="D280" s="1">
+        <v>29</v>
+      </c>
+      <c r="E280" s="1">
+        <v>1</v>
+      </c>
+      <c r="F280" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A281" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B281" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C281" s="1">
+        <v>11</v>
+      </c>
+      <c r="D281" s="1">
+        <v>35</v>
+      </c>
+      <c r="E281" s="1">
+        <v>1</v>
+      </c>
+      <c r="F281" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A282" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B282" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C282" s="1">
+        <v>12</v>
+      </c>
+      <c r="D282" s="1">
+        <v>39</v>
+      </c>
+      <c r="E282" s="1">
+        <v>1</v>
+      </c>
+      <c r="F282" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A283" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B283" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C283" s="1">
+        <v>13</v>
+      </c>
+      <c r="D283" s="1">
+        <v>39</v>
+      </c>
+      <c r="E283" s="1">
+        <v>1</v>
+      </c>
+      <c r="F283" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A284" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B284" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C284" s="1">
+        <v>14</v>
+      </c>
+      <c r="D284" s="1">
+        <v>39</v>
+      </c>
+      <c r="E284" s="1">
+        <v>1</v>
+      </c>
+      <c r="F284" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A285" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B285" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C285" s="1">
+        <v>15</v>
+      </c>
+      <c r="D285" s="1">
+        <v>39</v>
+      </c>
+      <c r="E285" s="1">
+        <v>1</v>
+      </c>
+      <c r="F285" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A286" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B286" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C286" s="1">
+        <v>16</v>
+      </c>
+      <c r="D286" s="1">
+        <v>46</v>
+      </c>
+      <c r="E286" s="1">
+        <v>1</v>
+      </c>
+      <c r="F286" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A287" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B287" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C287" s="1">
+        <v>17</v>
+      </c>
+      <c r="D287" s="1">
+        <v>48</v>
+      </c>
+      <c r="E287" s="1">
+        <v>1</v>
+      </c>
+      <c r="F287" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A288" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B288" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C288" s="1">
+        <v>18</v>
+      </c>
+      <c r="D288" s="1">
+        <v>48</v>
+      </c>
+      <c r="E288" s="1">
+        <v>1</v>
+      </c>
+      <c r="F288" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A289" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B289" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C289" s="1">
+        <v>19</v>
+      </c>
+      <c r="D289" s="1">
+        <v>48</v>
+      </c>
+      <c r="E289" s="1">
+        <v>1</v>
+      </c>
+      <c r="F289" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A290" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B290" s="1">
+        <v>1104</v>
+      </c>
+      <c r="C290" s="1">
+        <v>20</v>
+      </c>
+      <c r="D290" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E290" s="1">
+        <v>1</v>
+      </c>
+      <c r="F290" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C70FD8-C5A9-4DCB-9369-31AA79A5BE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BC9850-E974-47E5-A2F1-4BA17FB7F12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,246 +101,6 @@
   <si>
     <t>INT_S</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1101001</t>
-  </si>
-  <si>
-    <t>1101002</t>
-  </si>
-  <si>
-    <t>1101003</t>
-  </si>
-  <si>
-    <t>1101004</t>
-  </si>
-  <si>
-    <t>1101005</t>
-  </si>
-  <si>
-    <t>1101006</t>
-  </si>
-  <si>
-    <t>1101007</t>
-  </si>
-  <si>
-    <t>1101008</t>
-  </si>
-  <si>
-    <t>1101009</t>
-  </si>
-  <si>
-    <t>1101010</t>
-  </si>
-  <si>
-    <t>1101011</t>
-  </si>
-  <si>
-    <t>1101012</t>
-  </si>
-  <si>
-    <t>1101013</t>
-  </si>
-  <si>
-    <t>1101014</t>
-  </si>
-  <si>
-    <t>1101015</t>
-  </si>
-  <si>
-    <t>1101016</t>
-  </si>
-  <si>
-    <t>1101017</t>
-  </si>
-  <si>
-    <t>1101018</t>
-  </si>
-  <si>
-    <t>1101019</t>
-  </si>
-  <si>
-    <t>1101020</t>
-  </si>
-  <si>
-    <t>1102001</t>
-  </si>
-  <si>
-    <t>1102002</t>
-  </si>
-  <si>
-    <t>1102003</t>
-  </si>
-  <si>
-    <t>1102004</t>
-  </si>
-  <si>
-    <t>1102005</t>
-  </si>
-  <si>
-    <t>1102006</t>
-  </si>
-  <si>
-    <t>1102007</t>
-  </si>
-  <si>
-    <t>1102008</t>
-  </si>
-  <si>
-    <t>1102009</t>
-  </si>
-  <si>
-    <t>1102010</t>
-  </si>
-  <si>
-    <t>1102011</t>
-  </si>
-  <si>
-    <t>1102012</t>
-  </si>
-  <si>
-    <t>1102013</t>
-  </si>
-  <si>
-    <t>1102014</t>
-  </si>
-  <si>
-    <t>1102015</t>
-  </si>
-  <si>
-    <t>1102016</t>
-  </si>
-  <si>
-    <t>1102017</t>
-  </si>
-  <si>
-    <t>1102018</t>
-  </si>
-  <si>
-    <t>1102019</t>
-  </si>
-  <si>
-    <t>1102020</t>
-  </si>
-  <si>
-    <t>1103001</t>
-  </si>
-  <si>
-    <t>1103002</t>
-  </si>
-  <si>
-    <t>1103003</t>
-  </si>
-  <si>
-    <t>1103004</t>
-  </si>
-  <si>
-    <t>1103005</t>
-  </si>
-  <si>
-    <t>1103006</t>
-  </si>
-  <si>
-    <t>1103007</t>
-  </si>
-  <si>
-    <t>1103008</t>
-  </si>
-  <si>
-    <t>1103009</t>
-  </si>
-  <si>
-    <t>1103010</t>
-  </si>
-  <si>
-    <t>1103011</t>
-  </si>
-  <si>
-    <t>1103012</t>
-  </si>
-  <si>
-    <t>1103013</t>
-  </si>
-  <si>
-    <t>1103014</t>
-  </si>
-  <si>
-    <t>1103015</t>
-  </si>
-  <si>
-    <t>1103016</t>
-  </si>
-  <si>
-    <t>1103017</t>
-  </si>
-  <si>
-    <t>1103018</t>
-  </si>
-  <si>
-    <t>1103019</t>
-  </si>
-  <si>
-    <t>1103020</t>
-  </si>
-  <si>
-    <t>1104001</t>
-  </si>
-  <si>
-    <t>1104002</t>
-  </si>
-  <si>
-    <t>1104003</t>
-  </si>
-  <si>
-    <t>1104004</t>
-  </si>
-  <si>
-    <t>1104005</t>
-  </si>
-  <si>
-    <t>1104006</t>
-  </si>
-  <si>
-    <t>1104007</t>
-  </si>
-  <si>
-    <t>1104008</t>
-  </si>
-  <si>
-    <t>1104009</t>
-  </si>
-  <si>
-    <t>1104010</t>
-  </si>
-  <si>
-    <t>1104011</t>
-  </si>
-  <si>
-    <t>1104012</t>
-  </si>
-  <si>
-    <t>1104013</t>
-  </si>
-  <si>
-    <t>1104014</t>
-  </si>
-  <si>
-    <t>1104015</t>
-  </si>
-  <si>
-    <t>1104016</t>
-  </si>
-  <si>
-    <t>1104017</t>
-  </si>
-  <si>
-    <t>1104018</t>
-  </si>
-  <si>
-    <t>1104019</t>
-  </si>
-  <si>
-    <t>1104020</t>
   </si>
 </sst>
 </file>
@@ -4871,8 +4631,8 @@
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A211" s="1" t="s">
-        <v>16</v>
+      <c r="A211" s="1">
+        <v>11010001</v>
       </c>
       <c r="B211" s="1">
         <v>1101</v>
@@ -4891,8 +4651,8 @@
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A212" s="1" t="s">
-        <v>17</v>
+      <c r="A212" s="1">
+        <v>11010002</v>
       </c>
       <c r="B212" s="1">
         <v>1101</v>
@@ -4911,8 +4671,8 @@
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A213" s="1" t="s">
-        <v>18</v>
+      <c r="A213" s="1">
+        <v>11010003</v>
       </c>
       <c r="B213" s="1">
         <v>1101</v>
@@ -4931,8 +4691,8 @@
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A214" s="1" t="s">
-        <v>19</v>
+      <c r="A214" s="1">
+        <v>11010004</v>
       </c>
       <c r="B214" s="1">
         <v>1101</v>
@@ -4951,8 +4711,8 @@
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A215" s="1" t="s">
-        <v>20</v>
+      <c r="A215" s="1">
+        <v>11010005</v>
       </c>
       <c r="B215" s="1">
         <v>1101</v>
@@ -4971,8 +4731,8 @@
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A216" s="1" t="s">
-        <v>21</v>
+      <c r="A216" s="1">
+        <v>11010006</v>
       </c>
       <c r="B216" s="1">
         <v>1101</v>
@@ -4991,8 +4751,8 @@
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A217" s="1" t="s">
-        <v>22</v>
+      <c r="A217" s="1">
+        <v>11010007</v>
       </c>
       <c r="B217" s="1">
         <v>1101</v>
@@ -5011,8 +4771,8 @@
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A218" s="1" t="s">
-        <v>23</v>
+      <c r="A218" s="1">
+        <v>11010008</v>
       </c>
       <c r="B218" s="1">
         <v>1101</v>
@@ -5031,8 +4791,8 @@
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A219" s="1" t="s">
-        <v>24</v>
+      <c r="A219" s="1">
+        <v>11010009</v>
       </c>
       <c r="B219" s="1">
         <v>1101</v>
@@ -5051,8 +4811,8 @@
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A220" s="1" t="s">
-        <v>25</v>
+      <c r="A220" s="1">
+        <v>11010010</v>
       </c>
       <c r="B220" s="1">
         <v>1101</v>
@@ -5071,8 +4831,8 @@
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A221" s="1" t="s">
-        <v>26</v>
+      <c r="A221" s="1">
+        <v>11010011</v>
       </c>
       <c r="B221" s="1">
         <v>1101</v>
@@ -5091,8 +4851,8 @@
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A222" s="1" t="s">
-        <v>27</v>
+      <c r="A222" s="1">
+        <v>11010012</v>
       </c>
       <c r="B222" s="1">
         <v>1101</v>
@@ -5111,8 +4871,8 @@
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A223" s="1" t="s">
-        <v>28</v>
+      <c r="A223" s="1">
+        <v>11010013</v>
       </c>
       <c r="B223" s="1">
         <v>1101</v>
@@ -5131,8 +4891,8 @@
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A224" s="1" t="s">
-        <v>29</v>
+      <c r="A224" s="1">
+        <v>11010014</v>
       </c>
       <c r="B224" s="1">
         <v>1101</v>
@@ -5151,8 +4911,8 @@
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A225" s="1" t="s">
-        <v>30</v>
+      <c r="A225" s="1">
+        <v>11010015</v>
       </c>
       <c r="B225" s="1">
         <v>1101</v>
@@ -5171,8 +4931,8 @@
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A226" s="1" t="s">
-        <v>31</v>
+      <c r="A226" s="1">
+        <v>11010016</v>
       </c>
       <c r="B226" s="1">
         <v>1101</v>
@@ -5191,8 +4951,8 @@
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A227" s="1" t="s">
-        <v>32</v>
+      <c r="A227" s="1">
+        <v>11010017</v>
       </c>
       <c r="B227" s="1">
         <v>1101</v>
@@ -5211,8 +4971,8 @@
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A228" s="1" t="s">
-        <v>33</v>
+      <c r="A228" s="1">
+        <v>11010018</v>
       </c>
       <c r="B228" s="1">
         <v>1101</v>
@@ -5231,8 +4991,8 @@
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A229" s="1" t="s">
-        <v>34</v>
+      <c r="A229" s="1">
+        <v>11010019</v>
       </c>
       <c r="B229" s="1">
         <v>1101</v>
@@ -5251,8 +5011,8 @@
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A230" s="1" t="s">
-        <v>35</v>
+      <c r="A230" s="1">
+        <v>11010020</v>
       </c>
       <c r="B230" s="1">
         <v>1101</v>
@@ -5271,8 +5031,8 @@
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A231" s="1" t="s">
-        <v>36</v>
+      <c r="A231" s="1">
+        <v>11020001</v>
       </c>
       <c r="B231" s="1">
         <v>1102</v>
@@ -5291,8 +5051,8 @@
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A232" s="1" t="s">
-        <v>37</v>
+      <c r="A232" s="1">
+        <v>11020002</v>
       </c>
       <c r="B232" s="1">
         <v>1102</v>
@@ -5311,8 +5071,8 @@
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A233" s="1" t="s">
-        <v>38</v>
+      <c r="A233" s="1">
+        <v>11020003</v>
       </c>
       <c r="B233" s="1">
         <v>1102</v>
@@ -5331,8 +5091,8 @@
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A234" s="1" t="s">
-        <v>39</v>
+      <c r="A234" s="1">
+        <v>11020004</v>
       </c>
       <c r="B234" s="1">
         <v>1102</v>
@@ -5351,8 +5111,8 @@
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A235" s="1" t="s">
-        <v>40</v>
+      <c r="A235" s="1">
+        <v>11020005</v>
       </c>
       <c r="B235" s="1">
         <v>1102</v>
@@ -5371,8 +5131,8 @@
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A236" s="1" t="s">
-        <v>41</v>
+      <c r="A236" s="1">
+        <v>11020006</v>
       </c>
       <c r="B236" s="1">
         <v>1102</v>
@@ -5391,8 +5151,8 @@
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A237" s="1" t="s">
-        <v>42</v>
+      <c r="A237" s="1">
+        <v>11020007</v>
       </c>
       <c r="B237" s="1">
         <v>1102</v>
@@ -5411,8 +5171,8 @@
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A238" s="1" t="s">
-        <v>43</v>
+      <c r="A238" s="1">
+        <v>11020008</v>
       </c>
       <c r="B238" s="1">
         <v>1102</v>
@@ -5431,8 +5191,8 @@
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A239" s="1" t="s">
-        <v>44</v>
+      <c r="A239" s="1">
+        <v>11020009</v>
       </c>
       <c r="B239" s="1">
         <v>1102</v>
@@ -5451,8 +5211,8 @@
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A240" s="1" t="s">
-        <v>45</v>
+      <c r="A240" s="1">
+        <v>11020010</v>
       </c>
       <c r="B240" s="1">
         <v>1102</v>
@@ -5461,7 +5221,7 @@
         <v>10</v>
       </c>
       <c r="D240" s="1">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="E240" s="1">
         <v>1</v>
@@ -5471,8 +5231,8 @@
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A241" s="1" t="s">
-        <v>46</v>
+      <c r="A241" s="1">
+        <v>11020011</v>
       </c>
       <c r="B241" s="1">
         <v>1102</v>
@@ -5481,7 +5241,7 @@
         <v>11</v>
       </c>
       <c r="D241" s="1">
-        <v>-1</v>
+        <v>25</v>
       </c>
       <c r="E241" s="1">
         <v>1</v>
@@ -5491,8 +5251,8 @@
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A242" s="1" t="s">
-        <v>47</v>
+      <c r="A242" s="1">
+        <v>11020012</v>
       </c>
       <c r="B242" s="1">
         <v>1102</v>
@@ -5501,7 +5261,7 @@
         <v>12</v>
       </c>
       <c r="D242" s="1">
-        <v>-1</v>
+        <v>27</v>
       </c>
       <c r="E242" s="1">
         <v>1</v>
@@ -5511,8 +5271,8 @@
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A243" s="1" t="s">
-        <v>48</v>
+      <c r="A243" s="1">
+        <v>11020013</v>
       </c>
       <c r="B243" s="1">
         <v>1102</v>
@@ -5521,7 +5281,7 @@
         <v>13</v>
       </c>
       <c r="D243" s="1">
-        <v>-1</v>
+        <v>28</v>
       </c>
       <c r="E243" s="1">
         <v>1</v>
@@ -5531,8 +5291,8 @@
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A244" s="1" t="s">
-        <v>49</v>
+      <c r="A244" s="1">
+        <v>11020014</v>
       </c>
       <c r="B244" s="1">
         <v>1102</v>
@@ -5541,7 +5301,7 @@
         <v>14</v>
       </c>
       <c r="D244" s="1">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="E244" s="1">
         <v>1</v>
@@ -5551,8 +5311,8 @@
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A245" s="1" t="s">
-        <v>50</v>
+      <c r="A245" s="1">
+        <v>11020015</v>
       </c>
       <c r="B245" s="1">
         <v>1102</v>
@@ -5571,8 +5331,8 @@
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A246" s="1" t="s">
-        <v>51</v>
+      <c r="A246" s="1">
+        <v>11020016</v>
       </c>
       <c r="B246" s="1">
         <v>1102</v>
@@ -5591,8 +5351,8 @@
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A247" s="1" t="s">
-        <v>52</v>
+      <c r="A247" s="1">
+        <v>11020017</v>
       </c>
       <c r="B247" s="1">
         <v>1102</v>
@@ -5611,8 +5371,8 @@
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A248" s="1" t="s">
-        <v>53</v>
+      <c r="A248" s="1">
+        <v>11020018</v>
       </c>
       <c r="B248" s="1">
         <v>1102</v>
@@ -5631,8 +5391,8 @@
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A249" s="1" t="s">
-        <v>54</v>
+      <c r="A249" s="1">
+        <v>11020019</v>
       </c>
       <c r="B249" s="1">
         <v>1102</v>
@@ -5651,8 +5411,8 @@
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A250" s="1" t="s">
-        <v>55</v>
+      <c r="A250" s="1">
+        <v>11020020</v>
       </c>
       <c r="B250" s="1">
         <v>1102</v>
@@ -5671,8 +5431,8 @@
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A251" s="1" t="s">
-        <v>56</v>
+      <c r="A251" s="1">
+        <v>11030001</v>
       </c>
       <c r="B251" s="1">
         <v>1103</v>
@@ -5691,8 +5451,8 @@
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A252" s="1" t="s">
-        <v>57</v>
+      <c r="A252" s="1">
+        <v>11030002</v>
       </c>
       <c r="B252" s="1">
         <v>1103</v>
@@ -5711,8 +5471,8 @@
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A253" s="1" t="s">
-        <v>58</v>
+      <c r="A253" s="1">
+        <v>11030003</v>
       </c>
       <c r="B253" s="1">
         <v>1103</v>
@@ -5731,8 +5491,8 @@
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A254" s="1" t="s">
-        <v>59</v>
+      <c r="A254" s="1">
+        <v>11030004</v>
       </c>
       <c r="B254" s="1">
         <v>1103</v>
@@ -5751,8 +5511,8 @@
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A255" s="1" t="s">
-        <v>60</v>
+      <c r="A255" s="1">
+        <v>11030005</v>
       </c>
       <c r="B255" s="1">
         <v>1103</v>
@@ -5771,8 +5531,8 @@
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A256" s="1" t="s">
-        <v>61</v>
+      <c r="A256" s="1">
+        <v>11030006</v>
       </c>
       <c r="B256" s="1">
         <v>1103</v>
@@ -5791,8 +5551,8 @@
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A257" s="1" t="s">
-        <v>62</v>
+      <c r="A257" s="1">
+        <v>11030007</v>
       </c>
       <c r="B257" s="1">
         <v>1103</v>
@@ -5811,8 +5571,8 @@
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A258" s="1" t="s">
-        <v>63</v>
+      <c r="A258" s="1">
+        <v>11030008</v>
       </c>
       <c r="B258" s="1">
         <v>1103</v>
@@ -5831,8 +5591,8 @@
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A259" s="1" t="s">
-        <v>64</v>
+      <c r="A259" s="1">
+        <v>11030009</v>
       </c>
       <c r="B259" s="1">
         <v>1103</v>
@@ -5851,8 +5611,8 @@
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A260" s="1" t="s">
-        <v>65</v>
+      <c r="A260" s="1">
+        <v>11030010</v>
       </c>
       <c r="B260" s="1">
         <v>1103</v>
@@ -5871,8 +5631,8 @@
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A261" s="1" t="s">
-        <v>66</v>
+      <c r="A261" s="1">
+        <v>11030011</v>
       </c>
       <c r="B261" s="1">
         <v>1103</v>
@@ -5891,8 +5651,8 @@
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A262" s="1" t="s">
-        <v>67</v>
+      <c r="A262" s="1">
+        <v>11030012</v>
       </c>
       <c r="B262" s="1">
         <v>1103</v>
@@ -5911,8 +5671,8 @@
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A263" s="1" t="s">
-        <v>68</v>
+      <c r="A263" s="1">
+        <v>11030013</v>
       </c>
       <c r="B263" s="1">
         <v>1103</v>
@@ -5931,8 +5691,8 @@
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A264" s="1" t="s">
-        <v>69</v>
+      <c r="A264" s="1">
+        <v>11030014</v>
       </c>
       <c r="B264" s="1">
         <v>1103</v>
@@ -5951,8 +5711,8 @@
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A265" s="1" t="s">
-        <v>70</v>
+      <c r="A265" s="1">
+        <v>11030015</v>
       </c>
       <c r="B265" s="1">
         <v>1103</v>
@@ -5971,8 +5731,8 @@
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A266" s="1" t="s">
-        <v>71</v>
+      <c r="A266" s="1">
+        <v>11030016</v>
       </c>
       <c r="B266" s="1">
         <v>1103</v>
@@ -5991,8 +5751,8 @@
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A267" s="1" t="s">
-        <v>72</v>
+      <c r="A267" s="1">
+        <v>11030017</v>
       </c>
       <c r="B267" s="1">
         <v>1103</v>
@@ -6011,8 +5771,8 @@
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A268" s="1" t="s">
-        <v>73</v>
+      <c r="A268" s="1">
+        <v>11030018</v>
       </c>
       <c r="B268" s="1">
         <v>1103</v>
@@ -6031,8 +5791,8 @@
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A269" s="1" t="s">
-        <v>74</v>
+      <c r="A269" s="1">
+        <v>11030019</v>
       </c>
       <c r="B269" s="1">
         <v>1103</v>
@@ -6051,8 +5811,8 @@
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A270" s="1" t="s">
-        <v>75</v>
+      <c r="A270" s="1">
+        <v>11030020</v>
       </c>
       <c r="B270" s="1">
         <v>1103</v>
@@ -6071,8 +5831,8 @@
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A271" s="1" t="s">
-        <v>76</v>
+      <c r="A271" s="1">
+        <v>11040001</v>
       </c>
       <c r="B271" s="1">
         <v>1104</v>
@@ -6091,8 +5851,8 @@
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A272" s="1" t="s">
-        <v>77</v>
+      <c r="A272" s="1">
+        <v>11040002</v>
       </c>
       <c r="B272" s="1">
         <v>1104</v>
@@ -6111,8 +5871,8 @@
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A273" s="1" t="s">
-        <v>78</v>
+      <c r="A273" s="1">
+        <v>11040003</v>
       </c>
       <c r="B273" s="1">
         <v>1104</v>
@@ -6131,8 +5891,8 @@
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A274" s="1" t="s">
-        <v>79</v>
+      <c r="A274" s="1">
+        <v>11040004</v>
       </c>
       <c r="B274" s="1">
         <v>1104</v>
@@ -6151,8 +5911,8 @@
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A275" s="1" t="s">
-        <v>80</v>
+      <c r="A275" s="1">
+        <v>11040005</v>
       </c>
       <c r="B275" s="1">
         <v>1104</v>
@@ -6171,8 +5931,8 @@
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A276" s="1" t="s">
-        <v>81</v>
+      <c r="A276" s="1">
+        <v>11040006</v>
       </c>
       <c r="B276" s="1">
         <v>1104</v>
@@ -6191,8 +5951,8 @@
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A277" s="1" t="s">
-        <v>82</v>
+      <c r="A277" s="1">
+        <v>11040007</v>
       </c>
       <c r="B277" s="1">
         <v>1104</v>
@@ -6211,8 +5971,8 @@
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A278" s="1" t="s">
-        <v>83</v>
+      <c r="A278" s="1">
+        <v>11040008</v>
       </c>
       <c r="B278" s="1">
         <v>1104</v>
@@ -6231,8 +5991,8 @@
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A279" s="1" t="s">
-        <v>84</v>
+      <c r="A279" s="1">
+        <v>11040009</v>
       </c>
       <c r="B279" s="1">
         <v>1104</v>
@@ -6251,8 +6011,8 @@
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A280" s="1" t="s">
-        <v>85</v>
+      <c r="A280" s="1">
+        <v>11040010</v>
       </c>
       <c r="B280" s="1">
         <v>1104</v>
@@ -6271,8 +6031,8 @@
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A281" s="1" t="s">
-        <v>86</v>
+      <c r="A281" s="1">
+        <v>11040011</v>
       </c>
       <c r="B281" s="1">
         <v>1104</v>
@@ -6291,8 +6051,8 @@
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A282" s="1" t="s">
-        <v>87</v>
+      <c r="A282" s="1">
+        <v>11040012</v>
       </c>
       <c r="B282" s="1">
         <v>1104</v>
@@ -6311,8 +6071,8 @@
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A283" s="1" t="s">
-        <v>88</v>
+      <c r="A283" s="1">
+        <v>11040013</v>
       </c>
       <c r="B283" s="1">
         <v>1104</v>
@@ -6331,8 +6091,8 @@
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A284" s="1" t="s">
-        <v>89</v>
+      <c r="A284" s="1">
+        <v>11040014</v>
       </c>
       <c r="B284" s="1">
         <v>1104</v>
@@ -6351,8 +6111,8 @@
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A285" s="1" t="s">
-        <v>90</v>
+      <c r="A285" s="1">
+        <v>11040015</v>
       </c>
       <c r="B285" s="1">
         <v>1104</v>
@@ -6371,8 +6131,8 @@
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A286" s="1" t="s">
-        <v>91</v>
+      <c r="A286" s="1">
+        <v>11040016</v>
       </c>
       <c r="B286" s="1">
         <v>1104</v>
@@ -6391,8 +6151,8 @@
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A287" s="1" t="s">
-        <v>92</v>
+      <c r="A287" s="1">
+        <v>11040017</v>
       </c>
       <c r="B287" s="1">
         <v>1104</v>
@@ -6411,8 +6171,8 @@
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A288" s="1" t="s">
-        <v>93</v>
+      <c r="A288" s="1">
+        <v>11040018</v>
       </c>
       <c r="B288" s="1">
         <v>1104</v>
@@ -6431,8 +6191,8 @@
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A289" s="1" t="s">
-        <v>94</v>
+      <c r="A289" s="1">
+        <v>11040019</v>
       </c>
       <c r="B289" s="1">
         <v>1104</v>
@@ -6451,8 +6211,8 @@
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A290" s="1" t="s">
-        <v>95</v>
+      <c r="A290" s="1">
+        <v>11040020</v>
       </c>
       <c r="B290" s="1">
         <v>1104</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BC9850-E974-47E5-A2F1-4BA17FB7F12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169BB841-71A3-4178-B717-BB9F6BCE2A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="D211" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E211" s="1">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>-1</v>
+        <v>46</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{169BB841-71A3-4178-B717-BB9F6BCE2A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE400AF-C0C3-4131-BA35-BD8072F25932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F290"/>
+  <dimension ref="A1:F250"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
@@ -4841,7 +4841,7 @@
         <v>11</v>
       </c>
       <c r="D221" s="1">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E221" s="1">
         <v>1</v>
@@ -4861,7 +4861,7 @@
         <v>12</v>
       </c>
       <c r="D222" s="1">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="E222" s="1">
         <v>1</v>
@@ -4881,7 +4881,7 @@
         <v>13</v>
       </c>
       <c r="D223" s="1">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="E223" s="1">
         <v>1</v>
@@ -4901,7 +4901,7 @@
         <v>14</v>
       </c>
       <c r="D224" s="1">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="E224" s="1">
         <v>1</v>
@@ -4921,7 +4921,7 @@
         <v>15</v>
       </c>
       <c r="D225" s="1">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="E225" s="1">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>16</v>
       </c>
       <c r="D226" s="1">
-        <v>-1</v>
+        <v>37</v>
       </c>
       <c r="E226" s="1">
         <v>1</v>
@@ -4961,7 +4961,7 @@
         <v>17</v>
       </c>
       <c r="D227" s="1">
-        <v>-1</v>
+        <v>44</v>
       </c>
       <c r="E227" s="1">
         <v>1</v>
@@ -4981,7 +4981,7 @@
         <v>18</v>
       </c>
       <c r="D228" s="1">
-        <v>-1</v>
+        <v>57</v>
       </c>
       <c r="E228" s="1">
         <v>1</v>
@@ -5001,7 +5001,7 @@
         <v>19</v>
       </c>
       <c r="D229" s="1">
-        <v>-1</v>
+        <v>67</v>
       </c>
       <c r="E229" s="1">
         <v>1</v>
@@ -5021,7 +5021,7 @@
         <v>20</v>
       </c>
       <c r="D230" s="1">
-        <v>-1</v>
+        <v>79</v>
       </c>
       <c r="E230" s="1">
         <v>1</v>
@@ -5032,36 +5032,36 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>11020001</v>
+        <v>11010021</v>
       </c>
       <c r="B231" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C231" s="1">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D231" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E231" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F231" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>11020002</v>
+        <v>11010022</v>
       </c>
       <c r="B232" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C232" s="1">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D232" s="1">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E232" s="1">
         <v>1</v>
@@ -5072,16 +5072,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>11020003</v>
+        <v>11010023</v>
       </c>
       <c r="B233" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C233" s="1">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D233" s="1">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E233" s="1">
         <v>1</v>
@@ -5092,16 +5092,16 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>11020004</v>
+        <v>11010024</v>
       </c>
       <c r="B234" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C234" s="1">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D234" s="1">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="E234" s="1">
         <v>1</v>
@@ -5112,16 +5112,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A235" s="1">
-        <v>11020005</v>
+        <v>11010025</v>
       </c>
       <c r="B235" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C235" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D235" s="1">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="E235" s="1">
         <v>1</v>
@@ -5132,16 +5132,16 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A236" s="1">
-        <v>11020006</v>
+        <v>11010026</v>
       </c>
       <c r="B236" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C236" s="1">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D236" s="1">
-        <v>11</v>
+        <v>74</v>
       </c>
       <c r="E236" s="1">
         <v>1</v>
@@ -5152,16 +5152,16 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A237" s="1">
-        <v>11020007</v>
+        <v>11010027</v>
       </c>
       <c r="B237" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C237" s="1">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D237" s="1">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="E237" s="1">
         <v>1</v>
@@ -5172,16 +5172,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A238" s="1">
-        <v>11020008</v>
+        <v>11010028</v>
       </c>
       <c r="B238" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C238" s="1">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D238" s="1">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="E238" s="1">
         <v>1</v>
@@ -5192,16 +5192,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A239" s="1">
-        <v>11020009</v>
+        <v>11010029</v>
       </c>
       <c r="B239" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C239" s="1">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="D239" s="1">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="E239" s="1">
         <v>1</v>
@@ -5212,16 +5212,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A240" s="1">
-        <v>11020010</v>
+        <v>11010030</v>
       </c>
       <c r="B240" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C240" s="1">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D240" s="1">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="E240" s="1">
         <v>1</v>
@@ -5232,16 +5232,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A241" s="1">
-        <v>11020011</v>
+        <v>11010031</v>
       </c>
       <c r="B241" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C241" s="1">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D241" s="1">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E241" s="1">
         <v>1</v>
@@ -5252,16 +5252,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A242" s="1">
-        <v>11020012</v>
+        <v>11010032</v>
       </c>
       <c r="B242" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C242" s="1">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D242" s="1">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E242" s="1">
         <v>1</v>
@@ -5272,16 +5272,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A243" s="1">
-        <v>11020013</v>
+        <v>11010033</v>
       </c>
       <c r="B243" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C243" s="1">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D243" s="1">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E243" s="1">
         <v>1</v>
@@ -5292,16 +5292,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A244" s="1">
-        <v>11020014</v>
+        <v>11010034</v>
       </c>
       <c r="B244" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C244" s="1">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D244" s="1">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E244" s="1">
         <v>1</v>
@@ -5312,16 +5312,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A245" s="1">
-        <v>11020015</v>
+        <v>11010035</v>
       </c>
       <c r="B245" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C245" s="1">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D245" s="1">
-        <v>-1</v>
+        <v>56</v>
       </c>
       <c r="E245" s="1">
         <v>1</v>
@@ -5332,16 +5332,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A246" s="1">
-        <v>11020016</v>
+        <v>11010036</v>
       </c>
       <c r="B246" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C246" s="1">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D246" s="1">
-        <v>-1</v>
+        <v>74</v>
       </c>
       <c r="E246" s="1">
         <v>1</v>
@@ -5352,16 +5352,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A247" s="1">
-        <v>11020017</v>
+        <v>11010037</v>
       </c>
       <c r="B247" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C247" s="1">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D247" s="1">
-        <v>-1</v>
+        <v>78</v>
       </c>
       <c r="E247" s="1">
         <v>1</v>
@@ -5372,16 +5372,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A248" s="1">
-        <v>11020018</v>
+        <v>11010038</v>
       </c>
       <c r="B248" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C248" s="1">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="D248" s="1">
-        <v>-1</v>
+        <v>85</v>
       </c>
       <c r="E248" s="1">
         <v>1</v>
@@ -5392,16 +5392,16 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A249" s="1">
-        <v>11020019</v>
+        <v>11010039</v>
       </c>
       <c r="B249" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C249" s="1">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D249" s="1">
-        <v>-1</v>
+        <v>96</v>
       </c>
       <c r="E249" s="1">
         <v>1</v>
@@ -5412,13 +5412,13 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A250" s="1">
-        <v>11020020</v>
+        <v>11010040</v>
       </c>
       <c r="B250" s="1">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="C250" s="1">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D250" s="1">
         <v>-1</v>
@@ -5427,806 +5427,6 @@
         <v>1</v>
       </c>
       <c r="F250" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A251" s="1">
-        <v>11030001</v>
-      </c>
-      <c r="B251" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C251" s="1">
-        <v>1</v>
-      </c>
-      <c r="D251" s="1">
-        <v>4</v>
-      </c>
-      <c r="E251" s="1">
-        <v>0</v>
-      </c>
-      <c r="F251" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A252" s="1">
-        <v>11030002</v>
-      </c>
-      <c r="B252" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C252" s="1">
-        <v>2</v>
-      </c>
-      <c r="D252" s="1">
-        <v>6</v>
-      </c>
-      <c r="E252" s="1">
-        <v>1</v>
-      </c>
-      <c r="F252" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A253" s="1">
-        <v>11030003</v>
-      </c>
-      <c r="B253" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C253" s="1">
-        <v>3</v>
-      </c>
-      <c r="D253" s="1">
-        <v>8</v>
-      </c>
-      <c r="E253" s="1">
-        <v>1</v>
-      </c>
-      <c r="F253" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A254" s="1">
-        <v>11030004</v>
-      </c>
-      <c r="B254" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C254" s="1">
-        <v>4</v>
-      </c>
-      <c r="D254" s="1">
-        <v>11</v>
-      </c>
-      <c r="E254" s="1">
-        <v>1</v>
-      </c>
-      <c r="F254" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A255" s="1">
-        <v>11030005</v>
-      </c>
-      <c r="B255" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C255" s="1">
-        <v>5</v>
-      </c>
-      <c r="D255" s="1">
-        <v>14</v>
-      </c>
-      <c r="E255" s="1">
-        <v>1</v>
-      </c>
-      <c r="F255" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A256" s="1">
-        <v>11030006</v>
-      </c>
-      <c r="B256" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C256" s="1">
-        <v>6</v>
-      </c>
-      <c r="D256" s="1">
-        <v>17</v>
-      </c>
-      <c r="E256" s="1">
-        <v>1</v>
-      </c>
-      <c r="F256" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A257" s="1">
-        <v>11030007</v>
-      </c>
-      <c r="B257" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C257" s="1">
-        <v>7</v>
-      </c>
-      <c r="D257" s="1">
-        <v>19</v>
-      </c>
-      <c r="E257" s="1">
-        <v>1</v>
-      </c>
-      <c r="F257" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A258" s="1">
-        <v>11030008</v>
-      </c>
-      <c r="B258" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C258" s="1">
-        <v>8</v>
-      </c>
-      <c r="D258" s="1">
-        <v>21</v>
-      </c>
-      <c r="E258" s="1">
-        <v>1</v>
-      </c>
-      <c r="F258" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A259" s="1">
-        <v>11030009</v>
-      </c>
-      <c r="B259" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C259" s="1">
-        <v>9</v>
-      </c>
-      <c r="D259" s="1">
-        <v>27</v>
-      </c>
-      <c r="E259" s="1">
-        <v>1</v>
-      </c>
-      <c r="F259" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A260" s="1">
-        <v>11030010</v>
-      </c>
-      <c r="B260" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C260" s="1">
-        <v>10</v>
-      </c>
-      <c r="D260" s="1">
-        <v>29</v>
-      </c>
-      <c r="E260" s="1">
-        <v>1</v>
-      </c>
-      <c r="F260" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A261" s="1">
-        <v>11030011</v>
-      </c>
-      <c r="B261" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C261" s="1">
-        <v>11</v>
-      </c>
-      <c r="D261" s="1">
-        <v>35</v>
-      </c>
-      <c r="E261" s="1">
-        <v>1</v>
-      </c>
-      <c r="F261" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A262" s="1">
-        <v>11030012</v>
-      </c>
-      <c r="B262" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C262" s="1">
-        <v>12</v>
-      </c>
-      <c r="D262" s="1">
-        <v>39</v>
-      </c>
-      <c r="E262" s="1">
-        <v>1</v>
-      </c>
-      <c r="F262" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A263" s="1">
-        <v>11030013</v>
-      </c>
-      <c r="B263" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C263" s="1">
-        <v>13</v>
-      </c>
-      <c r="D263" s="1">
-        <v>39</v>
-      </c>
-      <c r="E263" s="1">
-        <v>1</v>
-      </c>
-      <c r="F263" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A264" s="1">
-        <v>11030014</v>
-      </c>
-      <c r="B264" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C264" s="1">
-        <v>14</v>
-      </c>
-      <c r="D264" s="1">
-        <v>39</v>
-      </c>
-      <c r="E264" s="1">
-        <v>1</v>
-      </c>
-      <c r="F264" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A265" s="1">
-        <v>11030015</v>
-      </c>
-      <c r="B265" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C265" s="1">
-        <v>15</v>
-      </c>
-      <c r="D265" s="1">
-        <v>39</v>
-      </c>
-      <c r="E265" s="1">
-        <v>1</v>
-      </c>
-      <c r="F265" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A266" s="1">
-        <v>11030016</v>
-      </c>
-      <c r="B266" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C266" s="1">
-        <v>16</v>
-      </c>
-      <c r="D266" s="1">
-        <v>46</v>
-      </c>
-      <c r="E266" s="1">
-        <v>1</v>
-      </c>
-      <c r="F266" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A267" s="1">
-        <v>11030017</v>
-      </c>
-      <c r="B267" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C267" s="1">
-        <v>17</v>
-      </c>
-      <c r="D267" s="1">
-        <v>48</v>
-      </c>
-      <c r="E267" s="1">
-        <v>1</v>
-      </c>
-      <c r="F267" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A268" s="1">
-        <v>11030018</v>
-      </c>
-      <c r="B268" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C268" s="1">
-        <v>18</v>
-      </c>
-      <c r="D268" s="1">
-        <v>48</v>
-      </c>
-      <c r="E268" s="1">
-        <v>1</v>
-      </c>
-      <c r="F268" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A269" s="1">
-        <v>11030019</v>
-      </c>
-      <c r="B269" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C269" s="1">
-        <v>19</v>
-      </c>
-      <c r="D269" s="1">
-        <v>48</v>
-      </c>
-      <c r="E269" s="1">
-        <v>1</v>
-      </c>
-      <c r="F269" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A270" s="1">
-        <v>11030020</v>
-      </c>
-      <c r="B270" s="1">
-        <v>1103</v>
-      </c>
-      <c r="C270" s="1">
-        <v>20</v>
-      </c>
-      <c r="D270" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E270" s="1">
-        <v>1</v>
-      </c>
-      <c r="F270" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A271" s="1">
-        <v>11040001</v>
-      </c>
-      <c r="B271" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C271" s="1">
-        <v>1</v>
-      </c>
-      <c r="D271" s="1">
-        <v>4</v>
-      </c>
-      <c r="E271" s="1">
-        <v>0</v>
-      </c>
-      <c r="F271" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A272" s="1">
-        <v>11040002</v>
-      </c>
-      <c r="B272" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C272" s="1">
-        <v>2</v>
-      </c>
-      <c r="D272" s="1">
-        <v>6</v>
-      </c>
-      <c r="E272" s="1">
-        <v>1</v>
-      </c>
-      <c r="F272" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A273" s="1">
-        <v>11040003</v>
-      </c>
-      <c r="B273" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C273" s="1">
-        <v>3</v>
-      </c>
-      <c r="D273" s="1">
-        <v>8</v>
-      </c>
-      <c r="E273" s="1">
-        <v>1</v>
-      </c>
-      <c r="F273" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A274" s="1">
-        <v>11040004</v>
-      </c>
-      <c r="B274" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C274" s="1">
-        <v>4</v>
-      </c>
-      <c r="D274" s="1">
-        <v>11</v>
-      </c>
-      <c r="E274" s="1">
-        <v>1</v>
-      </c>
-      <c r="F274" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A275" s="1">
-        <v>11040005</v>
-      </c>
-      <c r="B275" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C275" s="1">
-        <v>5</v>
-      </c>
-      <c r="D275" s="1">
-        <v>14</v>
-      </c>
-      <c r="E275" s="1">
-        <v>1</v>
-      </c>
-      <c r="F275" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A276" s="1">
-        <v>11040006</v>
-      </c>
-      <c r="B276" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C276" s="1">
-        <v>6</v>
-      </c>
-      <c r="D276" s="1">
-        <v>17</v>
-      </c>
-      <c r="E276" s="1">
-        <v>1</v>
-      </c>
-      <c r="F276" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A277" s="1">
-        <v>11040007</v>
-      </c>
-      <c r="B277" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C277" s="1">
-        <v>7</v>
-      </c>
-      <c r="D277" s="1">
-        <v>19</v>
-      </c>
-      <c r="E277" s="1">
-        <v>1</v>
-      </c>
-      <c r="F277" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A278" s="1">
-        <v>11040008</v>
-      </c>
-      <c r="B278" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C278" s="1">
-        <v>8</v>
-      </c>
-      <c r="D278" s="1">
-        <v>21</v>
-      </c>
-      <c r="E278" s="1">
-        <v>1</v>
-      </c>
-      <c r="F278" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A279" s="1">
-        <v>11040009</v>
-      </c>
-      <c r="B279" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C279" s="1">
-        <v>9</v>
-      </c>
-      <c r="D279" s="1">
-        <v>27</v>
-      </c>
-      <c r="E279" s="1">
-        <v>1</v>
-      </c>
-      <c r="F279" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A280" s="1">
-        <v>11040010</v>
-      </c>
-      <c r="B280" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C280" s="1">
-        <v>10</v>
-      </c>
-      <c r="D280" s="1">
-        <v>29</v>
-      </c>
-      <c r="E280" s="1">
-        <v>1</v>
-      </c>
-      <c r="F280" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A281" s="1">
-        <v>11040011</v>
-      </c>
-      <c r="B281" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C281" s="1">
-        <v>11</v>
-      </c>
-      <c r="D281" s="1">
-        <v>35</v>
-      </c>
-      <c r="E281" s="1">
-        <v>1</v>
-      </c>
-      <c r="F281" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A282" s="1">
-        <v>11040012</v>
-      </c>
-      <c r="B282" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C282" s="1">
-        <v>12</v>
-      </c>
-      <c r="D282" s="1">
-        <v>39</v>
-      </c>
-      <c r="E282" s="1">
-        <v>1</v>
-      </c>
-      <c r="F282" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A283" s="1">
-        <v>11040013</v>
-      </c>
-      <c r="B283" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C283" s="1">
-        <v>13</v>
-      </c>
-      <c r="D283" s="1">
-        <v>39</v>
-      </c>
-      <c r="E283" s="1">
-        <v>1</v>
-      </c>
-      <c r="F283" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A284" s="1">
-        <v>11040014</v>
-      </c>
-      <c r="B284" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C284" s="1">
-        <v>14</v>
-      </c>
-      <c r="D284" s="1">
-        <v>39</v>
-      </c>
-      <c r="E284" s="1">
-        <v>1</v>
-      </c>
-      <c r="F284" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A285" s="1">
-        <v>11040015</v>
-      </c>
-      <c r="B285" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C285" s="1">
-        <v>15</v>
-      </c>
-      <c r="D285" s="1">
-        <v>39</v>
-      </c>
-      <c r="E285" s="1">
-        <v>1</v>
-      </c>
-      <c r="F285" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A286" s="1">
-        <v>11040016</v>
-      </c>
-      <c r="B286" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C286" s="1">
-        <v>16</v>
-      </c>
-      <c r="D286" s="1">
-        <v>46</v>
-      </c>
-      <c r="E286" s="1">
-        <v>1</v>
-      </c>
-      <c r="F286" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A287" s="1">
-        <v>11040017</v>
-      </c>
-      <c r="B287" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C287" s="1">
-        <v>17</v>
-      </c>
-      <c r="D287" s="1">
-        <v>48</v>
-      </c>
-      <c r="E287" s="1">
-        <v>1</v>
-      </c>
-      <c r="F287" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A288" s="1">
-        <v>11040018</v>
-      </c>
-      <c r="B288" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C288" s="1">
-        <v>18</v>
-      </c>
-      <c r="D288" s="1">
-        <v>48</v>
-      </c>
-      <c r="E288" s="1">
-        <v>1</v>
-      </c>
-      <c r="F288" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A289" s="1">
-        <v>11040019</v>
-      </c>
-      <c r="B289" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C289" s="1">
-        <v>19</v>
-      </c>
-      <c r="D289" s="1">
-        <v>48</v>
-      </c>
-      <c r="E289" s="1">
-        <v>1</v>
-      </c>
-      <c r="F289" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A290" s="1">
-        <v>11040020</v>
-      </c>
-      <c r="B290" s="1">
-        <v>1104</v>
-      </c>
-      <c r="C290" s="1">
-        <v>20</v>
-      </c>
-      <c r="D290" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E290" s="1">
-        <v>1</v>
-      </c>
-      <c r="F290" s="1">
         <v>0</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DE400AF-C0C3-4131-BA35-BD8072F25932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421A2F0D-D7E7-45AF-BF16-E49262C08CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="D211" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E211" s="1">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>
@@ -4841,7 +4841,7 @@
         <v>11</v>
       </c>
       <c r="D221" s="1">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E221" s="1">
         <v>1</v>
@@ -4861,7 +4861,7 @@
         <v>12</v>
       </c>
       <c r="D222" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E222" s="1">
         <v>1</v>
@@ -4881,7 +4881,7 @@
         <v>13</v>
       </c>
       <c r="D223" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E223" s="1">
         <v>1</v>
@@ -4901,7 +4901,7 @@
         <v>14</v>
       </c>
       <c r="D224" s="1">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E224" s="1">
         <v>1</v>
@@ -4921,7 +4921,7 @@
         <v>15</v>
       </c>
       <c r="D225" s="1">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E225" s="1">
         <v>1</v>
@@ -5041,7 +5041,7 @@
         <v>21</v>
       </c>
       <c r="D231" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E231" s="1">
         <v>1</v>
@@ -5061,7 +5061,7 @@
         <v>22</v>
       </c>
       <c r="D232" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E232" s="1">
         <v>1</v>
@@ -5241,7 +5241,7 @@
         <v>31</v>
       </c>
       <c r="D241" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E241" s="1">
         <v>1</v>
@@ -5261,7 +5261,7 @@
         <v>32</v>
       </c>
       <c r="D242" s="1">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E242" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421A2F0D-D7E7-45AF-BF16-E49262C08CD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7F3DA8-4F26-41FD-9F98-99BBD9831AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
@@ -547,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.15">
@@ -567,7 +567,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.15">
@@ -587,7 +587,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.15">
@@ -607,7 +607,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.15">
@@ -627,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.15">
@@ -647,7 +647,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.15">
@@ -667,7 +667,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.15">
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.15">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
@@ -727,7 +727,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
@@ -747,7 +747,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
@@ -807,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
@@ -827,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
@@ -847,7 +847,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
@@ -867,7 +867,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.15">
@@ -907,7 +907,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
@@ -927,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.15">
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
@@ -967,7 +967,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
@@ -987,7 +987,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
@@ -1027,7 +1027,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
@@ -1047,7 +1047,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.15">
@@ -1087,7 +1087,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
@@ -1107,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
@@ -1127,7 +1127,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
@@ -1147,7 +1147,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.15">
@@ -1167,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.15">
@@ -1187,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
@@ -1207,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.15">
@@ -1227,7 +1227,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.15">
@@ -1267,7 +1267,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.15">
@@ -1287,7 +1287,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
@@ -1307,7 +1307,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
@@ -1327,7 +1327,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.15">
@@ -1347,7 +1347,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
@@ -1367,7 +1367,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
@@ -1387,7 +1387,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.15">
@@ -1407,7 +1407,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.15">
@@ -1427,7 +1427,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.15">
@@ -1447,7 +1447,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.15">
@@ -1467,7 +1467,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.15">
@@ -1487,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.15">
@@ -1507,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.15">
@@ -1527,7 +1527,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.15">
@@ -1547,7 +1547,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.15">
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="F57" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.15">
@@ -1587,7 +1587,7 @@
         <v>1</v>
       </c>
       <c r="F58" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.15">
@@ -1607,7 +1607,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.15">
@@ -1627,7 +1627,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.15">
@@ -1647,7 +1647,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.15">
@@ -1667,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.15">
@@ -1687,7 +1687,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.15">
@@ -1707,7 +1707,7 @@
         <v>1</v>
       </c>
       <c r="F64" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.15">
@@ -1727,7 +1727,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.15">
@@ -1747,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
@@ -1767,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
@@ -1787,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="F68" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.15">
@@ -1807,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.15">
@@ -1827,7 +1827,7 @@
         <v>1</v>
       </c>
       <c r="F70" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.15">
@@ -1847,7 +1847,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.15">
@@ -1867,7 +1867,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.15">
@@ -1887,7 +1887,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.15">
@@ -1907,7 +1907,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
@@ -1927,7 +1927,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.15">
@@ -1947,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
@@ -1967,7 +1967,7 @@
         <v>1</v>
       </c>
       <c r="F77" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.15">
@@ -1987,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="F78" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.15">
@@ -2007,7 +2007,7 @@
         <v>1</v>
       </c>
       <c r="F79" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.15">
@@ -2027,7 +2027,7 @@
         <v>1</v>
       </c>
       <c r="F80" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.15">
@@ -2047,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.15">
@@ -2067,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.15">
@@ -2087,7 +2087,7 @@
         <v>1</v>
       </c>
       <c r="F83" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.15">
@@ -2107,7 +2107,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.15">
@@ -2127,7 +2127,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
@@ -2147,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="F86" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.15">
@@ -2167,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="F87" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.15">
@@ -2187,7 +2187,7 @@
         <v>1</v>
       </c>
       <c r="F88" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
@@ -2207,7 +2207,7 @@
         <v>1</v>
       </c>
       <c r="F89" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.15">
@@ -2227,7 +2227,7 @@
         <v>1</v>
       </c>
       <c r="F90" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
@@ -2267,7 +2267,7 @@
         <v>1</v>
       </c>
       <c r="F92" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.15">
@@ -2287,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="F93" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.15">
@@ -2307,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="F94" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.15">
@@ -2327,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="F95" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
@@ -2347,7 +2347,7 @@
         <v>1</v>
       </c>
       <c r="F96" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.15">
@@ -2367,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.15">
@@ -2387,7 +2387,7 @@
         <v>1</v>
       </c>
       <c r="F98" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.15">
@@ -2407,7 +2407,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.15">
@@ -2427,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="F100" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.15">
@@ -2447,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="F101" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.15">
@@ -2467,7 +2467,7 @@
         <v>1</v>
       </c>
       <c r="F102" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.15">
@@ -2487,7 +2487,7 @@
         <v>1</v>
       </c>
       <c r="F103" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.15">
@@ -2507,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="F104" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.15">
@@ -2527,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="F105" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.15">
@@ -2547,7 +2547,7 @@
         <v>1</v>
       </c>
       <c r="F106" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.15">
@@ -2567,7 +2567,7 @@
         <v>1</v>
       </c>
       <c r="F107" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.15">
@@ -2587,7 +2587,7 @@
         <v>1</v>
       </c>
       <c r="F108" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.15">
@@ -2607,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="F109" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.15">
@@ -2627,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="F110" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.15">
@@ -2647,7 +2647,7 @@
         <v>1</v>
       </c>
       <c r="F111" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.15">
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="F112" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
@@ -2687,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.15">
@@ -2707,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="F114" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.15">
@@ -2727,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="F115" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.15">
@@ -2747,7 +2747,7 @@
         <v>1</v>
       </c>
       <c r="F116" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.15">
@@ -2767,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="F117" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.15">
@@ -2787,7 +2787,7 @@
         <v>1</v>
       </c>
       <c r="F118" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.15">
@@ -2807,7 +2807,7 @@
         <v>1</v>
       </c>
       <c r="F119" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.15">
@@ -2827,7 +2827,7 @@
         <v>1</v>
       </c>
       <c r="F120" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.15">
@@ -2847,7 +2847,7 @@
         <v>1</v>
       </c>
       <c r="F121" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.15">
@@ -2867,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="F122" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.15">
@@ -2887,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="F123" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.15">
@@ -2907,7 +2907,7 @@
         <v>1</v>
       </c>
       <c r="F124" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.15">
@@ -2927,7 +2927,7 @@
         <v>1</v>
       </c>
       <c r="F125" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.15">
@@ -2947,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="F126" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.15">
@@ -2967,7 +2967,7 @@
         <v>1</v>
       </c>
       <c r="F127" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.15">
@@ -2987,7 +2987,7 @@
         <v>1</v>
       </c>
       <c r="F128" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.15">
@@ -3007,7 +3007,7 @@
         <v>1</v>
       </c>
       <c r="F129" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.15">
@@ -3027,7 +3027,7 @@
         <v>1</v>
       </c>
       <c r="F130" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="1">
-        <v>3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.15">
@@ -3067,7 +3067,7 @@
         <v>1</v>
       </c>
       <c r="F132" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
@@ -3087,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="F133" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.15">
@@ -3107,7 +3107,7 @@
         <v>1</v>
       </c>
       <c r="F134" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
@@ -3127,7 +3127,7 @@
         <v>1</v>
       </c>
       <c r="F135" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.15">
@@ -3147,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="F136" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.15">
@@ -3167,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="F137" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
@@ -3187,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="F138" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.15">
@@ -3207,7 +3207,7 @@
         <v>1</v>
       </c>
       <c r="F139" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.15">
@@ -3227,7 +3227,7 @@
         <v>1</v>
       </c>
       <c r="F140" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.15">
@@ -3247,7 +3247,7 @@
         <v>0</v>
       </c>
       <c r="F141" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
@@ -3267,7 +3267,7 @@
         <v>1</v>
       </c>
       <c r="F142" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
@@ -3287,7 +3287,7 @@
         <v>1</v>
       </c>
       <c r="F143" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -3307,7 +3307,7 @@
         <v>1</v>
       </c>
       <c r="F144" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.15">
@@ -3327,7 +3327,7 @@
         <v>1</v>
       </c>
       <c r="F145" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.15">
@@ -3347,7 +3347,7 @@
         <v>1</v>
       </c>
       <c r="F146" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.15">
@@ -3367,7 +3367,7 @@
         <v>1</v>
       </c>
       <c r="F147" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.15">
@@ -3387,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="F148" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.15">
@@ -3407,7 +3407,7 @@
         <v>1</v>
       </c>
       <c r="F149" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.15">
@@ -3427,7 +3427,7 @@
         <v>1</v>
       </c>
       <c r="F150" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.15">
@@ -3467,7 +3467,7 @@
         <v>1</v>
       </c>
       <c r="F152" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.15">
@@ -3487,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="F153" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.15">
@@ -3507,7 +3507,7 @@
         <v>1</v>
       </c>
       <c r="F154" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.15">
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="F155" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.15">
@@ -3547,7 +3547,7 @@
         <v>1</v>
       </c>
       <c r="F156" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.15">
@@ -3567,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="F157" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.15">
@@ -3587,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="F158" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.15">
@@ -3607,7 +3607,7 @@
         <v>1</v>
       </c>
       <c r="F159" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.15">
@@ -3627,7 +3627,7 @@
         <v>1</v>
       </c>
       <c r="F160" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.15">
@@ -3647,7 +3647,7 @@
         <v>1</v>
       </c>
       <c r="F161" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.15">
@@ -3667,7 +3667,7 @@
         <v>1</v>
       </c>
       <c r="F162" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.15">
@@ -3687,7 +3687,7 @@
         <v>1</v>
       </c>
       <c r="F163" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.15">
@@ -3707,7 +3707,7 @@
         <v>1</v>
       </c>
       <c r="F164" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.15">
@@ -3727,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="F165" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.15">
@@ -3747,7 +3747,7 @@
         <v>1</v>
       </c>
       <c r="F166" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
@@ -3767,7 +3767,7 @@
         <v>1</v>
       </c>
       <c r="F167" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
@@ -3787,7 +3787,7 @@
         <v>1</v>
       </c>
       <c r="F168" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.15">
@@ -3807,7 +3807,7 @@
         <v>1</v>
       </c>
       <c r="F169" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.15">
@@ -3827,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="F170" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.15">
@@ -3847,7 +3847,7 @@
         <v>1</v>
       </c>
       <c r="F171" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.15">
@@ -3867,7 +3867,7 @@
         <v>1</v>
       </c>
       <c r="F172" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.15">
@@ -3887,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="F173" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
@@ -3907,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="F174" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.15">
@@ -3927,7 +3927,7 @@
         <v>1</v>
       </c>
       <c r="F175" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
@@ -3947,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="F176" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.15">
@@ -3967,7 +3967,7 @@
         <v>1</v>
       </c>
       <c r="F177" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.15">
@@ -3987,7 +3987,7 @@
         <v>1</v>
       </c>
       <c r="F178" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.15">
@@ -4007,7 +4007,7 @@
         <v>1</v>
       </c>
       <c r="F179" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.15">
@@ -4027,7 +4027,7 @@
         <v>1</v>
       </c>
       <c r="F180" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.15">
@@ -4047,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="F181" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.15">
@@ -4067,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="F182" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.15">
@@ -4087,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="F183" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.15">
@@ -4107,7 +4107,7 @@
         <v>1</v>
       </c>
       <c r="F184" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.15">
@@ -4127,7 +4127,7 @@
         <v>1</v>
       </c>
       <c r="F185" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.15">
@@ -4147,7 +4147,7 @@
         <v>1</v>
       </c>
       <c r="F186" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.15">
@@ -4167,7 +4167,7 @@
         <v>1</v>
       </c>
       <c r="F187" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.15">
@@ -4187,7 +4187,7 @@
         <v>1</v>
       </c>
       <c r="F188" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.15">
@@ -4207,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="F189" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.15">
@@ -4227,7 +4227,7 @@
         <v>1</v>
       </c>
       <c r="F190" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.15">
@@ -4247,7 +4247,7 @@
         <v>1</v>
       </c>
       <c r="F191" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.15">
@@ -4267,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="F192" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.15">
@@ -4287,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="F193" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.15">
@@ -4307,7 +4307,7 @@
         <v>1</v>
       </c>
       <c r="F194" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.15">
@@ -4327,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="F195" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.15">
@@ -4347,7 +4347,7 @@
         <v>1</v>
       </c>
       <c r="F196" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.15">
@@ -4367,7 +4367,7 @@
         <v>1</v>
       </c>
       <c r="F197" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.15">
@@ -4387,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="F198" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.15">
@@ -4407,7 +4407,7 @@
         <v>1</v>
       </c>
       <c r="F199" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.15">
@@ -4427,7 +4427,7 @@
         <v>1</v>
       </c>
       <c r="F200" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.15">
@@ -4447,7 +4447,7 @@
         <v>1</v>
       </c>
       <c r="F201" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.15">
@@ -4467,7 +4467,7 @@
         <v>1</v>
       </c>
       <c r="F202" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.15">
@@ -4487,7 +4487,7 @@
         <v>1</v>
       </c>
       <c r="F203" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.15">
@@ -4507,7 +4507,7 @@
         <v>1</v>
       </c>
       <c r="F204" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.15">
@@ -4527,7 +4527,7 @@
         <v>1</v>
       </c>
       <c r="F205" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.15">
@@ -4547,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="F206" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.15">
@@ -4567,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="F207" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.15">
@@ -4587,7 +4587,7 @@
         <v>1</v>
       </c>
       <c r="F208" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.15">
@@ -4607,7 +4607,7 @@
         <v>1</v>
       </c>
       <c r="F209" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.15">
@@ -4627,7 +4627,7 @@
         <v>1</v>
       </c>
       <c r="F210" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.15">
@@ -4667,7 +4667,7 @@
         <v>1</v>
       </c>
       <c r="F212" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.15">
@@ -4687,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="F213" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.15">
@@ -4707,7 +4707,7 @@
         <v>1</v>
       </c>
       <c r="F214" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.15">
@@ -4727,7 +4727,7 @@
         <v>1</v>
       </c>
       <c r="F215" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.15">
@@ -4747,7 +4747,7 @@
         <v>1</v>
       </c>
       <c r="F216" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.15">
@@ -4767,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="F217" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.15">
@@ -4787,7 +4787,7 @@
         <v>1</v>
       </c>
       <c r="F218" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.15">
@@ -4807,7 +4807,7 @@
         <v>1</v>
       </c>
       <c r="F219" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.15">
@@ -4827,7 +4827,7 @@
         <v>1</v>
       </c>
       <c r="F220" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.15">
@@ -4847,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="F221" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.15">
@@ -4867,7 +4867,7 @@
         <v>1</v>
       </c>
       <c r="F222" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.15">
@@ -4887,7 +4887,7 @@
         <v>1</v>
       </c>
       <c r="F223" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.15">
@@ -4907,7 +4907,7 @@
         <v>1</v>
       </c>
       <c r="F224" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.15">
@@ -4927,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="F225" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.15">
@@ -4947,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="F226" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.15">
@@ -4967,7 +4967,7 @@
         <v>1</v>
       </c>
       <c r="F227" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.15">
@@ -4987,7 +4987,7 @@
         <v>1</v>
       </c>
       <c r="F228" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.15">
@@ -5007,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="F229" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.15">
@@ -5027,7 +5027,7 @@
         <v>1</v>
       </c>
       <c r="F230" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.15">
@@ -5047,7 +5047,7 @@
         <v>1</v>
       </c>
       <c r="F231" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.15">
@@ -5067,7 +5067,7 @@
         <v>1</v>
       </c>
       <c r="F232" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.15">
@@ -5087,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="F233" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.15">
@@ -5107,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="F234" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.15">
@@ -5127,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="F235" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.15">
@@ -5147,7 +5147,7 @@
         <v>1</v>
       </c>
       <c r="F236" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.15">
@@ -5167,7 +5167,7 @@
         <v>1</v>
       </c>
       <c r="F237" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.15">
@@ -5187,7 +5187,7 @@
         <v>1</v>
       </c>
       <c r="F238" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.15">
@@ -5207,7 +5207,7 @@
         <v>1</v>
       </c>
       <c r="F239" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.15">
@@ -5227,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="F240" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.15">
@@ -5247,7 +5247,7 @@
         <v>1</v>
       </c>
       <c r="F241" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.15">
@@ -5267,7 +5267,7 @@
         <v>1</v>
       </c>
       <c r="F242" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.15">
@@ -5287,7 +5287,7 @@
         <v>1</v>
       </c>
       <c r="F243" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.15">
@@ -5307,7 +5307,7 @@
         <v>1</v>
       </c>
       <c r="F244" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.15">
@@ -5327,7 +5327,7 @@
         <v>1</v>
       </c>
       <c r="F245" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.15">
@@ -5347,7 +5347,7 @@
         <v>1</v>
       </c>
       <c r="F246" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.15">
@@ -5367,7 +5367,7 @@
         <v>1</v>
       </c>
       <c r="F247" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.15">
@@ -5387,7 +5387,7 @@
         <v>1</v>
       </c>
       <c r="F248" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.15">
@@ -5407,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="F249" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.15">
@@ -5427,7 +5427,7 @@
         <v>1</v>
       </c>
       <c r="F250" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7F3DA8-4F26-41FD-9F98-99BBD9831AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58811E1E-75FD-4FFC-B203-056F2060B71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58811E1E-75FD-4FFC-B203-056F2060B71B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06B253A-2F27-46C2-8B86-A64B20370B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="D211" s="1">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E211" s="1">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06B253A-2F27-46C2-8B86-A64B20370B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A8303A-584C-42A2-8578-29C56534A8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A8303A-584C-42A2-8578-29C56534A8DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCA0BCC-51B9-4B72-9E9E-2A5964889EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCA0BCC-51B9-4B72-9E9E-2A5964889EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A2E008-A64B-422C-B9EB-8CA8E9486C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="D211" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E211" s="1">
         <v>0</v>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A2E008-A64B-422C-B9EB-8CA8E9486C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02A9887-FFF1-4E2B-B531-916EB8EADCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>144</v>
+        <v>468</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>216</v>
+        <v>648</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02A9887-FFF1-4E2B-B531-916EB8EADCB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60AB824-2E2F-4ED0-8ABE-9B6B00E0DF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>648</v>
+        <v>612</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60AB824-2E2F-4ED0-8ABE-9B6B00E0DF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C147704-694F-4566-AEBF-151846701485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>94</v>
+        <v>137</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C147704-694F-4566-AEBF-151846701485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D0C902-723A-49C5-A4F3-4AE90FE8E440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="D211" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E211" s="1">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>137</v>
+        <v>40</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>168</v>
+        <v>55</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>196</v>
+        <v>75</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>454</v>
+        <v>95</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>612</v>
+        <v>125</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D0C902-723A-49C5-A4F3-4AE90FE8E440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F59622-609F-41D3-8E76-4BB86112B9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F59622-609F-41D3-8E76-4BB86112B9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18C16EA-AD17-4557-B87D-40836736E909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18C16EA-AD17-4557-B87D-40836736E909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F92F1C-B975-490E-92C9-EA552CA0C702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="1">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5F59622-609F-41D3-8E76-4BB86112B9C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E47A5C6-7416-43ED-B310-8A488FD680A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D212" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F92F1C-B975-490E-92C9-EA552CA0C702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E47A5C6-7416-43ED-B310-8A488FD680A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>56</v>
+        <v>150</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E47A5C6-7416-43ED-B310-8A488FD680A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F92F1C-B975-490E-92C9-EA552CA0C702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4681,7 +4681,7 @@
         <v>3</v>
       </c>
       <c r="D213" s="1">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4701,7 +4701,7 @@
         <v>4</v>
       </c>
       <c r="D214" s="1">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
       <c r="D215" s="1">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4741,7 +4741,7 @@
         <v>6</v>
       </c>
       <c r="D216" s="1">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4761,7 +4761,7 @@
         <v>7</v>
       </c>
       <c r="D217" s="1">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>8</v>
       </c>
       <c r="D218" s="1">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4801,7 +4801,7 @@
         <v>9</v>
       </c>
       <c r="D219" s="1">
-        <v>150</v>
+        <v>56</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4821,7 +4821,7 @@
         <v>10</v>
       </c>
       <c r="D220" s="1">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E47A5C6-7416-43ED-B310-8A488FD680A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1ED820-9967-47FA-8EC5-44F468E9BCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F250"/>
+  <dimension ref="A1:F280"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
@@ -5430,6 +5430,606 @@
         <v>100</v>
       </c>
     </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A251" s="1">
+        <v>11020001</v>
+      </c>
+      <c r="B251" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C251" s="1">
+        <v>1</v>
+      </c>
+      <c r="D251" s="1">
+        <v>4</v>
+      </c>
+      <c r="E251" s="1">
+        <v>0</v>
+      </c>
+      <c r="F251" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A252" s="1">
+        <v>11020002</v>
+      </c>
+      <c r="B252" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C252" s="1">
+        <v>2</v>
+      </c>
+      <c r="D252" s="1">
+        <v>8</v>
+      </c>
+      <c r="E252" s="1">
+        <v>1</v>
+      </c>
+      <c r="F252" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A253" s="1">
+        <v>11020003</v>
+      </c>
+      <c r="B253" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C253" s="1">
+        <v>3</v>
+      </c>
+      <c r="D253" s="1">
+        <v>14</v>
+      </c>
+      <c r="E253" s="1">
+        <v>1</v>
+      </c>
+      <c r="F253" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A254" s="1">
+        <v>11020004</v>
+      </c>
+      <c r="B254" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C254" s="1">
+        <v>4</v>
+      </c>
+      <c r="D254" s="1">
+        <v>23</v>
+      </c>
+      <c r="E254" s="1">
+        <v>1</v>
+      </c>
+      <c r="F254" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A255" s="1">
+        <v>11020005</v>
+      </c>
+      <c r="B255" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C255" s="1">
+        <v>5</v>
+      </c>
+      <c r="D255" s="1">
+        <v>35</v>
+      </c>
+      <c r="E255" s="1">
+        <v>1</v>
+      </c>
+      <c r="F255" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A256" s="1">
+        <v>11020006</v>
+      </c>
+      <c r="B256" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C256" s="1">
+        <v>6</v>
+      </c>
+      <c r="D256" s="1">
+        <v>50</v>
+      </c>
+      <c r="E256" s="1">
+        <v>1</v>
+      </c>
+      <c r="F256" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A257" s="1">
+        <v>11020007</v>
+      </c>
+      <c r="B257" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C257" s="1">
+        <v>7</v>
+      </c>
+      <c r="D257" s="1">
+        <v>70</v>
+      </c>
+      <c r="E257" s="1">
+        <v>1</v>
+      </c>
+      <c r="F257" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A258" s="1">
+        <v>11020008</v>
+      </c>
+      <c r="B258" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C258" s="1">
+        <v>8</v>
+      </c>
+      <c r="D258" s="1">
+        <v>95</v>
+      </c>
+      <c r="E258" s="1">
+        <v>1</v>
+      </c>
+      <c r="F258" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A259" s="1">
+        <v>11020009</v>
+      </c>
+      <c r="B259" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C259" s="1">
+        <v>9</v>
+      </c>
+      <c r="D259" s="1">
+        <v>120</v>
+      </c>
+      <c r="E259" s="1">
+        <v>1</v>
+      </c>
+      <c r="F259" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A260" s="1">
+        <v>11020010</v>
+      </c>
+      <c r="B260" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C260" s="1">
+        <v>10</v>
+      </c>
+      <c r="D260" s="1">
+        <v>150</v>
+      </c>
+      <c r="E260" s="1">
+        <v>1</v>
+      </c>
+      <c r="F260" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A261" s="1">
+        <v>11020011</v>
+      </c>
+      <c r="B261" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C261" s="1">
+        <v>11</v>
+      </c>
+      <c r="D261" s="1">
+        <v>25</v>
+      </c>
+      <c r="E261" s="1">
+        <v>1</v>
+      </c>
+      <c r="F261" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A262" s="1">
+        <v>11020012</v>
+      </c>
+      <c r="B262" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C262" s="1">
+        <v>12</v>
+      </c>
+      <c r="D262" s="1">
+        <v>35</v>
+      </c>
+      <c r="E262" s="1">
+        <v>1</v>
+      </c>
+      <c r="F262" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A263" s="1">
+        <v>11020013</v>
+      </c>
+      <c r="B263" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C263" s="1">
+        <v>13</v>
+      </c>
+      <c r="D263" s="1">
+        <v>45</v>
+      </c>
+      <c r="E263" s="1">
+        <v>1</v>
+      </c>
+      <c r="F263" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A264" s="1">
+        <v>11020014</v>
+      </c>
+      <c r="B264" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C264" s="1">
+        <v>14</v>
+      </c>
+      <c r="D264" s="1">
+        <v>55</v>
+      </c>
+      <c r="E264" s="1">
+        <v>1</v>
+      </c>
+      <c r="F264" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A265" s="1">
+        <v>11020015</v>
+      </c>
+      <c r="B265" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C265" s="1">
+        <v>15</v>
+      </c>
+      <c r="D265" s="1">
+        <v>65</v>
+      </c>
+      <c r="E265" s="1">
+        <v>1</v>
+      </c>
+      <c r="F265" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A266" s="1">
+        <v>11020016</v>
+      </c>
+      <c r="B266" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C266" s="1">
+        <v>16</v>
+      </c>
+      <c r="D266" s="1">
+        <v>80</v>
+      </c>
+      <c r="E266" s="1">
+        <v>1</v>
+      </c>
+      <c r="F266" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A267" s="1">
+        <v>11020017</v>
+      </c>
+      <c r="B267" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C267" s="1">
+        <v>17</v>
+      </c>
+      <c r="D267" s="1">
+        <v>95</v>
+      </c>
+      <c r="E267" s="1">
+        <v>1</v>
+      </c>
+      <c r="F267" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A268" s="1">
+        <v>11020018</v>
+      </c>
+      <c r="B268" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C268" s="1">
+        <v>18</v>
+      </c>
+      <c r="D268" s="1">
+        <v>110</v>
+      </c>
+      <c r="E268" s="1">
+        <v>1</v>
+      </c>
+      <c r="F268" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A269" s="1">
+        <v>11020019</v>
+      </c>
+      <c r="B269" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C269" s="1">
+        <v>19</v>
+      </c>
+      <c r="D269" s="1">
+        <v>135</v>
+      </c>
+      <c r="E269" s="1">
+        <v>1</v>
+      </c>
+      <c r="F269" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A270" s="1">
+        <v>11020020</v>
+      </c>
+      <c r="B270" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C270" s="1">
+        <v>20</v>
+      </c>
+      <c r="D270" s="1">
+        <v>160</v>
+      </c>
+      <c r="E270" s="1">
+        <v>1</v>
+      </c>
+      <c r="F270" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A271" s="1">
+        <v>11020021</v>
+      </c>
+      <c r="B271" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C271" s="1">
+        <v>21</v>
+      </c>
+      <c r="D271" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E271" s="1">
+        <v>1</v>
+      </c>
+      <c r="F271" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A272" s="1">
+        <v>11020022</v>
+      </c>
+      <c r="B272" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C272" s="1">
+        <v>22</v>
+      </c>
+      <c r="D272" s="1">
+        <v>20</v>
+      </c>
+      <c r="E272" s="1">
+        <v>1</v>
+      </c>
+      <c r="F272" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A273" s="1">
+        <v>11020023</v>
+      </c>
+      <c r="B273" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C273" s="1">
+        <v>23</v>
+      </c>
+      <c r="D273" s="1">
+        <v>20</v>
+      </c>
+      <c r="E273" s="1">
+        <v>1</v>
+      </c>
+      <c r="F273" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A274" s="1">
+        <v>11020024</v>
+      </c>
+      <c r="B274" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C274" s="1">
+        <v>24</v>
+      </c>
+      <c r="D274" s="1">
+        <v>20</v>
+      </c>
+      <c r="E274" s="1">
+        <v>1</v>
+      </c>
+      <c r="F274" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A275" s="1">
+        <v>11020025</v>
+      </c>
+      <c r="B275" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C275" s="1">
+        <v>25</v>
+      </c>
+      <c r="D275" s="1">
+        <v>20</v>
+      </c>
+      <c r="E275" s="1">
+        <v>1</v>
+      </c>
+      <c r="F275" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A276" s="1">
+        <v>11020026</v>
+      </c>
+      <c r="B276" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C276" s="1">
+        <v>26</v>
+      </c>
+      <c r="D276" s="1">
+        <v>20</v>
+      </c>
+      <c r="E276" s="1">
+        <v>1</v>
+      </c>
+      <c r="F276" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A277" s="1">
+        <v>11020027</v>
+      </c>
+      <c r="B277" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C277" s="1">
+        <v>27</v>
+      </c>
+      <c r="D277" s="1">
+        <v>20</v>
+      </c>
+      <c r="E277" s="1">
+        <v>1</v>
+      </c>
+      <c r="F277" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A278" s="1">
+        <v>11020028</v>
+      </c>
+      <c r="B278" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C278" s="1">
+        <v>28</v>
+      </c>
+      <c r="D278" s="1">
+        <v>20</v>
+      </c>
+      <c r="E278" s="1">
+        <v>1</v>
+      </c>
+      <c r="F278" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A279" s="1">
+        <v>11020029</v>
+      </c>
+      <c r="B279" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C279" s="1">
+        <v>29</v>
+      </c>
+      <c r="D279" s="1">
+        <v>20</v>
+      </c>
+      <c r="E279" s="1">
+        <v>1</v>
+      </c>
+      <c r="F279" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A280" s="1">
+        <v>11020030</v>
+      </c>
+      <c r="B280" s="1">
+        <v>1102</v>
+      </c>
+      <c r="C280" s="1">
+        <v>30</v>
+      </c>
+      <c r="D280" s="1">
+        <v>20</v>
+      </c>
+      <c r="E280" s="1">
+        <v>1</v>
+      </c>
+      <c r="F280" s="1">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1ED820-9967-47FA-8EC5-44F468E9BCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9EFC62-3F17-4B1B-A524-F793E68C4823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5481,7 +5481,7 @@
         <v>3</v>
       </c>
       <c r="D253" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E253" s="1">
         <v>1</v>
@@ -5501,7 +5501,7 @@
         <v>4</v>
       </c>
       <c r="D254" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E254" s="1">
         <v>1</v>
@@ -5521,7 +5521,7 @@
         <v>5</v>
       </c>
       <c r="D255" s="1">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E255" s="1">
         <v>1</v>
@@ -5541,7 +5541,7 @@
         <v>6</v>
       </c>
       <c r="D256" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E256" s="1">
         <v>1</v>
@@ -5561,7 +5561,7 @@
         <v>7</v>
       </c>
       <c r="D257" s="1">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="E257" s="1">
         <v>1</v>
@@ -5581,7 +5581,7 @@
         <v>8</v>
       </c>
       <c r="D258" s="1">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="E258" s="1">
         <v>1</v>
@@ -5601,7 +5601,7 @@
         <v>9</v>
       </c>
       <c r="D259" s="1">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E259" s="1">
         <v>1</v>
@@ -5621,7 +5621,7 @@
         <v>10</v>
       </c>
       <c r="D260" s="1">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E260" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9EFC62-3F17-4B1B-A524-F793E68C4823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBF8CAB-2BD1-4E97-937B-EE0751B5B36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5441,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="D251" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E251" s="1">
         <v>0</v>
@@ -5461,7 +5461,7 @@
         <v>2</v>
       </c>
       <c r="D252" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E252" s="1">
         <v>1</v>
@@ -5481,7 +5481,7 @@
         <v>3</v>
       </c>
       <c r="D253" s="1">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E253" s="1">
         <v>1</v>
@@ -5501,7 +5501,7 @@
         <v>4</v>
       </c>
       <c r="D254" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E254" s="1">
         <v>1</v>
@@ -5521,7 +5521,7 @@
         <v>5</v>
       </c>
       <c r="D255" s="1">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E255" s="1">
         <v>1</v>
@@ -5541,7 +5541,7 @@
         <v>6</v>
       </c>
       <c r="D256" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E256" s="1">
         <v>1</v>
@@ -5561,7 +5561,7 @@
         <v>7</v>
       </c>
       <c r="D257" s="1">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E257" s="1">
         <v>1</v>
@@ -5581,7 +5581,7 @@
         <v>8</v>
       </c>
       <c r="D258" s="1">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E258" s="1">
         <v>1</v>
@@ -5641,7 +5641,7 @@
         <v>11</v>
       </c>
       <c r="D261" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E261" s="1">
         <v>1</v>
@@ -5661,7 +5661,7 @@
         <v>12</v>
       </c>
       <c r="D262" s="1">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E262" s="1">
         <v>1</v>
@@ -5681,7 +5681,7 @@
         <v>13</v>
       </c>
       <c r="D263" s="1">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E263" s="1">
         <v>1</v>
@@ -5701,7 +5701,7 @@
         <v>14</v>
       </c>
       <c r="D264" s="1">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E264" s="1">
         <v>1</v>
@@ -5721,7 +5721,7 @@
         <v>15</v>
       </c>
       <c r="D265" s="1">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E265" s="1">
         <v>1</v>
@@ -5741,7 +5741,7 @@
         <v>16</v>
       </c>
       <c r="D266" s="1">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E266" s="1">
         <v>1</v>
@@ -5761,7 +5761,7 @@
         <v>17</v>
       </c>
       <c r="D267" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E267" s="1">
         <v>1</v>
@@ -5781,7 +5781,7 @@
         <v>18</v>
       </c>
       <c r="D268" s="1">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E268" s="1">
         <v>1</v>
@@ -5801,7 +5801,7 @@
         <v>19</v>
       </c>
       <c r="D269" s="1">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="E269" s="1">
         <v>1</v>
@@ -5821,7 +5821,7 @@
         <v>20</v>
       </c>
       <c r="D270" s="1">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="E270" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBF8CAB-2BD1-4E97-937B-EE0751B5B36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD089108-7EB8-44A8-91FA-47BF7A436C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5441,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="D251" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E251" s="1">
         <v>0</v>
@@ -5461,7 +5461,7 @@
         <v>2</v>
       </c>
       <c r="D252" s="1">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E252" s="1">
         <v>1</v>
@@ -5481,7 +5481,7 @@
         <v>3</v>
       </c>
       <c r="D253" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E253" s="1">
         <v>1</v>
@@ -5501,7 +5501,7 @@
         <v>4</v>
       </c>
       <c r="D254" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E254" s="1">
         <v>1</v>
@@ -5521,7 +5521,7 @@
         <v>5</v>
       </c>
       <c r="D255" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E255" s="1">
         <v>1</v>
@@ -5541,7 +5541,7 @@
         <v>6</v>
       </c>
       <c r="D256" s="1">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E256" s="1">
         <v>1</v>
@@ -5561,7 +5561,7 @@
         <v>7</v>
       </c>
       <c r="D257" s="1">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="E257" s="1">
         <v>1</v>
@@ -5581,7 +5581,7 @@
         <v>8</v>
       </c>
       <c r="D258" s="1">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E258" s="1">
         <v>1</v>
@@ -5601,7 +5601,7 @@
         <v>9</v>
       </c>
       <c r="D259" s="1">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="E259" s="1">
         <v>1</v>
@@ -5621,7 +5621,7 @@
         <v>10</v>
       </c>
       <c r="D260" s="1">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E260" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD089108-7EB8-44A8-91FA-47BF7A436C04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C71A9ED-74BF-45BF-92EC-077A03DCCC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5641,7 +5641,7 @@
         <v>11</v>
       </c>
       <c r="D261" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E261" s="1">
         <v>1</v>
@@ -5661,7 +5661,7 @@
         <v>12</v>
       </c>
       <c r="D262" s="1">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E262" s="1">
         <v>1</v>
@@ -5681,7 +5681,7 @@
         <v>13</v>
       </c>
       <c r="D263" s="1">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E263" s="1">
         <v>1</v>
@@ -5701,7 +5701,7 @@
         <v>14</v>
       </c>
       <c r="D264" s="1">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E264" s="1">
         <v>1</v>
@@ -5721,7 +5721,7 @@
         <v>15</v>
       </c>
       <c r="D265" s="1">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E265" s="1">
         <v>1</v>
@@ -5741,7 +5741,7 @@
         <v>16</v>
       </c>
       <c r="D266" s="1">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="E266" s="1">
         <v>1</v>
@@ -5761,7 +5761,7 @@
         <v>17</v>
       </c>
       <c r="D267" s="1">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="E267" s="1">
         <v>1</v>
@@ -5781,7 +5781,7 @@
         <v>18</v>
       </c>
       <c r="D268" s="1">
-        <v>105</v>
+        <v>84</v>
       </c>
       <c r="E268" s="1">
         <v>1</v>
@@ -5801,7 +5801,7 @@
         <v>19</v>
       </c>
       <c r="D269" s="1">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="E269" s="1">
         <v>1</v>
@@ -5821,7 +5821,7 @@
         <v>20</v>
       </c>
       <c r="D270" s="1">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="E270" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C71A9ED-74BF-45BF-92EC-077A03DCCC2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9529FE09-DC37-44E7-BFB5-37770D0E5062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_energy_level_v8!$A$4:$E$183</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F280"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
@@ -521,7 +521,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -541,7 +541,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
@@ -581,7 +581,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="1">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -601,7 +601,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="1">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
@@ -621,7 +621,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="1">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
@@ -641,7 +641,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="1">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -661,7 +661,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="1">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>9</v>
       </c>
       <c r="D13" s="1">
-        <v>1000</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
@@ -701,7 +701,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="1">
-        <v>1000</v>
+        <v>-1</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -712,19 +712,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
-        <v>10011</v>
+        <v>20001</v>
       </c>
       <c r="B15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D15" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="E15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1">
         <v>100</v>
@@ -732,16 +732,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
-        <v>10012</v>
+        <v>20002</v>
       </c>
       <c r="B16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1">
         <v>12</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1000</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
@@ -752,16 +752,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
-        <v>10013</v>
+        <v>20003</v>
       </c>
       <c r="B17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="1">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -772,16 +772,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
-        <v>10014</v>
+        <v>20004</v>
       </c>
       <c r="B18" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18" s="1">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="E18" s="1">
         <v>1</v>
@@ -792,16 +792,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
-        <v>10015</v>
+        <v>20005</v>
       </c>
       <c r="B19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D19" s="1">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="E19" s="1">
         <v>1</v>
@@ -812,16 +812,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
-        <v>10016</v>
+        <v>20006</v>
       </c>
       <c r="B20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D20" s="1">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
@@ -832,16 +832,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
-        <v>10017</v>
+        <v>20007</v>
       </c>
       <c r="B21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="1">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="E21" s="1">
         <v>1</v>
@@ -852,16 +852,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
-        <v>10018</v>
+        <v>20008</v>
       </c>
       <c r="B22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="E22" s="1">
         <v>1</v>
@@ -872,16 +872,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
-        <v>10019</v>
+        <v>20009</v>
       </c>
       <c r="B23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="1">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D23" s="1">
-        <v>1000</v>
+        <v>54</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -892,16 +892,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
-        <v>10020</v>
+        <v>20010</v>
       </c>
       <c r="B24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C24" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1">
-        <v>1000</v>
+        <v>-1</v>
       </c>
       <c r="E24" s="1">
         <v>1</v>
@@ -912,19 +912,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
-        <v>10021</v>
+        <v>30001</v>
       </c>
       <c r="B25" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" s="1">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D25" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="E25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1">
         <v>100</v>
@@ -932,16 +932,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
-        <v>10022</v>
+        <v>30002</v>
       </c>
       <c r="B26" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26" s="1">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D26" s="1">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -952,16 +952,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
-        <v>10023</v>
+        <v>30003</v>
       </c>
       <c r="B27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" s="1">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="E27" s="1">
         <v>1</v>
@@ -972,16 +972,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
-        <v>10024</v>
+        <v>30004</v>
       </c>
       <c r="B28" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" s="1">
+        <v>4</v>
+      </c>
+      <c r="D28" s="1">
         <v>24</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1000</v>
       </c>
       <c r="E28" s="1">
         <v>1</v>
@@ -992,16 +992,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
-        <v>10025</v>
+        <v>30005</v>
       </c>
       <c r="B29" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" s="1">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D29" s="1">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -1012,16 +1012,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
-        <v>10026</v>
+        <v>30006</v>
       </c>
       <c r="B30" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C30" s="1">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D30" s="1">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="E30" s="1">
         <v>1</v>
@@ -1032,16 +1032,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
-        <v>10027</v>
+        <v>30007</v>
       </c>
       <c r="B31" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D31" s="1">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
@@ -1052,16 +1052,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
-        <v>10028</v>
+        <v>30008</v>
       </c>
       <c r="B32" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="1">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D32" s="1">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -1072,16 +1072,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
-        <v>10029</v>
+        <v>30009</v>
       </c>
       <c r="B33" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C33" s="1">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D33" s="1">
-        <v>1000</v>
+        <v>54</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -1092,16 +1092,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
-        <v>10030</v>
+        <v>30010</v>
       </c>
       <c r="B34" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" s="1">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D34" s="1">
-        <v>1000</v>
+        <v>-1</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
@@ -1112,19 +1112,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
-        <v>10031</v>
+        <v>40001</v>
       </c>
       <c r="B35" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C35" s="1">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D35" s="1">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="E35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1">
         <v>100</v>
@@ -1132,16 +1132,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
-        <v>10032</v>
+        <v>40002</v>
       </c>
       <c r="B36" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C36" s="1">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="D36" s="1">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="E36" s="1">
         <v>1</v>
@@ -1152,16 +1152,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
-        <v>10033</v>
+        <v>40003</v>
       </c>
       <c r="B37" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C37" s="1">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="E37" s="1">
         <v>1</v>
@@ -1172,16 +1172,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
-        <v>10034</v>
+        <v>40004</v>
       </c>
       <c r="B38" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C38" s="1">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="D38" s="1">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -1192,16 +1192,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>10035</v>
+        <v>40005</v>
       </c>
       <c r="B39" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C39" s="1">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D39" s="1">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="E39" s="1">
         <v>1</v>
@@ -1212,16 +1212,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>10036</v>
+        <v>40006</v>
       </c>
       <c r="B40" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C40" s="1">
+        <v>6</v>
+      </c>
+      <c r="D40" s="1">
         <v>36</v>
-      </c>
-      <c r="D40" s="1">
-        <v>-1</v>
       </c>
       <c r="E40" s="1">
         <v>1</v>
@@ -1232,19 +1232,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>20001</v>
+        <v>40007</v>
       </c>
       <c r="B41" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D41" s="1">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="1">
         <v>100</v>
@@ -1252,16 +1252,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>20002</v>
+        <v>40008</v>
       </c>
       <c r="B42" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C42" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D42" s="1">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E42" s="1">
         <v>1</v>
@@ -1272,16 +1272,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>20003</v>
+        <v>40009</v>
       </c>
       <c r="B43" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C43" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D43" s="1">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="E43" s="1">
         <v>1</v>
@@ -1292,16 +1292,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>20004</v>
+        <v>40010</v>
       </c>
       <c r="B44" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C44" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D44" s="1">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
@@ -1312,19 +1312,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>20005</v>
+        <v>50001</v>
       </c>
       <c r="B45" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C45" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D45" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="1">
         <v>100</v>
@@ -1332,16 +1332,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
-        <v>20006</v>
+        <v>50002</v>
       </c>
       <c r="B46" s="1">
+        <v>5</v>
+      </c>
+      <c r="C46" s="1">
         <v>2</v>
       </c>
-      <c r="C46" s="1">
-        <v>6</v>
-      </c>
       <c r="D46" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E46" s="1">
         <v>1</v>
@@ -1352,16 +1352,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>20007</v>
+        <v>50003</v>
       </c>
       <c r="B47" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C47" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D47" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E47" s="1">
         <v>1</v>
@@ -1372,16 +1372,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>20008</v>
+        <v>50004</v>
       </c>
       <c r="B48" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C48" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D48" s="1">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E48" s="1">
         <v>1</v>
@@ -1392,16 +1392,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>20009</v>
+        <v>50005</v>
       </c>
       <c r="B49" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C49" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D49" s="1">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E49" s="1">
         <v>1</v>
@@ -1412,16 +1412,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>20010</v>
+        <v>50006</v>
       </c>
       <c r="B50" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C50" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D50" s="1">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -1432,16 +1432,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>20011</v>
+        <v>50007</v>
       </c>
       <c r="B51" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C51" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D51" s="1">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="E51" s="1">
         <v>1</v>
@@ -1452,16 +1452,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
-        <v>20012</v>
+        <v>50008</v>
       </c>
       <c r="B52" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C52" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D52" s="1">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E52" s="1">
         <v>1</v>
@@ -1472,16 +1472,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
-        <v>20013</v>
+        <v>50009</v>
       </c>
       <c r="B53" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C53" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D53" s="1">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="E53" s="1">
         <v>1</v>
@@ -1492,16 +1492,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
-        <v>20014</v>
+        <v>50010</v>
       </c>
       <c r="B54" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C54" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D54" s="1">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="E54" s="1">
         <v>1</v>
@@ -1512,19 +1512,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>20015</v>
+        <v>50011</v>
       </c>
       <c r="B55" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C55" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D55" s="1">
         <v>16</v>
       </c>
       <c r="E55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="1">
         <v>100</v>
@@ -1532,16 +1532,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
-        <v>20016</v>
+        <v>50012</v>
       </c>
       <c r="B56" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C56" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D56" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E56" s="1">
         <v>1</v>
@@ -1552,16 +1552,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
-        <v>20017</v>
+        <v>50013</v>
       </c>
       <c r="B57" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C57" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D57" s="1">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E57" s="1">
         <v>1</v>
@@ -1572,16 +1572,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
-        <v>20018</v>
+        <v>50014</v>
       </c>
       <c r="B58" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C58" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D58" s="1">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E58" s="1">
         <v>1</v>
@@ -1592,16 +1592,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
-        <v>20019</v>
+        <v>50015</v>
       </c>
       <c r="B59" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C59" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D59" s="1">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="E59" s="1">
         <v>1</v>
@@ -1612,16 +1612,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
-        <v>20020</v>
+        <v>50016</v>
       </c>
       <c r="B60" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C60" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D60" s="1">
-        <v>-1</v>
+        <v>60</v>
       </c>
       <c r="E60" s="1">
         <v>1</v>
@@ -1632,19 +1632,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
-        <v>30001</v>
+        <v>50017</v>
       </c>
       <c r="B61" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C61" s="1">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D61" s="1">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="E61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="1">
         <v>100</v>
@@ -1652,16 +1652,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
-        <v>30002</v>
+        <v>50018</v>
       </c>
       <c r="B62" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C62" s="1">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D62" s="1">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="E62" s="1">
         <v>1</v>
@@ -1672,16 +1672,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
-        <v>30003</v>
+        <v>50019</v>
       </c>
       <c r="B63" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63" s="1">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D63" s="1">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="E63" s="1">
         <v>1</v>
@@ -1692,16 +1692,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
-        <v>30004</v>
+        <v>50020</v>
       </c>
       <c r="B64" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C64" s="1">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D64" s="1">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="E64" s="1">
         <v>1</v>
@@ -1712,19 +1712,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
-        <v>30005</v>
+        <v>60001</v>
       </c>
       <c r="B65" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C65" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D65" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E65" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F65" s="1">
         <v>100</v>
@@ -1732,16 +1732,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
-        <v>30006</v>
+        <v>60002</v>
       </c>
       <c r="B66" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C66" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D66" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E66" s="1">
         <v>1</v>
@@ -1752,13 +1752,13 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
-        <v>30007</v>
+        <v>60003</v>
       </c>
       <c r="B67" s="1">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1">
         <v>3</v>
-      </c>
-      <c r="C67" s="1">
-        <v>7</v>
       </c>
       <c r="D67" s="1">
         <v>18</v>
@@ -1772,16 +1772,16 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
-        <v>30008</v>
+        <v>60004</v>
       </c>
       <c r="B68" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C68" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D68" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E68" s="1">
         <v>1</v>
@@ -1792,16 +1792,16 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
-        <v>30009</v>
+        <v>60005</v>
       </c>
       <c r="B69" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C69" s="1">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D69" s="1">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E69" s="1">
         <v>1</v>
@@ -1812,16 +1812,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
-        <v>30010</v>
+        <v>60006</v>
       </c>
       <c r="B70" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C70" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D70" s="1">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E70" s="1">
         <v>1</v>
@@ -1832,16 +1832,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
-        <v>30011</v>
+        <v>60007</v>
       </c>
       <c r="B71" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C71" s="1">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D71" s="1">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E71" s="1">
         <v>1</v>
@@ -1852,16 +1852,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
-        <v>30012</v>
+        <v>60008</v>
       </c>
       <c r="B72" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C72" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D72" s="1">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="E72" s="1">
         <v>1</v>
@@ -1872,16 +1872,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
-        <v>30013</v>
+        <v>60009</v>
       </c>
       <c r="B73" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C73" s="1">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D73" s="1">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="E73" s="1">
         <v>1</v>
@@ -1892,16 +1892,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
-        <v>30014</v>
+        <v>60010</v>
       </c>
       <c r="B74" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C74" s="1">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D74" s="1">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E74" s="1">
         <v>1</v>
@@ -1912,19 +1912,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
-        <v>30015</v>
+        <v>60011</v>
       </c>
       <c r="B75" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C75" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D75" s="1">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E75" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" s="1">
         <v>100</v>
@@ -1932,16 +1932,16 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
-        <v>30016</v>
+        <v>60012</v>
       </c>
       <c r="B76" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C76" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D76" s="1">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E76" s="1">
         <v>1</v>
@@ -1952,13 +1952,13 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
-        <v>30017</v>
+        <v>60013</v>
       </c>
       <c r="B77" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C77" s="1">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D77" s="1">
         <v>32</v>
@@ -1972,16 +1972,16 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
-        <v>30018</v>
+        <v>60014</v>
       </c>
       <c r="B78" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C78" s="1">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D78" s="1">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E78" s="1">
         <v>1</v>
@@ -1992,16 +1992,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
-        <v>30019</v>
+        <v>60015</v>
       </c>
       <c r="B79" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C79" s="1">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D79" s="1">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="E79" s="1">
         <v>1</v>
@@ -2012,16 +2012,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
-        <v>30020</v>
+        <v>60016</v>
       </c>
       <c r="B80" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C80" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D80" s="1">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E80" s="1">
         <v>1</v>
@@ -2032,16 +2032,16 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
-        <v>30021</v>
+        <v>60017</v>
       </c>
       <c r="B81" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C81" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D81" s="1">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="E81" s="1">
         <v>1</v>
@@ -2052,16 +2052,16 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
-        <v>30022</v>
+        <v>60018</v>
       </c>
       <c r="B82" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C82" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D82" s="1">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="E82" s="1">
         <v>1</v>
@@ -2072,16 +2072,16 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
-        <v>30023</v>
+        <v>60019</v>
       </c>
       <c r="B83" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C83" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D83" s="1">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="E83" s="1">
         <v>1</v>
@@ -2092,16 +2092,16 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
-        <v>30024</v>
+        <v>60020</v>
       </c>
       <c r="B84" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C84" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D84" s="1">
-        <v>22</v>
+        <v>-1</v>
       </c>
       <c r="E84" s="1">
         <v>1</v>
@@ -2112,19 +2112,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
-        <v>30025</v>
+        <v>70001</v>
       </c>
       <c r="B85" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C85" s="1">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D85" s="1">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E85" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="1">
         <v>100</v>
@@ -2132,16 +2132,16 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
-        <v>30026</v>
+        <v>70002</v>
       </c>
       <c r="B86" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C86" s="1">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="D86" s="1">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E86" s="1">
         <v>1</v>
@@ -2152,16 +2152,16 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
-        <v>30027</v>
+        <v>70003</v>
       </c>
       <c r="B87" s="1">
+        <v>7</v>
+      </c>
+      <c r="C87" s="1">
         <v>3</v>
       </c>
-      <c r="C87" s="1">
-        <v>27</v>
-      </c>
       <c r="D87" s="1">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="E87" s="1">
         <v>1</v>
@@ -2172,16 +2172,16 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
-        <v>30028</v>
+        <v>70004</v>
       </c>
       <c r="B88" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C88" s="1">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D88" s="1">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E88" s="1">
         <v>1</v>
@@ -2192,16 +2192,16 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
-        <v>30029</v>
+        <v>70005</v>
       </c>
       <c r="B89" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C89" s="1">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D89" s="1">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="E89" s="1">
         <v>1</v>
@@ -2212,16 +2212,16 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
-        <v>30030</v>
+        <v>70006</v>
       </c>
       <c r="B90" s="1">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C90" s="1">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="D90" s="1">
-        <v>-1</v>
+        <v>36</v>
       </c>
       <c r="E90" s="1">
         <v>1</v>
@@ -2232,19 +2232,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
-        <v>40001</v>
+        <v>70007</v>
       </c>
       <c r="B91" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C91" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D91" s="1">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E91" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="1">
         <v>100</v>
@@ -2252,16 +2252,16 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
-        <v>40002</v>
+        <v>70008</v>
       </c>
       <c r="B92" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C92" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D92" s="1">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E92" s="1">
         <v>1</v>
@@ -2272,16 +2272,16 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
-        <v>40003</v>
+        <v>70009</v>
       </c>
       <c r="B93" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C93" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D93" s="1">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="E93" s="1">
         <v>1</v>
@@ -2292,16 +2292,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
-        <v>40004</v>
+        <v>70010</v>
       </c>
       <c r="B94" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C94" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D94" s="1">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E94" s="1">
         <v>1</v>
@@ -2312,19 +2312,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
-        <v>40005</v>
+        <v>70011</v>
       </c>
       <c r="B95" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C95" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D95" s="1">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E95" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" s="1">
         <v>100</v>
@@ -2332,16 +2332,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
-        <v>40006</v>
+        <v>70012</v>
       </c>
       <c r="B96" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C96" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D96" s="1">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E96" s="1">
         <v>1</v>
@@ -2352,16 +2352,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
-        <v>40007</v>
+        <v>70013</v>
       </c>
       <c r="B97" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C97" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D97" s="1">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E97" s="1">
         <v>1</v>
@@ -2372,16 +2372,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
-        <v>40008</v>
+        <v>70014</v>
       </c>
       <c r="B98" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C98" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D98" s="1">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -2392,16 +2392,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
-        <v>40009</v>
+        <v>70015</v>
       </c>
       <c r="B99" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C99" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D99" s="1">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E99" s="1">
         <v>1</v>
@@ -2412,16 +2412,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
-        <v>40010</v>
+        <v>70016</v>
       </c>
       <c r="B100" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C100" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D100" s="1">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E100" s="1">
         <v>1</v>
@@ -2432,16 +2432,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
-        <v>40011</v>
+        <v>70017</v>
       </c>
       <c r="B101" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C101" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D101" s="1">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="E101" s="1">
         <v>1</v>
@@ -2452,16 +2452,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
-        <v>40012</v>
+        <v>70018</v>
       </c>
       <c r="B102" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C102" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D102" s="1">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="E102" s="1">
         <v>1</v>
@@ -2472,16 +2472,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
-        <v>40013</v>
+        <v>70019</v>
       </c>
       <c r="B103" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C103" s="1">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D103" s="1">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="E103" s="1">
         <v>1</v>
@@ -2492,16 +2492,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
-        <v>40014</v>
+        <v>70020</v>
       </c>
       <c r="B104" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C104" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D104" s="1">
-        <v>18</v>
+        <v>-1</v>
       </c>
       <c r="E104" s="1">
         <v>1</v>
@@ -2512,19 +2512,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
-        <v>40015</v>
+        <v>1000001</v>
       </c>
       <c r="B105" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C105" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D105" s="1">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E105" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="1">
         <v>100</v>
@@ -2532,16 +2532,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
-        <v>40016</v>
+        <v>1000002</v>
       </c>
       <c r="B106" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C106" s="1">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D106" s="1">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E106" s="1">
         <v>1</v>
@@ -2552,16 +2552,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
-        <v>40017</v>
+        <v>1000003</v>
       </c>
       <c r="B107" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C107" s="1">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D107" s="1">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E107" s="1">
         <v>1</v>
@@ -2572,16 +2572,16 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
-        <v>40018</v>
+        <v>1000004</v>
       </c>
       <c r="B108" s="1">
+        <v>100</v>
+      </c>
+      <c r="C108" s="1">
         <v>4</v>
       </c>
-      <c r="C108" s="1">
-        <v>18</v>
-      </c>
       <c r="D108" s="1">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E108" s="1">
         <v>1</v>
@@ -2592,16 +2592,16 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
-        <v>40019</v>
+        <v>1000005</v>
       </c>
       <c r="B109" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C109" s="1">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D109" s="1">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E109" s="1">
         <v>1</v>
@@ -2612,16 +2612,16 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
-        <v>40020</v>
+        <v>1000006</v>
       </c>
       <c r="B110" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C110" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D110" s="1">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E110" s="1">
         <v>1</v>
@@ -2632,16 +2632,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
-        <v>40021</v>
+        <v>1000007</v>
       </c>
       <c r="B111" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C111" s="1">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D111" s="1">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E111" s="1">
         <v>1</v>
@@ -2652,16 +2652,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
-        <v>40022</v>
+        <v>1000008</v>
       </c>
       <c r="B112" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C112" s="1">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D112" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E112" s="1">
         <v>1</v>
@@ -2672,16 +2672,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
-        <v>40023</v>
+        <v>1000009</v>
       </c>
       <c r="B113" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C113" s="1">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D113" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E113" s="1">
         <v>1</v>
@@ -2692,16 +2692,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
-        <v>40024</v>
+        <v>1000010</v>
       </c>
       <c r="B114" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C114" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D114" s="1">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="E114" s="1">
         <v>1</v>
@@ -2712,16 +2712,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
-        <v>40025</v>
+        <v>1000011</v>
       </c>
       <c r="B115" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C115" s="1">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D115" s="1">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E115" s="1">
         <v>1</v>
@@ -2732,16 +2732,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
-        <v>40026</v>
+        <v>1000012</v>
       </c>
       <c r="B116" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C116" s="1">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D116" s="1">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E116" s="1">
         <v>1</v>
@@ -2752,16 +2752,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
-        <v>40027</v>
+        <v>1000013</v>
       </c>
       <c r="B117" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C117" s="1">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D117" s="1">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E117" s="1">
         <v>1</v>
@@ -2772,16 +2772,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
-        <v>40028</v>
+        <v>1000014</v>
       </c>
       <c r="B118" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C118" s="1">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D118" s="1">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="E118" s="1">
         <v>1</v>
@@ -2792,16 +2792,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
-        <v>40029</v>
+        <v>1000015</v>
       </c>
       <c r="B119" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C119" s="1">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D119" s="1">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="E119" s="1">
         <v>1</v>
@@ -2812,16 +2812,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
-        <v>40030</v>
+        <v>1000016</v>
       </c>
       <c r="B120" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C120" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D120" s="1">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="E120" s="1">
         <v>1</v>
@@ -2832,16 +2832,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
-        <v>40031</v>
+        <v>1000017</v>
       </c>
       <c r="B121" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C121" s="1">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D121" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E121" s="1">
         <v>1</v>
@@ -2852,16 +2852,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
-        <v>40032</v>
+        <v>1000018</v>
       </c>
       <c r="B122" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C122" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D122" s="1">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E122" s="1">
         <v>1</v>
@@ -2872,16 +2872,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
-        <v>40033</v>
+        <v>1000019</v>
       </c>
       <c r="B123" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C123" s="1">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D123" s="1">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E123" s="1">
         <v>1</v>
@@ -2892,16 +2892,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
-        <v>40034</v>
+        <v>1000020</v>
       </c>
       <c r="B124" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C124" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D124" s="1">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E124" s="1">
         <v>1</v>
@@ -2912,16 +2912,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
-        <v>40035</v>
+        <v>1000021</v>
       </c>
       <c r="B125" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C125" s="1">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D125" s="1">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E125" s="1">
         <v>1</v>
@@ -2932,16 +2932,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
-        <v>40036</v>
+        <v>1000022</v>
       </c>
       <c r="B126" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C126" s="1">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D126" s="1">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="E126" s="1">
         <v>1</v>
@@ -2952,16 +2952,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
-        <v>40037</v>
+        <v>1000023</v>
       </c>
       <c r="B127" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C127" s="1">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D127" s="1">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="E127" s="1">
         <v>1</v>
@@ -2972,16 +2972,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
-        <v>40038</v>
+        <v>1000024</v>
       </c>
       <c r="B128" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C128" s="1">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D128" s="1">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E128" s="1">
         <v>1</v>
@@ -2992,16 +2992,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
-        <v>40039</v>
+        <v>1000025</v>
       </c>
       <c r="B129" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C129" s="1">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D129" s="1">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="E129" s="1">
         <v>1</v>
@@ -3012,16 +3012,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
-        <v>40040</v>
+        <v>1000026</v>
       </c>
       <c r="B130" s="1">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="C130" s="1">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D130" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E130" s="1">
         <v>1</v>
@@ -3032,19 +3032,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
-        <v>990001</v>
+        <v>1000027</v>
       </c>
       <c r="B131" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C131" s="1">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D131" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E131" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="1">
         <v>100</v>
@@ -3052,16 +3052,16 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
-        <v>990002</v>
+        <v>1000028</v>
       </c>
       <c r="B132" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C132" s="1">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D132" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E132" s="1">
         <v>1</v>
@@ -3072,16 +3072,16 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
-        <v>990003</v>
+        <v>1000029</v>
       </c>
       <c r="B133" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C133" s="1">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="D133" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E133" s="1">
         <v>1</v>
@@ -3092,16 +3092,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
-        <v>990004</v>
+        <v>1000030</v>
       </c>
       <c r="B134" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C134" s="1">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="D134" s="1">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E134" s="1">
         <v>1</v>
@@ -3112,16 +3112,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
-        <v>990005</v>
+        <v>1000031</v>
       </c>
       <c r="B135" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C135" s="1">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D135" s="1">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E135" s="1">
         <v>1</v>
@@ -3132,16 +3132,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
-        <v>990006</v>
+        <v>1000032</v>
       </c>
       <c r="B136" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C136" s="1">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D136" s="1">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E136" s="1">
         <v>1</v>
@@ -3152,16 +3152,16 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
-        <v>990007</v>
+        <v>1000033</v>
       </c>
       <c r="B137" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C137" s="1">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D137" s="1">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E137" s="1">
         <v>1</v>
@@ -3172,16 +3172,16 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
-        <v>990008</v>
+        <v>1000034</v>
       </c>
       <c r="B138" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C138" s="1">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="D138" s="1">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E138" s="1">
         <v>1</v>
@@ -3192,16 +3192,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
-        <v>990009</v>
+        <v>1000035</v>
       </c>
       <c r="B139" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C139" s="1">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="D139" s="1">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E139" s="1">
         <v>1</v>
@@ -3212,16 +3212,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
-        <v>990010</v>
+        <v>1000036</v>
       </c>
       <c r="B140" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C140" s="1">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D140" s="1">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E140" s="1">
         <v>1</v>
@@ -3232,19 +3232,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
-        <v>990011</v>
+        <v>1000037</v>
       </c>
       <c r="B141" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C141" s="1">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D141" s="1">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E141" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" s="1">
         <v>100</v>
@@ -3252,16 +3252,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
-        <v>990012</v>
+        <v>1000038</v>
       </c>
       <c r="B142" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C142" s="1">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D142" s="1">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E142" s="1">
         <v>1</v>
@@ -3272,16 +3272,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
-        <v>990013</v>
+        <v>1000039</v>
       </c>
       <c r="B143" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C143" s="1">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="D143" s="1">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E143" s="1">
         <v>1</v>
@@ -3292,16 +3292,16 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
-        <v>990014</v>
+        <v>1000040</v>
       </c>
       <c r="B144" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C144" s="1">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D144" s="1">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E144" s="1">
         <v>1</v>
@@ -3312,16 +3312,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
-        <v>990015</v>
+        <v>1000041</v>
       </c>
       <c r="B145" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C145" s="1">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D145" s="1">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E145" s="1">
         <v>1</v>
@@ -3332,16 +3332,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
-        <v>990016</v>
+        <v>1000042</v>
       </c>
       <c r="B146" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C146" s="1">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="D146" s="1">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E146" s="1">
         <v>1</v>
@@ -3352,16 +3352,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
-        <v>990017</v>
+        <v>1000043</v>
       </c>
       <c r="B147" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C147" s="1">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D147" s="1">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E147" s="1">
         <v>1</v>
@@ -3372,16 +3372,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
-        <v>990018</v>
+        <v>1000044</v>
       </c>
       <c r="B148" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C148" s="1">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D148" s="1">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E148" s="1">
         <v>1</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
-        <v>990019</v>
+        <v>1000045</v>
       </c>
       <c r="B149" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C149" s="1">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D149" s="1">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E149" s="1">
         <v>1</v>
@@ -3412,16 +3412,16 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
-        <v>990020</v>
+        <v>1000046</v>
       </c>
       <c r="B150" s="1">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C150" s="1">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="D150" s="1">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="E150" s="1">
         <v>1</v>
@@ -3432,19 +3432,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
-        <v>1000001</v>
+        <v>1000047</v>
       </c>
       <c r="B151" s="1">
         <v>100</v>
       </c>
       <c r="C151" s="1">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="D151" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E151" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" s="1">
         <v>100</v>
@@ -3452,16 +3452,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
-        <v>1000002</v>
+        <v>1000048</v>
       </c>
       <c r="B152" s="1">
         <v>100</v>
       </c>
       <c r="C152" s="1">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="D152" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E152" s="1">
         <v>1</v>
@@ -3472,16 +3472,16 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
-        <v>1000003</v>
+        <v>1000049</v>
       </c>
       <c r="B153" s="1">
         <v>100</v>
       </c>
       <c r="C153" s="1">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="D153" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E153" s="1">
         <v>1</v>
@@ -3492,16 +3492,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
-        <v>1000004</v>
+        <v>1000050</v>
       </c>
       <c r="B154" s="1">
         <v>100</v>
       </c>
       <c r="C154" s="1">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="D154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E154" s="1">
         <v>1</v>
@@ -3512,16 +3512,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
-        <v>1000005</v>
+        <v>1000051</v>
       </c>
       <c r="B155" s="1">
         <v>100</v>
       </c>
       <c r="C155" s="1">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="D155" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E155" s="1">
         <v>1</v>
@@ -3532,16 +3532,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
-        <v>1000006</v>
+        <v>1000052</v>
       </c>
       <c r="B156" s="1">
         <v>100</v>
       </c>
       <c r="C156" s="1">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="D156" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" s="1">
         <v>1</v>
@@ -3552,16 +3552,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
-        <v>1000007</v>
+        <v>1000053</v>
       </c>
       <c r="B157" s="1">
         <v>100</v>
       </c>
       <c r="C157" s="1">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="D157" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" s="1">
         <v>1</v>
@@ -3572,16 +3572,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
-        <v>1000008</v>
+        <v>1000054</v>
       </c>
       <c r="B158" s="1">
         <v>100</v>
       </c>
       <c r="C158" s="1">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D158" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E158" s="1">
         <v>1</v>
@@ -3592,16 +3592,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
-        <v>1000009</v>
+        <v>1000055</v>
       </c>
       <c r="B159" s="1">
         <v>100</v>
       </c>
       <c r="C159" s="1">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="D159" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E159" s="1">
         <v>1</v>
@@ -3612,16 +3612,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
-        <v>1000010</v>
+        <v>1000056</v>
       </c>
       <c r="B160" s="1">
         <v>100</v>
       </c>
       <c r="C160" s="1">
-        <v>10</v>
+        <v>56</v>
       </c>
       <c r="D160" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E160" s="1">
         <v>1</v>
@@ -3632,16 +3632,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
-        <v>1000011</v>
+        <v>1000057</v>
       </c>
       <c r="B161" s="1">
         <v>100</v>
       </c>
       <c r="C161" s="1">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="D161" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E161" s="1">
         <v>1</v>
@@ -3652,16 +3652,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
-        <v>1000012</v>
+        <v>1000058</v>
       </c>
       <c r="B162" s="1">
         <v>100</v>
       </c>
       <c r="C162" s="1">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="D162" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E162" s="1">
         <v>1</v>
@@ -3672,16 +3672,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
-        <v>1000013</v>
+        <v>1000059</v>
       </c>
       <c r="B163" s="1">
         <v>100</v>
       </c>
       <c r="C163" s="1">
-        <v>13</v>
+        <v>59</v>
       </c>
       <c r="D163" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" s="1">
         <v>1</v>
@@ -3692,16 +3692,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
-        <v>1000014</v>
+        <v>1000060</v>
       </c>
       <c r="B164" s="1">
         <v>100</v>
       </c>
       <c r="C164" s="1">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="D164" s="1">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E164" s="1">
         <v>1</v>
@@ -3712,19 +3712,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
-        <v>1000015</v>
+        <v>11010001</v>
       </c>
       <c r="B165" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C165" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D165" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E165" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F165" s="1">
         <v>100</v>
@@ -3732,16 +3732,16 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
-        <v>1000016</v>
+        <v>11010002</v>
       </c>
       <c r="B166" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C166" s="1">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D166" s="1">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E166" s="1">
         <v>1</v>
@@ -3752,16 +3752,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
-        <v>1000017</v>
+        <v>11010003</v>
       </c>
       <c r="B167" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C167" s="1">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D167" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E167" s="1">
         <v>1</v>
@@ -3772,16 +3772,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
-        <v>1000018</v>
+        <v>11010004</v>
       </c>
       <c r="B168" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C168" s="1">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D168" s="1">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E168" s="1">
         <v>1</v>
@@ -3792,16 +3792,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
-        <v>1000019</v>
+        <v>11010005</v>
       </c>
       <c r="B169" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C169" s="1">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="D169" s="1">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E169" s="1">
         <v>1</v>
@@ -3812,16 +3812,16 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
-        <v>1000020</v>
+        <v>11010006</v>
       </c>
       <c r="B170" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C170" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D170" s="1">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="E170" s="1">
         <v>1</v>
@@ -3832,16 +3832,16 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
-        <v>1000021</v>
+        <v>11010007</v>
       </c>
       <c r="B171" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C171" s="1">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D171" s="1">
-        <v>2</v>
+        <v>95</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -3852,16 +3852,16 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
-        <v>1000022</v>
+        <v>11010008</v>
       </c>
       <c r="B172" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C172" s="1">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D172" s="1">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
@@ -3872,16 +3872,16 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
-        <v>1000023</v>
+        <v>11010009</v>
       </c>
       <c r="B173" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C173" s="1">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D173" s="1">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
@@ -3892,16 +3892,16 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
-        <v>1000024</v>
+        <v>11010010</v>
       </c>
       <c r="B174" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C174" s="1">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D174" s="1">
-        <v>2</v>
+        <v>200</v>
       </c>
       <c r="E174" s="1">
         <v>1</v>
@@ -3912,16 +3912,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
-        <v>1000025</v>
+        <v>11010011</v>
       </c>
       <c r="B175" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C175" s="1">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D175" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E175" s="1">
         <v>1</v>
@@ -3932,16 +3932,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
-        <v>1000026</v>
+        <v>11010012</v>
       </c>
       <c r="B176" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C176" s="1">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D176" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E176" s="1">
         <v>1</v>
@@ -3952,16 +3952,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
-        <v>1000027</v>
+        <v>11010013</v>
       </c>
       <c r="B177" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C177" s="1">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D177" s="1">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E177" s="1">
         <v>1</v>
@@ -3972,16 +3972,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
-        <v>1000028</v>
+        <v>11010014</v>
       </c>
       <c r="B178" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C178" s="1">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D178" s="1">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
@@ -3992,16 +3992,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
-        <v>1000029</v>
+        <v>11010015</v>
       </c>
       <c r="B179" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C179" s="1">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D179" s="1">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
@@ -4012,16 +4012,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
-        <v>1000030</v>
+        <v>11010016</v>
       </c>
       <c r="B180" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C180" s="1">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D180" s="1">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="E180" s="1">
         <v>1</v>
@@ -4032,16 +4032,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
-        <v>1000031</v>
+        <v>11010017</v>
       </c>
       <c r="B181" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C181" s="1">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D181" s="1">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="E181" s="1">
         <v>1</v>
@@ -4052,16 +4052,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
-        <v>1000032</v>
+        <v>11010018</v>
       </c>
       <c r="B182" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C182" s="1">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D182" s="1">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E182" s="1">
         <v>1</v>
@@ -4072,16 +4072,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
-        <v>1000033</v>
+        <v>11010019</v>
       </c>
       <c r="B183" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C183" s="1">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D183" s="1">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="E183" s="1">
         <v>1</v>
@@ -4092,16 +4092,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
-        <v>1000034</v>
+        <v>11010020</v>
       </c>
       <c r="B184" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C184" s="1">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D184" s="1">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="E184" s="1">
         <v>1</v>
@@ -4112,16 +4112,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
-        <v>1000035</v>
+        <v>11010021</v>
       </c>
       <c r="B185" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C185" s="1">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D185" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E185" s="1">
         <v>1</v>
@@ -4132,16 +4132,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
-        <v>1000036</v>
+        <v>11010022</v>
       </c>
       <c r="B186" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C186" s="1">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D186" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E186" s="1">
         <v>1</v>
@@ -4152,16 +4152,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
-        <v>1000037</v>
+        <v>11010023</v>
       </c>
       <c r="B187" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C187" s="1">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D187" s="1">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E187" s="1">
         <v>1</v>
@@ -4172,16 +4172,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
-        <v>1000038</v>
+        <v>11010024</v>
       </c>
       <c r="B188" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C188" s="1">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D188" s="1">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E188" s="1">
         <v>1</v>
@@ -4192,16 +4192,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
-        <v>1000039</v>
+        <v>11010025</v>
       </c>
       <c r="B189" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C189" s="1">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D189" s="1">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E189" s="1">
         <v>1</v>
@@ -4212,16 +4212,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
-        <v>1000040</v>
+        <v>11010026</v>
       </c>
       <c r="B190" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C190" s="1">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D190" s="1">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="E190" s="1">
         <v>1</v>
@@ -4232,16 +4232,16 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
-        <v>1000041</v>
+        <v>11010027</v>
       </c>
       <c r="B191" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C191" s="1">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D191" s="1">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="E191" s="1">
         <v>1</v>
@@ -4252,16 +4252,16 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
-        <v>1000042</v>
+        <v>11010028</v>
       </c>
       <c r="B192" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C192" s="1">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D192" s="1">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E192" s="1">
         <v>1</v>
@@ -4272,16 +4272,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
-        <v>1000043</v>
+        <v>11010029</v>
       </c>
       <c r="B193" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C193" s="1">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D193" s="1">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="E193" s="1">
         <v>1</v>
@@ -4292,16 +4292,16 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
-        <v>1000044</v>
+        <v>11010030</v>
       </c>
       <c r="B194" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C194" s="1">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D194" s="1">
-        <v>2</v>
+        <v>108</v>
       </c>
       <c r="E194" s="1">
         <v>1</v>
@@ -4312,16 +4312,16 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
-        <v>1000045</v>
+        <v>11010031</v>
       </c>
       <c r="B195" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C195" s="1">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D195" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E195" s="1">
         <v>1</v>
@@ -4332,16 +4332,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
-        <v>1000046</v>
+        <v>11010032</v>
       </c>
       <c r="B196" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C196" s="1">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="D196" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E196" s="1">
         <v>1</v>
@@ -4352,16 +4352,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
-        <v>1000047</v>
+        <v>11010033</v>
       </c>
       <c r="B197" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C197" s="1">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="D197" s="1">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E197" s="1">
         <v>1</v>
@@ -4372,16 +4372,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
-        <v>1000048</v>
+        <v>11010034</v>
       </c>
       <c r="B198" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C198" s="1">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D198" s="1">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="E198" s="1">
         <v>1</v>
@@ -4392,16 +4392,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
-        <v>1000049</v>
+        <v>11010035</v>
       </c>
       <c r="B199" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C199" s="1">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D199" s="1">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="E199" s="1">
         <v>1</v>
@@ -4412,16 +4412,16 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
-        <v>1000050</v>
+        <v>11010036</v>
       </c>
       <c r="B200" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C200" s="1">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D200" s="1">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="E200" s="1">
         <v>1</v>
@@ -4432,16 +4432,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
-        <v>1000051</v>
+        <v>11010037</v>
       </c>
       <c r="B201" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C201" s="1">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D201" s="1">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="E201" s="1">
         <v>1</v>
@@ -4452,16 +4452,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
-        <v>1000052</v>
+        <v>11010038</v>
       </c>
       <c r="B202" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C202" s="1">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D202" s="1">
-        <v>2</v>
+        <v>85</v>
       </c>
       <c r="E202" s="1">
         <v>1</v>
@@ -4472,16 +4472,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
-        <v>1000053</v>
+        <v>11010039</v>
       </c>
       <c r="B203" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C203" s="1">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D203" s="1">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="E203" s="1">
         <v>1</v>
@@ -4492,16 +4492,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
-        <v>1000054</v>
+        <v>11010040</v>
       </c>
       <c r="B204" s="1">
-        <v>100</v>
+        <v>1101</v>
       </c>
       <c r="C204" s="1">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D204" s="1">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E204" s="1">
         <v>1</v>
@@ -4512,19 +4512,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
-        <v>1000055</v>
+        <v>11020001</v>
       </c>
       <c r="B205" s="1">
-        <v>100</v>
+        <v>1102</v>
       </c>
       <c r="C205" s="1">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="D205" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E205" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" s="1">
         <v>100</v>
@@ -4532,16 +4532,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
-        <v>1000056</v>
+        <v>11020002</v>
       </c>
       <c r="B206" s="1">
-        <v>100</v>
+        <v>1102</v>
       </c>
       <c r="C206" s="1">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="D206" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E206" s="1">
         <v>1</v>
@@ -4552,16 +4552,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
-        <v>1000057</v>
+        <v>11020003</v>
       </c>
       <c r="B207" s="1">
-        <v>100</v>
+        <v>1102</v>
       </c>
       <c r="C207" s="1">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="D207" s="1">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E207" s="1">
         <v>1</v>
@@ -4572,16 +4572,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
-        <v>1000058</v>
+        <v>11020004</v>
       </c>
       <c r="B208" s="1">
-        <v>100</v>
+        <v>1102</v>
       </c>
       <c r="C208" s="1">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="D208" s="1">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E208" s="1">
         <v>1</v>
@@ -4592,16 +4592,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
-        <v>1000059</v>
+        <v>11020005</v>
       </c>
       <c r="B209" s="1">
-        <v>100</v>
+        <v>1102</v>
       </c>
       <c r="C209" s="1">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="D209" s="1">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E209" s="1">
         <v>1</v>
@@ -4612,16 +4612,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
-        <v>1000060</v>
+        <v>11020006</v>
       </c>
       <c r="B210" s="1">
-        <v>100</v>
+        <v>1102</v>
       </c>
       <c r="C210" s="1">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="D210" s="1">
-        <v>-1</v>
+        <v>36</v>
       </c>
       <c r="E210" s="1">
         <v>1</v>
@@ -4632,19 +4632,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
-        <v>11010001</v>
+        <v>11020007</v>
       </c>
       <c r="B211" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C211" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D211" s="1">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="E211" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F211" s="1">
         <v>100</v>
@@ -4652,16 +4652,16 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
-        <v>11010002</v>
+        <v>11020008</v>
       </c>
       <c r="B212" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C212" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D212" s="1">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="E212" s="1">
         <v>1</v>
@@ -4672,16 +4672,16 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
-        <v>11010003</v>
+        <v>11020009</v>
       </c>
       <c r="B213" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C213" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D213" s="1">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="E213" s="1">
         <v>1</v>
@@ -4692,16 +4692,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
-        <v>11010004</v>
+        <v>11020010</v>
       </c>
       <c r="B214" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C214" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D214" s="1">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="E214" s="1">
         <v>1</v>
@@ -4712,16 +4712,16 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
-        <v>11010005</v>
+        <v>11020011</v>
       </c>
       <c r="B215" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C215" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D215" s="1">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E215" s="1">
         <v>1</v>
@@ -4732,16 +4732,16 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
-        <v>11010006</v>
+        <v>11020012</v>
       </c>
       <c r="B216" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C216" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D216" s="1">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="E216" s="1">
         <v>1</v>
@@ -4752,16 +4752,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
-        <v>11010007</v>
+        <v>11020013</v>
       </c>
       <c r="B217" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C217" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D217" s="1">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="E217" s="1">
         <v>1</v>
@@ -4772,16 +4772,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
-        <v>11010008</v>
+        <v>11020014</v>
       </c>
       <c r="B218" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C218" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D218" s="1">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="E218" s="1">
         <v>1</v>
@@ -4792,16 +4792,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
-        <v>11010009</v>
+        <v>11020015</v>
       </c>
       <c r="B219" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C219" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D219" s="1">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="E219" s="1">
         <v>1</v>
@@ -4812,16 +4812,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
-        <v>11010010</v>
+        <v>11020016</v>
       </c>
       <c r="B220" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C220" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D220" s="1">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="E220" s="1">
         <v>1</v>
@@ -4832,16 +4832,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
-        <v>11010011</v>
+        <v>11020017</v>
       </c>
       <c r="B221" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C221" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D221" s="1">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="E221" s="1">
         <v>1</v>
@@ -4852,16 +4852,16 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
-        <v>11010012</v>
+        <v>11020018</v>
       </c>
       <c r="B222" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C222" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D222" s="1">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="E222" s="1">
         <v>1</v>
@@ -4872,16 +4872,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
-        <v>11010013</v>
+        <v>11020019</v>
       </c>
       <c r="B223" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C223" s="1">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D223" s="1">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="E223" s="1">
         <v>1</v>
@@ -4892,16 +4892,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
-        <v>11010014</v>
+        <v>11020020</v>
       </c>
       <c r="B224" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C224" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D224" s="1">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="E224" s="1">
         <v>1</v>
@@ -4912,16 +4912,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
-        <v>11010015</v>
+        <v>11020021</v>
       </c>
       <c r="B225" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C225" s="1">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D225" s="1">
-        <v>31</v>
+        <v>-1</v>
       </c>
       <c r="E225" s="1">
         <v>1</v>
@@ -4932,16 +4932,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
-        <v>11010016</v>
+        <v>11020022</v>
       </c>
       <c r="B226" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C226" s="1">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D226" s="1">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="E226" s="1">
         <v>1</v>
@@ -4952,16 +4952,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
-        <v>11010017</v>
+        <v>11020023</v>
       </c>
       <c r="B227" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C227" s="1">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D227" s="1">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E227" s="1">
         <v>1</v>
@@ -4972,16 +4972,16 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
-        <v>11010018</v>
+        <v>11020024</v>
       </c>
       <c r="B228" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C228" s="1">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D228" s="1">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="E228" s="1">
         <v>1</v>
@@ -4992,16 +4992,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
-        <v>11010019</v>
+        <v>11020025</v>
       </c>
       <c r="B229" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C229" s="1">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D229" s="1">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="E229" s="1">
         <v>1</v>
@@ -5012,16 +5012,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
-        <v>11010020</v>
+        <v>11020026</v>
       </c>
       <c r="B230" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C230" s="1">
+        <v>26</v>
+      </c>
+      <c r="D230" s="1">
         <v>20</v>
-      </c>
-      <c r="D230" s="1">
-        <v>79</v>
       </c>
       <c r="E230" s="1">
         <v>1</v>
@@ -5032,13 +5032,13 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
-        <v>11010021</v>
+        <v>11020027</v>
       </c>
       <c r="B231" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C231" s="1">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D231" s="1">
         <v>20</v>
@@ -5052,16 +5052,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
-        <v>11010022</v>
+        <v>11020028</v>
       </c>
       <c r="B232" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C232" s="1">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D232" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E232" s="1">
         <v>1</v>
@@ -5072,16 +5072,16 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
-        <v>11010023</v>
+        <v>11020029</v>
       </c>
       <c r="B233" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C233" s="1">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D233" s="1">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E233" s="1">
         <v>1</v>
@@ -5092,941 +5092,21 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
-        <v>11010024</v>
+        <v>11020030</v>
       </c>
       <c r="B234" s="1">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C234" s="1">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D234" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E234" s="1">
         <v>1</v>
       </c>
       <c r="F234" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A235" s="1">
-        <v>11010025</v>
-      </c>
-      <c r="B235" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C235" s="1">
-        <v>25</v>
-      </c>
-      <c r="D235" s="1">
-        <v>56</v>
-      </c>
-      <c r="E235" s="1">
-        <v>1</v>
-      </c>
-      <c r="F235" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A236" s="1">
-        <v>11010026</v>
-      </c>
-      <c r="B236" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C236" s="1">
-        <v>26</v>
-      </c>
-      <c r="D236" s="1">
-        <v>74</v>
-      </c>
-      <c r="E236" s="1">
-        <v>1</v>
-      </c>
-      <c r="F236" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A237" s="1">
-        <v>11010027</v>
-      </c>
-      <c r="B237" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C237" s="1">
-        <v>27</v>
-      </c>
-      <c r="D237" s="1">
-        <v>78</v>
-      </c>
-      <c r="E237" s="1">
-        <v>1</v>
-      </c>
-      <c r="F237" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A238" s="1">
-        <v>11010028</v>
-      </c>
-      <c r="B238" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C238" s="1">
-        <v>28</v>
-      </c>
-      <c r="D238" s="1">
-        <v>85</v>
-      </c>
-      <c r="E238" s="1">
-        <v>1</v>
-      </c>
-      <c r="F238" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A239" s="1">
-        <v>11010029</v>
-      </c>
-      <c r="B239" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C239" s="1">
-        <v>29</v>
-      </c>
-      <c r="D239" s="1">
-        <v>96</v>
-      </c>
-      <c r="E239" s="1">
-        <v>1</v>
-      </c>
-      <c r="F239" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A240" s="1">
-        <v>11010030</v>
-      </c>
-      <c r="B240" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C240" s="1">
-        <v>30</v>
-      </c>
-      <c r="D240" s="1">
-        <v>96</v>
-      </c>
-      <c r="E240" s="1">
-        <v>1</v>
-      </c>
-      <c r="F240" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A241" s="1">
-        <v>11010031</v>
-      </c>
-      <c r="B241" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C241" s="1">
-        <v>31</v>
-      </c>
-      <c r="D241" s="1">
-        <v>20</v>
-      </c>
-      <c r="E241" s="1">
-        <v>1</v>
-      </c>
-      <c r="F241" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A242" s="1">
-        <v>11010032</v>
-      </c>
-      <c r="B242" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C242" s="1">
-        <v>32</v>
-      </c>
-      <c r="D242" s="1">
-        <v>24</v>
-      </c>
-      <c r="E242" s="1">
-        <v>1</v>
-      </c>
-      <c r="F242" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A243" s="1">
-        <v>11010033</v>
-      </c>
-      <c r="B243" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C243" s="1">
-        <v>33</v>
-      </c>
-      <c r="D243" s="1">
-        <v>31</v>
-      </c>
-      <c r="E243" s="1">
-        <v>1</v>
-      </c>
-      <c r="F243" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A244" s="1">
-        <v>11010034</v>
-      </c>
-      <c r="B244" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C244" s="1">
-        <v>34</v>
-      </c>
-      <c r="D244" s="1">
-        <v>40</v>
-      </c>
-      <c r="E244" s="1">
-        <v>1</v>
-      </c>
-      <c r="F244" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A245" s="1">
-        <v>11010035</v>
-      </c>
-      <c r="B245" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C245" s="1">
-        <v>35</v>
-      </c>
-      <c r="D245" s="1">
-        <v>56</v>
-      </c>
-      <c r="E245" s="1">
-        <v>1</v>
-      </c>
-      <c r="F245" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A246" s="1">
-        <v>11010036</v>
-      </c>
-      <c r="B246" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C246" s="1">
-        <v>36</v>
-      </c>
-      <c r="D246" s="1">
-        <v>74</v>
-      </c>
-      <c r="E246" s="1">
-        <v>1</v>
-      </c>
-      <c r="F246" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A247" s="1">
-        <v>11010037</v>
-      </c>
-      <c r="B247" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C247" s="1">
-        <v>37</v>
-      </c>
-      <c r="D247" s="1">
-        <v>78</v>
-      </c>
-      <c r="E247" s="1">
-        <v>1</v>
-      </c>
-      <c r="F247" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A248" s="1">
-        <v>11010038</v>
-      </c>
-      <c r="B248" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C248" s="1">
-        <v>38</v>
-      </c>
-      <c r="D248" s="1">
-        <v>85</v>
-      </c>
-      <c r="E248" s="1">
-        <v>1</v>
-      </c>
-      <c r="F248" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A249" s="1">
-        <v>11010039</v>
-      </c>
-      <c r="B249" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C249" s="1">
-        <v>39</v>
-      </c>
-      <c r="D249" s="1">
-        <v>96</v>
-      </c>
-      <c r="E249" s="1">
-        <v>1</v>
-      </c>
-      <c r="F249" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A250" s="1">
-        <v>11010040</v>
-      </c>
-      <c r="B250" s="1">
-        <v>1101</v>
-      </c>
-      <c r="C250" s="1">
-        <v>40</v>
-      </c>
-      <c r="D250" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E250" s="1">
-        <v>1</v>
-      </c>
-      <c r="F250" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A251" s="1">
-        <v>11020001</v>
-      </c>
-      <c r="B251" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C251" s="1">
-        <v>1</v>
-      </c>
-      <c r="D251" s="1">
-        <v>6</v>
-      </c>
-      <c r="E251" s="1">
-        <v>0</v>
-      </c>
-      <c r="F251" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A252" s="1">
-        <v>11020002</v>
-      </c>
-      <c r="B252" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C252" s="1">
-        <v>2</v>
-      </c>
-      <c r="D252" s="1">
-        <v>12</v>
-      </c>
-      <c r="E252" s="1">
-        <v>1</v>
-      </c>
-      <c r="F252" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A253" s="1">
-        <v>11020003</v>
-      </c>
-      <c r="B253" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C253" s="1">
-        <v>3</v>
-      </c>
-      <c r="D253" s="1">
-        <v>18</v>
-      </c>
-      <c r="E253" s="1">
-        <v>1</v>
-      </c>
-      <c r="F253" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A254" s="1">
-        <v>11020004</v>
-      </c>
-      <c r="B254" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C254" s="1">
-        <v>4</v>
-      </c>
-      <c r="D254" s="1">
-        <v>24</v>
-      </c>
-      <c r="E254" s="1">
-        <v>1</v>
-      </c>
-      <c r="F254" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A255" s="1">
-        <v>11020005</v>
-      </c>
-      <c r="B255" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C255" s="1">
-        <v>5</v>
-      </c>
-      <c r="D255" s="1">
-        <v>30</v>
-      </c>
-      <c r="E255" s="1">
-        <v>1</v>
-      </c>
-      <c r="F255" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A256" s="1">
-        <v>11020006</v>
-      </c>
-      <c r="B256" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C256" s="1">
-        <v>6</v>
-      </c>
-      <c r="D256" s="1">
-        <v>36</v>
-      </c>
-      <c r="E256" s="1">
-        <v>1</v>
-      </c>
-      <c r="F256" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A257" s="1">
-        <v>11020007</v>
-      </c>
-      <c r="B257" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C257" s="1">
-        <v>7</v>
-      </c>
-      <c r="D257" s="1">
-        <v>42</v>
-      </c>
-      <c r="E257" s="1">
-        <v>1</v>
-      </c>
-      <c r="F257" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A258" s="1">
-        <v>11020008</v>
-      </c>
-      <c r="B258" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C258" s="1">
-        <v>8</v>
-      </c>
-      <c r="D258" s="1">
-        <v>48</v>
-      </c>
-      <c r="E258" s="1">
-        <v>1</v>
-      </c>
-      <c r="F258" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A259" s="1">
-        <v>11020009</v>
-      </c>
-      <c r="B259" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C259" s="1">
-        <v>9</v>
-      </c>
-      <c r="D259" s="1">
-        <v>54</v>
-      </c>
-      <c r="E259" s="1">
-        <v>1</v>
-      </c>
-      <c r="F259" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A260" s="1">
-        <v>11020010</v>
-      </c>
-      <c r="B260" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C260" s="1">
-        <v>10</v>
-      </c>
-      <c r="D260" s="1">
-        <v>60</v>
-      </c>
-      <c r="E260" s="1">
-        <v>1</v>
-      </c>
-      <c r="F260" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A261" s="1">
-        <v>11020011</v>
-      </c>
-      <c r="B261" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C261" s="1">
-        <v>11</v>
-      </c>
-      <c r="D261" s="1">
-        <v>16</v>
-      </c>
-      <c r="E261" s="1">
-        <v>1</v>
-      </c>
-      <c r="F261" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A262" s="1">
-        <v>11020012</v>
-      </c>
-      <c r="B262" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C262" s="1">
-        <v>12</v>
-      </c>
-      <c r="D262" s="1">
-        <v>24</v>
-      </c>
-      <c r="E262" s="1">
-        <v>1</v>
-      </c>
-      <c r="F262" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A263" s="1">
-        <v>11020013</v>
-      </c>
-      <c r="B263" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C263" s="1">
-        <v>13</v>
-      </c>
-      <c r="D263" s="1">
-        <v>32</v>
-      </c>
-      <c r="E263" s="1">
-        <v>1</v>
-      </c>
-      <c r="F263" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A264" s="1">
-        <v>11020014</v>
-      </c>
-      <c r="B264" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C264" s="1">
-        <v>14</v>
-      </c>
-      <c r="D264" s="1">
-        <v>40</v>
-      </c>
-      <c r="E264" s="1">
-        <v>1</v>
-      </c>
-      <c r="F264" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A265" s="1">
-        <v>11020015</v>
-      </c>
-      <c r="B265" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C265" s="1">
-        <v>15</v>
-      </c>
-      <c r="D265" s="1">
-        <v>50</v>
-      </c>
-      <c r="E265" s="1">
-        <v>1</v>
-      </c>
-      <c r="F265" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A266" s="1">
-        <v>11020016</v>
-      </c>
-      <c r="B266" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C266" s="1">
-        <v>16</v>
-      </c>
-      <c r="D266" s="1">
-        <v>60</v>
-      </c>
-      <c r="E266" s="1">
-        <v>1</v>
-      </c>
-      <c r="F266" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A267" s="1">
-        <v>11020017</v>
-      </c>
-      <c r="B267" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C267" s="1">
-        <v>17</v>
-      </c>
-      <c r="D267" s="1">
-        <v>72</v>
-      </c>
-      <c r="E267" s="1">
-        <v>1</v>
-      </c>
-      <c r="F267" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A268" s="1">
-        <v>11020018</v>
-      </c>
-      <c r="B268" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C268" s="1">
-        <v>18</v>
-      </c>
-      <c r="D268" s="1">
-        <v>84</v>
-      </c>
-      <c r="E268" s="1">
-        <v>1</v>
-      </c>
-      <c r="F268" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A269" s="1">
-        <v>11020019</v>
-      </c>
-      <c r="B269" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C269" s="1">
-        <v>19</v>
-      </c>
-      <c r="D269" s="1">
-        <v>96</v>
-      </c>
-      <c r="E269" s="1">
-        <v>1</v>
-      </c>
-      <c r="F269" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A270" s="1">
-        <v>11020020</v>
-      </c>
-      <c r="B270" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C270" s="1">
-        <v>20</v>
-      </c>
-      <c r="D270" s="1">
-        <v>108</v>
-      </c>
-      <c r="E270" s="1">
-        <v>1</v>
-      </c>
-      <c r="F270" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A271" s="1">
-        <v>11020021</v>
-      </c>
-      <c r="B271" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C271" s="1">
-        <v>21</v>
-      </c>
-      <c r="D271" s="1">
-        <v>-1</v>
-      </c>
-      <c r="E271" s="1">
-        <v>1</v>
-      </c>
-      <c r="F271" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A272" s="1">
-        <v>11020022</v>
-      </c>
-      <c r="B272" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C272" s="1">
-        <v>22</v>
-      </c>
-      <c r="D272" s="1">
-        <v>20</v>
-      </c>
-      <c r="E272" s="1">
-        <v>1</v>
-      </c>
-      <c r="F272" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A273" s="1">
-        <v>11020023</v>
-      </c>
-      <c r="B273" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C273" s="1">
-        <v>23</v>
-      </c>
-      <c r="D273" s="1">
-        <v>20</v>
-      </c>
-      <c r="E273" s="1">
-        <v>1</v>
-      </c>
-      <c r="F273" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A274" s="1">
-        <v>11020024</v>
-      </c>
-      <c r="B274" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C274" s="1">
-        <v>24</v>
-      </c>
-      <c r="D274" s="1">
-        <v>20</v>
-      </c>
-      <c r="E274" s="1">
-        <v>1</v>
-      </c>
-      <c r="F274" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A275" s="1">
-        <v>11020025</v>
-      </c>
-      <c r="B275" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C275" s="1">
-        <v>25</v>
-      </c>
-      <c r="D275" s="1">
-        <v>20</v>
-      </c>
-      <c r="E275" s="1">
-        <v>1</v>
-      </c>
-      <c r="F275" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A276" s="1">
-        <v>11020026</v>
-      </c>
-      <c r="B276" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C276" s="1">
-        <v>26</v>
-      </c>
-      <c r="D276" s="1">
-        <v>20</v>
-      </c>
-      <c r="E276" s="1">
-        <v>1</v>
-      </c>
-      <c r="F276" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A277" s="1">
-        <v>11020027</v>
-      </c>
-      <c r="B277" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C277" s="1">
-        <v>27</v>
-      </c>
-      <c r="D277" s="1">
-        <v>20</v>
-      </c>
-      <c r="E277" s="1">
-        <v>1</v>
-      </c>
-      <c r="F277" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A278" s="1">
-        <v>11020028</v>
-      </c>
-      <c r="B278" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C278" s="1">
-        <v>28</v>
-      </c>
-      <c r="D278" s="1">
-        <v>20</v>
-      </c>
-      <c r="E278" s="1">
-        <v>1</v>
-      </c>
-      <c r="F278" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A279" s="1">
-        <v>11020029</v>
-      </c>
-      <c r="B279" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C279" s="1">
-        <v>29</v>
-      </c>
-      <c r="D279" s="1">
-        <v>20</v>
-      </c>
-      <c r="E279" s="1">
-        <v>1</v>
-      </c>
-      <c r="F279" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A280" s="1">
-        <v>11020030</v>
-      </c>
-      <c r="B280" s="1">
-        <v>1102</v>
-      </c>
-      <c r="C280" s="1">
-        <v>30</v>
-      </c>
-      <c r="D280" s="1">
-        <v>20</v>
-      </c>
-      <c r="E280" s="1">
-        <v>1</v>
-      </c>
-      <c r="F280" s="1">
         <v>100</v>
       </c>
     </row>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9529FE09-DC37-44E7-BFB5-37770D0E5062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -20,9 +14,6 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,6 +21,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,85 +33,68 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>paipaiworld_config</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>INT_K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>INT_S_C</t>
+  </si>
+  <si>
+    <t>INT_S</t>
   </si>
   <si>
     <t>order</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energy_id</t>
+  </si>
+  <si>
+    <t>energy_level</t>
+  </si>
+  <si>
+    <t>max_energy</t>
+  </si>
+  <si>
+    <t>energy_select</t>
+  </si>
+  <si>
+    <t>energy_item_select</t>
+  </si>
+  <si>
+    <t>序号（能力id*10000+等级</t>
+  </si>
+  <si>
+    <t>能力id</t>
   </si>
   <si>
     <t>等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max_energy</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>升到下一级需要的能量点数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_select</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>提升到当前等级时可以选择能力的次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S_C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_level</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序号（能力id*10000+等级</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>能力id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>energy_item_select</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>提升到当前等级时，可以使用道具触发的选择能力次数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>INT_S</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -126,19 +102,355 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -146,25 +458,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -213,7 +811,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -248,7 +846,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -422,95 +1020,90 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F234"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="25.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="35.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="25.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="50.5" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>10001</v>
       </c>
@@ -530,7 +1123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>10002</v>
       </c>
@@ -550,7 +1143,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>10003</v>
       </c>
@@ -570,7 +1163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>10004</v>
       </c>
@@ -590,7 +1183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>10005</v>
       </c>
@@ -610,7 +1203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>10006</v>
       </c>
@@ -630,7 +1223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>10007</v>
       </c>
@@ -650,7 +1243,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>10008</v>
       </c>
@@ -670,7 +1263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>10009</v>
       </c>
@@ -690,7 +1283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>10010</v>
       </c>
@@ -710,7 +1303,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>20001</v>
       </c>
@@ -730,7 +1323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>20002</v>
       </c>
@@ -750,7 +1343,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>20003</v>
       </c>
@@ -770,7 +1363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>20004</v>
       </c>
@@ -790,7 +1383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>20005</v>
       </c>
@@ -810,7 +1403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>20006</v>
       </c>
@@ -830,7 +1423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>20007</v>
       </c>
@@ -850,7 +1443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>20008</v>
       </c>
@@ -870,7 +1463,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>20009</v>
       </c>
@@ -890,7 +1483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>20010</v>
       </c>
@@ -910,7 +1503,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>30001</v>
       </c>
@@ -930,7 +1523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>30002</v>
       </c>
@@ -950,7 +1543,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>30003</v>
       </c>
@@ -970,7 +1563,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>30004</v>
       </c>
@@ -990,7 +1583,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>30005</v>
       </c>
@@ -1010,7 +1603,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>30006</v>
       </c>
@@ -1030,7 +1623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>30007</v>
       </c>
@@ -1050,7 +1643,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>30008</v>
       </c>
@@ -1070,7 +1663,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>30009</v>
       </c>
@@ -1090,7 +1683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:6">
       <c r="A34" s="1">
         <v>30010</v>
       </c>
@@ -1110,7 +1703,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:6">
       <c r="A35" s="1">
         <v>40001</v>
       </c>
@@ -1130,7 +1723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6">
       <c r="A36" s="1">
         <v>40002</v>
       </c>
@@ -1150,7 +1743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6">
       <c r="A37" s="1">
         <v>40003</v>
       </c>
@@ -1170,7 +1763,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:6">
       <c r="A38" s="1">
         <v>40004</v>
       </c>
@@ -1190,7 +1783,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="A39" s="1">
         <v>40005</v>
       </c>
@@ -1210,7 +1803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6">
       <c r="A40" s="1">
         <v>40006</v>
       </c>
@@ -1230,7 +1823,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="A41" s="1">
         <v>40007</v>
       </c>
@@ -1250,7 +1843,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="A42" s="1">
         <v>40008</v>
       </c>
@@ -1270,7 +1863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6">
       <c r="A43" s="1">
         <v>40009</v>
       </c>
@@ -1290,7 +1883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="A44" s="1">
         <v>40010</v>
       </c>
@@ -1310,7 +1903,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="A45" s="1">
         <v>50001</v>
       </c>
@@ -1330,7 +1923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:6">
       <c r="A46" s="1">
         <v>50002</v>
       </c>
@@ -1350,7 +1943,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="A47" s="1">
         <v>50003</v>
       </c>
@@ -1370,7 +1963,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="A48" s="1">
         <v>50004</v>
       </c>
@@ -1390,7 +1983,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:6">
       <c r="A49" s="1">
         <v>50005</v>
       </c>
@@ -1410,7 +2003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:6">
       <c r="A50" s="1">
         <v>50006</v>
       </c>
@@ -1430,7 +2023,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:6">
       <c r="A51" s="1">
         <v>50007</v>
       </c>
@@ -1450,7 +2043,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:6">
       <c r="A52" s="1">
         <v>50008</v>
       </c>
@@ -1470,7 +2063,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:6">
       <c r="A53" s="1">
         <v>50009</v>
       </c>
@@ -1490,7 +2083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:6">
       <c r="A54" s="1">
         <v>50010</v>
       </c>
@@ -1510,7 +2103,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:6">
       <c r="A55" s="1">
         <v>50011</v>
       </c>
@@ -1530,7 +2123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:6">
       <c r="A56" s="1">
         <v>50012</v>
       </c>
@@ -1550,7 +2143,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:6">
       <c r="A57" s="1">
         <v>50013</v>
       </c>
@@ -1570,7 +2163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:6">
       <c r="A58" s="1">
         <v>50014</v>
       </c>
@@ -1590,7 +2183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:6">
       <c r="A59" s="1">
         <v>50015</v>
       </c>
@@ -1610,7 +2203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:6">
       <c r="A60" s="1">
         <v>50016</v>
       </c>
@@ -1630,7 +2223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:6">
       <c r="A61" s="1">
         <v>50017</v>
       </c>
@@ -1650,7 +2243,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:6">
       <c r="A62" s="1">
         <v>50018</v>
       </c>
@@ -1670,7 +2263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:6">
       <c r="A63" s="1">
         <v>50019</v>
       </c>
@@ -1690,7 +2283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:6">
       <c r="A64" s="1">
         <v>50020</v>
       </c>
@@ -1710,7 +2303,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="A65" s="1">
         <v>60001</v>
       </c>
@@ -1730,7 +2323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="A66" s="1">
         <v>60002</v>
       </c>
@@ -1750,7 +2343,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="A67" s="1">
         <v>60003</v>
       </c>
@@ -1770,7 +2363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="A68" s="1">
         <v>60004</v>
       </c>
@@ -1790,7 +2383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="A69" s="1">
         <v>60005</v>
       </c>
@@ -1810,7 +2403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="A70" s="1">
         <v>60006</v>
       </c>
@@ -1830,7 +2423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:6">
       <c r="A71" s="1">
         <v>60007</v>
       </c>
@@ -1850,7 +2443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="1">
         <v>60008</v>
       </c>
@@ -1870,7 +2463,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="1">
         <v>60009</v>
       </c>
@@ -1890,7 +2483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="A74" s="1">
         <v>60010</v>
       </c>
@@ -1910,7 +2503,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="1">
         <v>60011</v>
       </c>
@@ -1930,7 +2523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="1">
         <v>60012</v>
       </c>
@@ -1950,7 +2543,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="1">
         <v>60013</v>
       </c>
@@ -1970,7 +2563,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="A78" s="1">
         <v>60014</v>
       </c>
@@ -1990,7 +2583,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="1">
         <v>60015</v>
       </c>
@@ -2010,7 +2603,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="1">
         <v>60016</v>
       </c>
@@ -2030,7 +2623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="1">
         <v>60017</v>
       </c>
@@ -2050,7 +2643,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="1">
         <v>60018</v>
       </c>
@@ -2070,7 +2663,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="1">
         <v>60019</v>
       </c>
@@ -2090,7 +2683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="1">
         <v>60020</v>
       </c>
@@ -2110,7 +2703,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="1">
         <v>70001</v>
       </c>
@@ -2130,7 +2723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="1">
         <v>70002</v>
       </c>
@@ -2150,7 +2743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="1">
         <v>70003</v>
       </c>
@@ -2170,7 +2763,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="1">
         <v>70004</v>
       </c>
@@ -2190,7 +2783,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="1">
         <v>70005</v>
       </c>
@@ -2210,7 +2803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="1">
         <v>70006</v>
       </c>
@@ -2230,7 +2823,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="1">
         <v>70007</v>
       </c>
@@ -2250,7 +2843,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="1">
         <v>70008</v>
       </c>
@@ -2270,7 +2863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="A93" s="1">
         <v>70009</v>
       </c>
@@ -2290,7 +2883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="A94" s="1">
         <v>70010</v>
       </c>
@@ -2310,7 +2903,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="1">
         <v>70011</v>
       </c>
@@ -2330,7 +2923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="1">
         <v>70012</v>
       </c>
@@ -2350,7 +2943,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:6">
       <c r="A97" s="1">
         <v>70013</v>
       </c>
@@ -2370,7 +2963,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:6">
       <c r="A98" s="1">
         <v>70014</v>
       </c>
@@ -2390,7 +2983,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:6">
       <c r="A99" s="1">
         <v>70015</v>
       </c>
@@ -2410,7 +3003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:6">
       <c r="A100" s="1">
         <v>70016</v>
       </c>
@@ -2430,7 +3023,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:6">
       <c r="A101" s="1">
         <v>70017</v>
       </c>
@@ -2450,7 +3043,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:6">
       <c r="A102" s="1">
         <v>70018</v>
       </c>
@@ -2470,7 +3063,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:6">
       <c r="A103" s="1">
         <v>70019</v>
       </c>
@@ -2490,7 +3083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:6">
       <c r="A104" s="1">
         <v>70020</v>
       </c>
@@ -2510,7 +3103,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:6">
       <c r="A105" s="1">
         <v>1000001</v>
       </c>
@@ -2530,7 +3123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:6">
       <c r="A106" s="1">
         <v>1000002</v>
       </c>
@@ -2550,7 +3143,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:6">
       <c r="A107" s="1">
         <v>1000003</v>
       </c>
@@ -2570,7 +3163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:6">
       <c r="A108" s="1">
         <v>1000004</v>
       </c>
@@ -2590,7 +3183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:6">
       <c r="A109" s="1">
         <v>1000005</v>
       </c>
@@ -2610,7 +3203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:6">
       <c r="A110" s="1">
         <v>1000006</v>
       </c>
@@ -2630,7 +3223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:6">
       <c r="A111" s="1">
         <v>1000007</v>
       </c>
@@ -2650,7 +3243,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:6">
       <c r="A112" s="1">
         <v>1000008</v>
       </c>
@@ -2670,7 +3263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="A113" s="1">
         <v>1000009</v>
       </c>
@@ -2690,7 +3283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="A114" s="1">
         <v>1000010</v>
       </c>
@@ -2710,7 +3303,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:6">
       <c r="A115" s="1">
         <v>1000011</v>
       </c>
@@ -2730,7 +3323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:6">
       <c r="A116" s="1">
         <v>1000012</v>
       </c>
@@ -2750,7 +3343,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:6">
       <c r="A117" s="1">
         <v>1000013</v>
       </c>
@@ -2770,7 +3363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6">
       <c r="A118" s="1">
         <v>1000014</v>
       </c>
@@ -2790,7 +3383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="A119" s="1">
         <v>1000015</v>
       </c>
@@ -2810,7 +3403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:6">
       <c r="A120" s="1">
         <v>1000016</v>
       </c>
@@ -2830,7 +3423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="A121" s="1">
         <v>1000017</v>
       </c>
@@ -2850,7 +3443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="A122" s="1">
         <v>1000018</v>
       </c>
@@ -2870,7 +3463,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="A123" s="1">
         <v>1000019</v>
       </c>
@@ -2890,7 +3483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="A124" s="1">
         <v>1000020</v>
       </c>
@@ -2910,7 +3503,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="A125" s="1">
         <v>1000021</v>
       </c>
@@ -2930,7 +3523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="A126" s="1">
         <v>1000022</v>
       </c>
@@ -2950,7 +3543,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="A127" s="1">
         <v>1000023</v>
       </c>
@@ -2970,7 +3563,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="A128" s="1">
         <v>1000024</v>
       </c>
@@ -2990,7 +3583,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="A129" s="1">
         <v>1000025</v>
       </c>
@@ -3010,7 +3603,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="A130" s="1">
         <v>1000026</v>
       </c>
@@ -3030,7 +3623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:6">
       <c r="A131" s="1">
         <v>1000027</v>
       </c>
@@ -3050,7 +3643,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="A132" s="1">
         <v>1000028</v>
       </c>
@@ -3070,7 +3663,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="A133" s="1">
         <v>1000029</v>
       </c>
@@ -3090,7 +3683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6">
       <c r="A134" s="1">
         <v>1000030</v>
       </c>
@@ -3110,7 +3703,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="A135" s="1">
         <v>1000031</v>
       </c>
@@ -3130,7 +3723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="A136" s="1">
         <v>1000032</v>
       </c>
@@ -3150,7 +3743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="A137" s="1">
         <v>1000033</v>
       </c>
@@ -3170,7 +3763,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="A138" s="1">
         <v>1000034</v>
       </c>
@@ -3190,7 +3783,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:6">
       <c r="A139" s="1">
         <v>1000035</v>
       </c>
@@ -3210,7 +3803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="A140" s="1">
         <v>1000036</v>
       </c>
@@ -3230,7 +3823,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="A141" s="1">
         <v>1000037</v>
       </c>
@@ -3250,7 +3843,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="A142" s="1">
         <v>1000038</v>
       </c>
@@ -3270,7 +3863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="A143" s="1">
         <v>1000039</v>
       </c>
@@ -3290,7 +3883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="A144" s="1">
         <v>1000040</v>
       </c>
@@ -3310,7 +3903,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="A145" s="1">
         <v>1000041</v>
       </c>
@@ -3330,7 +3923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:6">
       <c r="A146" s="1">
         <v>1000042</v>
       </c>
@@ -3350,7 +3943,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:6">
       <c r="A147" s="1">
         <v>1000043</v>
       </c>
@@ -3370,7 +3963,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:6">
       <c r="A148" s="1">
         <v>1000044</v>
       </c>
@@ -3390,7 +3983,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:6">
       <c r="A149" s="1">
         <v>1000045</v>
       </c>
@@ -3410,7 +4003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:6">
       <c r="A150" s="1">
         <v>1000046</v>
       </c>
@@ -3430,7 +4023,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:6">
       <c r="A151" s="1">
         <v>1000047</v>
       </c>
@@ -3450,7 +4043,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="A152" s="1">
         <v>1000048</v>
       </c>
@@ -3470,7 +4063,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="A153" s="1">
         <v>1000049</v>
       </c>
@@ -3490,7 +4083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="A154" s="1">
         <v>1000050</v>
       </c>
@@ -3510,7 +4103,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="A155" s="1">
         <v>1000051</v>
       </c>
@@ -3530,7 +4123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:6">
       <c r="A156" s="1">
         <v>1000052</v>
       </c>
@@ -3550,7 +4143,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="A157" s="1">
         <v>1000053</v>
       </c>
@@ -3570,7 +4163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:6">
       <c r="A158" s="1">
         <v>1000054</v>
       </c>
@@ -3590,7 +4183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:6">
       <c r="A159" s="1">
         <v>1000055</v>
       </c>
@@ -3610,7 +4203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:6">
       <c r="A160" s="1">
         <v>1000056</v>
       </c>
@@ -3630,7 +4223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="A161" s="1">
         <v>1000057</v>
       </c>
@@ -3650,7 +4243,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="A162" s="1">
         <v>1000058</v>
       </c>
@@ -3670,7 +4263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:6">
       <c r="A163" s="1">
         <v>1000059</v>
       </c>
@@ -3690,7 +4283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:6">
       <c r="A164" s="1">
         <v>1000060</v>
       </c>
@@ -3710,7 +4303,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="A165" s="1">
         <v>11010001</v>
       </c>
@@ -3730,7 +4323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:6">
       <c r="A166" s="1">
         <v>11010002</v>
       </c>
@@ -3741,7 +4334,7 @@
         <v>2</v>
       </c>
       <c r="D166" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E166" s="1">
         <v>1</v>
@@ -3750,7 +4343,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:6">
       <c r="A167" s="1">
         <v>11010003</v>
       </c>
@@ -3761,7 +4354,7 @@
         <v>3</v>
       </c>
       <c r="D167" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E167" s="1">
         <v>1</v>
@@ -3770,7 +4363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:6">
       <c r="A168" s="1">
         <v>11010004</v>
       </c>
@@ -3781,7 +4374,7 @@
         <v>4</v>
       </c>
       <c r="D168" s="1">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E168" s="1">
         <v>1</v>
@@ -3790,7 +4383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="A169" s="1">
         <v>11010005</v>
       </c>
@@ -3801,7 +4394,7 @@
         <v>5</v>
       </c>
       <c r="D169" s="1">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="E169" s="1">
         <v>1</v>
@@ -3810,7 +4403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="A170" s="1">
         <v>11010006</v>
       </c>
@@ -3821,7 +4414,7 @@
         <v>6</v>
       </c>
       <c r="D170" s="1">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="E170" s="1">
         <v>1</v>
@@ -3830,7 +4423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:6">
       <c r="A171" s="1">
         <v>11010007</v>
       </c>
@@ -3841,7 +4434,7 @@
         <v>7</v>
       </c>
       <c r="D171" s="1">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -3850,7 +4443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:6">
       <c r="A172" s="1">
         <v>11010008</v>
       </c>
@@ -3861,7 +4454,7 @@
         <v>8</v>
       </c>
       <c r="D172" s="1">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
@@ -3870,7 +4463,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:6">
       <c r="A173" s="1">
         <v>11010009</v>
       </c>
@@ -3881,7 +4474,7 @@
         <v>9</v>
       </c>
       <c r="D173" s="1">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
@@ -3890,7 +4483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="A174" s="1">
         <v>11010010</v>
       </c>
@@ -3901,7 +4494,7 @@
         <v>10</v>
       </c>
       <c r="D174" s="1">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="E174" s="1">
         <v>1</v>
@@ -3910,7 +4503,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:6">
       <c r="A175" s="1">
         <v>11010011</v>
       </c>
@@ -3921,7 +4514,7 @@
         <v>11</v>
       </c>
       <c r="D175" s="1">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="E175" s="1">
         <v>1</v>
@@ -3930,7 +4523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="A176" s="1">
         <v>11010012</v>
       </c>
@@ -3941,7 +4534,7 @@
         <v>12</v>
       </c>
       <c r="D176" s="1">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="E176" s="1">
         <v>1</v>
@@ -3950,7 +4543,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:6">
       <c r="A177" s="1">
         <v>11010013</v>
       </c>
@@ -3961,7 +4554,7 @@
         <v>13</v>
       </c>
       <c r="D177" s="1">
-        <v>31</v>
+        <v>155</v>
       </c>
       <c r="E177" s="1">
         <v>1</v>
@@ -3970,7 +4563,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:6">
       <c r="A178" s="1">
         <v>11010014</v>
       </c>
@@ -3981,7 +4574,7 @@
         <v>14</v>
       </c>
       <c r="D178" s="1">
-        <v>40</v>
+        <v>170</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
@@ -3990,7 +4583,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:6">
       <c r="A179" s="1">
         <v>11010015</v>
       </c>
@@ -4001,7 +4594,7 @@
         <v>15</v>
       </c>
       <c r="D179" s="1">
-        <v>56</v>
+        <v>185</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
@@ -4010,7 +4603,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:6">
       <c r="A180" s="1">
         <v>11010016</v>
       </c>
@@ -4021,7 +4614,7 @@
         <v>16</v>
       </c>
       <c r="D180" s="1">
-        <v>74</v>
+        <v>200</v>
       </c>
       <c r="E180" s="1">
         <v>1</v>
@@ -4030,7 +4623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:6">
       <c r="A181" s="1">
         <v>11010017</v>
       </c>
@@ -4041,7 +4634,7 @@
         <v>17</v>
       </c>
       <c r="D181" s="1">
-        <v>78</v>
+        <v>215</v>
       </c>
       <c r="E181" s="1">
         <v>1</v>
@@ -4050,7 +4643,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="A182" s="1">
         <v>11010018</v>
       </c>
@@ -4061,7 +4654,7 @@
         <v>18</v>
       </c>
       <c r="D182" s="1">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="E182" s="1">
         <v>1</v>
@@ -4070,7 +4663,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="A183" s="1">
         <v>11010019</v>
       </c>
@@ -4081,7 +4674,7 @@
         <v>19</v>
       </c>
       <c r="D183" s="1">
-        <v>96</v>
+        <v>245</v>
       </c>
       <c r="E183" s="1">
         <v>1</v>
@@ -4090,7 +4683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="A184" s="1">
         <v>11010020</v>
       </c>
@@ -4101,7 +4694,7 @@
         <v>20</v>
       </c>
       <c r="D184" s="1">
-        <v>108</v>
+        <v>260</v>
       </c>
       <c r="E184" s="1">
         <v>1</v>
@@ -4110,7 +4703,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="A185" s="1">
         <v>11010021</v>
       </c>
@@ -4130,7 +4723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:6">
       <c r="A186" s="1">
         <v>11010022</v>
       </c>
@@ -4150,7 +4743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="A187" s="1">
         <v>11010023</v>
       </c>
@@ -4170,7 +4763,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:6">
       <c r="A188" s="1">
         <v>11010024</v>
       </c>
@@ -4190,7 +4783,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:6">
       <c r="A189" s="1">
         <v>11010025</v>
       </c>
@@ -4210,7 +4803,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:6">
       <c r="A190" s="1">
         <v>11010026</v>
       </c>
@@ -4230,7 +4823,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:6">
       <c r="A191" s="1">
         <v>11010027</v>
       </c>
@@ -4250,7 +4843,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:6">
       <c r="A192" s="1">
         <v>11010028</v>
       </c>
@@ -4270,7 +4863,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:6">
       <c r="A193" s="1">
         <v>11010029</v>
       </c>
@@ -4290,7 +4883,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:6">
       <c r="A194" s="1">
         <v>11010030</v>
       </c>
@@ -4310,7 +4903,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:6">
       <c r="A195" s="1">
         <v>11010031</v>
       </c>
@@ -4330,7 +4923,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:6">
       <c r="A196" s="1">
         <v>11010032</v>
       </c>
@@ -4350,7 +4943,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:6">
       <c r="A197" s="1">
         <v>11010033</v>
       </c>
@@ -4370,7 +4963,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:6">
       <c r="A198" s="1">
         <v>11010034</v>
       </c>
@@ -4390,7 +4983,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:6">
       <c r="A199" s="1">
         <v>11010035</v>
       </c>
@@ -4410,7 +5003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:6">
       <c r="A200" s="1">
         <v>11010036</v>
       </c>
@@ -4430,7 +5023,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:6">
       <c r="A201" s="1">
         <v>11010037</v>
       </c>
@@ -4450,7 +5043,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:6">
       <c r="A202" s="1">
         <v>11010038</v>
       </c>
@@ -4470,7 +5063,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:6">
       <c r="A203" s="1">
         <v>11010039</v>
       </c>
@@ -4490,7 +5083,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:6">
       <c r="A204" s="1">
         <v>11010040</v>
       </c>
@@ -4510,7 +5103,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:6">
       <c r="A205" s="1">
         <v>11020001</v>
       </c>
@@ -4530,7 +5123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:6">
       <c r="A206" s="1">
         <v>11020002</v>
       </c>
@@ -4550,7 +5143,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:6">
       <c r="A207" s="1">
         <v>11020003</v>
       </c>
@@ -4570,7 +5163,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:6">
       <c r="A208" s="1">
         <v>11020004</v>
       </c>
@@ -4590,7 +5183,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:6">
       <c r="A209" s="1">
         <v>11020005</v>
       </c>
@@ -4610,7 +5203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:6">
       <c r="A210" s="1">
         <v>11020006</v>
       </c>
@@ -4630,7 +5223,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:6">
       <c r="A211" s="1">
         <v>11020007</v>
       </c>
@@ -4650,7 +5243,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:6">
       <c r="A212" s="1">
         <v>11020008</v>
       </c>
@@ -4670,7 +5263,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:6">
       <c r="A213" s="1">
         <v>11020009</v>
       </c>
@@ -4690,7 +5283,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:6">
       <c r="A214" s="1">
         <v>11020010</v>
       </c>
@@ -4710,7 +5303,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:6">
       <c r="A215" s="1">
         <v>11020011</v>
       </c>
@@ -4730,7 +5323,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:6">
       <c r="A216" s="1">
         <v>11020012</v>
       </c>
@@ -4750,7 +5343,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:6">
       <c r="A217" s="1">
         <v>11020013</v>
       </c>
@@ -4770,7 +5363,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:6">
       <c r="A218" s="1">
         <v>11020014</v>
       </c>
@@ -4790,7 +5383,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:6">
       <c r="A219" s="1">
         <v>11020015</v>
       </c>
@@ -4810,7 +5403,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:6">
       <c r="A220" s="1">
         <v>11020016</v>
       </c>
@@ -4830,7 +5423,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:6">
       <c r="A221" s="1">
         <v>11020017</v>
       </c>
@@ -4850,7 +5443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:6">
       <c r="A222" s="1">
         <v>11020018</v>
       </c>
@@ -4870,7 +5463,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:6">
       <c r="A223" s="1">
         <v>11020019</v>
       </c>
@@ -4890,7 +5483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:6">
       <c r="A224" s="1">
         <v>11020020</v>
       </c>
@@ -4910,7 +5503,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:6">
       <c r="A225" s="1">
         <v>11020021</v>
       </c>
@@ -4930,7 +5523,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:6">
       <c r="A226" s="1">
         <v>11020022</v>
       </c>
@@ -4950,7 +5543,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:6">
       <c r="A227" s="1">
         <v>11020023</v>
       </c>
@@ -4970,7 +5563,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:6">
       <c r="A228" s="1">
         <v>11020024</v>
       </c>
@@ -4990,7 +5583,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:6">
       <c r="A229" s="1">
         <v>11020025</v>
       </c>
@@ -5010,7 +5603,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:6">
       <c r="A230" s="1">
         <v>11020026</v>
       </c>
@@ -5030,7 +5623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:6">
       <c r="A231" s="1">
         <v>11020027</v>
       </c>
@@ -5050,7 +5643,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:6">
       <c r="A232" s="1">
         <v>11020028</v>
       </c>
@@ -5070,7 +5663,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:6">
       <c r="A233" s="1">
         <v>11020029</v>
       </c>
@@ -5090,7 +5683,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:6">
       <c r="A234" s="1">
         <v>11020030</v>
       </c>
@@ -5111,7 +5704,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -90,7 +90,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,13 +103,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -559,28 +552,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -589,118 +585,115 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4314,7 +4307,7 @@
         <v>1</v>
       </c>
       <c r="D165" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E165" s="1">
         <v>0</v>
@@ -4334,7 +4327,7 @@
         <v>2</v>
       </c>
       <c r="D166" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E166" s="1">
         <v>1</v>
@@ -4354,7 +4347,7 @@
         <v>3</v>
       </c>
       <c r="D167" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E167" s="1">
         <v>1</v>
@@ -4374,7 +4367,7 @@
         <v>4</v>
       </c>
       <c r="D168" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E168" s="1">
         <v>1</v>
@@ -4394,7 +4387,7 @@
         <v>5</v>
       </c>
       <c r="D169" s="1">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E169" s="1">
         <v>1</v>
@@ -4414,7 +4407,7 @@
         <v>6</v>
       </c>
       <c r="D170" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E170" s="1">
         <v>1</v>
@@ -4434,7 +4427,7 @@
         <v>7</v>
       </c>
       <c r="D171" s="1">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="E171" s="1">
         <v>1</v>
@@ -4454,7 +4447,7 @@
         <v>8</v>
       </c>
       <c r="D172" s="1">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="E172" s="1">
         <v>1</v>
@@ -4474,7 +4467,7 @@
         <v>9</v>
       </c>
       <c r="D173" s="1">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="E173" s="1">
         <v>1</v>
@@ -4494,7 +4487,7 @@
         <v>10</v>
       </c>
       <c r="D174" s="1">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="E174" s="1">
         <v>1</v>
@@ -4514,7 +4507,7 @@
         <v>11</v>
       </c>
       <c r="D175" s="1">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="E175" s="1">
         <v>1</v>
@@ -4534,7 +4527,7 @@
         <v>12</v>
       </c>
       <c r="D176" s="1">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="E176" s="1">
         <v>1</v>
@@ -4554,7 +4547,7 @@
         <v>13</v>
       </c>
       <c r="D177" s="1">
-        <v>155</v>
+        <v>50</v>
       </c>
       <c r="E177" s="1">
         <v>1</v>
@@ -4574,7 +4567,7 @@
         <v>14</v>
       </c>
       <c r="D178" s="1">
-        <v>170</v>
+        <v>55</v>
       </c>
       <c r="E178" s="1">
         <v>1</v>
@@ -4594,7 +4587,7 @@
         <v>15</v>
       </c>
       <c r="D179" s="1">
-        <v>185</v>
+        <v>60</v>
       </c>
       <c r="E179" s="1">
         <v>1</v>
@@ -4614,7 +4607,7 @@
         <v>16</v>
       </c>
       <c r="D180" s="1">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="E180" s="1">
         <v>1</v>
@@ -4634,7 +4627,7 @@
         <v>17</v>
       </c>
       <c r="D181" s="1">
-        <v>215</v>
+        <v>70</v>
       </c>
       <c r="E181" s="1">
         <v>1</v>
@@ -4654,7 +4647,7 @@
         <v>18</v>
       </c>
       <c r="D182" s="1">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="E182" s="1">
         <v>1</v>
@@ -4674,7 +4667,7 @@
         <v>19</v>
       </c>
       <c r="D183" s="1">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="E183" s="1">
         <v>1</v>
@@ -4694,7 +4687,7 @@
         <v>20</v>
       </c>
       <c r="D184" s="1">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="E184" s="1">
         <v>1</v>
@@ -4714,7 +4707,7 @@
         <v>21</v>
       </c>
       <c r="D185" s="1">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E185" s="1">
         <v>1</v>

--- a/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_energy_level_v8【迷宫-能力等级】.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7232379E-23D9-40D1-BA20-7060D54F8292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_energy_level_v8" sheetId="1" r:id="rId1"/>
@@ -21,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -83,14 +87,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,348 +100,26 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -451,311 +127,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1013,14 +403,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:F234"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F244"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="25.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="1" customWidth="1"/>
@@ -1031,12 +421,12 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1056,7 +446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1076,7 +466,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1096,7 +486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>10001</v>
       </c>
@@ -1116,7 +506,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>10002</v>
       </c>
@@ -1136,7 +526,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>10003</v>
       </c>
@@ -1156,7 +546,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>10004</v>
       </c>
@@ -1176,7 +566,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>10005</v>
       </c>
@@ -1196,7 +586,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>10006</v>
       </c>
@@ -1216,7 +606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>10007</v>
       </c>
@@ -1236,7 +626,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>10008</v>
       </c>
@@ -1256,7 +646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>10009</v>
       </c>
@@ -1276,7 +666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>10010</v>
       </c>
@@ -1296,7 +686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>20001</v>
       </c>
@@ -1316,7 +706,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>20002</v>
       </c>
@@ -1336,7 +726,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>20003</v>
       </c>
@@ -1356,7 +746,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>20004</v>
       </c>
@@ -1376,7 +766,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>20005</v>
       </c>
@@ -1396,7 +786,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>20006</v>
       </c>
@@ -1416,7 +806,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>20007</v>
       </c>
@@ -1436,7 +826,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>20008</v>
       </c>
@@ -1456,7 +846,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>20009</v>
       </c>
@@ -1476,7 +866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>20010</v>
       </c>
@@ -1496,7 +886,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>30001</v>
       </c>
@@ -1516,7 +906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>30002</v>
       </c>
@@ -1536,7 +926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>30003</v>
       </c>
@@ -1556,7 +946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>30004</v>
       </c>
@@ -1576,7 +966,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>30005</v>
       </c>
@@ -1596,7 +986,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>30006</v>
       </c>
@@ -1616,7 +1006,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>30007</v>
       </c>
@@ -1636,7 +1026,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>30008</v>
       </c>
@@ -1656,7 +1046,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
         <v>30009</v>
       </c>
@@ -1676,7 +1066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A34" s="1">
         <v>30010</v>
       </c>
@@ -1696,7 +1086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A35" s="1">
         <v>40001</v>
       </c>
@@ -1716,7 +1106,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
         <v>40002</v>
       </c>
@@ -1736,7 +1126,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
         <v>40003</v>
       </c>
@@ -1756,7 +1146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
         <v>40004</v>
       </c>
@@ -1776,7 +1166,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
         <v>40005</v>
       </c>
@@ -1796,7 +1186,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
         <v>40006</v>
       </c>
@@ -1816,7 +1206,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>40007</v>
       </c>
@@ -1836,7 +1226,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>40008</v>
       </c>
@@ -1856,7 +1246,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>40009</v>
       </c>
@@ -1876,7 +1266,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
         <v>40010</v>
       </c>
@@ -1896,7 +1286,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>50001</v>
       </c>
@@ -1916,7 +1306,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>50002</v>
       </c>
@@ -1936,7 +1326,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>50003</v>
       </c>
@@ -1956,7 +1346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>50004</v>
       </c>
@@ -1976,7 +1366,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>50005</v>
       </c>
@@ -1996,7 +1386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>50006</v>
       </c>
@@ -2016,7 +1406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>50007</v>
       </c>
@@ -2036,7 +1426,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:6">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>50008</v>
       </c>
@@ -2056,7 +1446,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:6">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>50009</v>
       </c>
@@ -2076,7 +1466,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>50010</v>
       </c>
@@ -2096,7 +1486,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>50011</v>
       </c>
@@ -2116,7 +1506,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:6">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>50012</v>
       </c>
@@ -2136,7 +1526,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>50013</v>
       </c>
@@ -2156,7 +1546,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A58" s="1">
         <v>50014</v>
       </c>
@@ -2176,7 +1566,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A59" s="1">
         <v>50015</v>
       </c>
@@ -2196,7 +1586,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:6">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A60" s="1">
         <v>50016</v>
       </c>
@@ -2216,7 +1606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:6">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A61" s="1">
         <v>50017</v>
       </c>
@@ -2236,7 +1626,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="1:6">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>50018</v>
       </c>
@@ -2256,7 +1646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:6">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>50019</v>
       </c>
@@ -2276,7 +1666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:6">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A64" s="1">
         <v>50020</v>
       </c>
@@ -2296,7 +1686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A65" s="1">
         <v>60001</v>
       </c>
@@ -2316,7 +1706,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A66" s="1">
         <v>60002</v>
       </c>
@@ -2336,7 +1726,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A67" s="1">
         <v>60003</v>
       </c>
@@ -2356,7 +1746,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A68" s="1">
         <v>60004</v>
       </c>
@@ -2376,7 +1766,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A69" s="1">
         <v>60005</v>
       </c>
@@ -2396,7 +1786,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A70" s="1">
         <v>60006</v>
       </c>
@@ -2416,7 +1806,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:6">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A71" s="1">
         <v>60007</v>
       </c>
@@ -2436,7 +1826,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="1">
         <v>60008</v>
       </c>
@@ -2456,7 +1846,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="1">
         <v>60009</v>
       </c>
@@ -2476,7 +1866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="1">
         <v>60010</v>
       </c>
@@ -2496,7 +1886,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="1">
         <v>60011</v>
       </c>
@@ -2516,7 +1906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="1">
         <v>60012</v>
       </c>
@@ -2536,7 +1926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="1">
         <v>60013</v>
       </c>
@@ -2556,7 +1946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="1">
         <v>60014</v>
       </c>
@@ -2576,7 +1966,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="1">
         <v>60015</v>
       </c>
@@ -2596,7 +1986,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="1">
         <v>60016</v>
       </c>
@@ -2616,7 +2006,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="1">
         <v>60017</v>
       </c>
@@ -2636,7 +2026,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="1">
         <v>60018</v>
       </c>
@@ -2656,7 +2046,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="1">
         <v>60019</v>
       </c>
@@ -2676,7 +2066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="1">
         <v>60020</v>
       </c>
@@ -2696,7 +2086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="1">
         <v>70001</v>
       </c>
@@ -2716,7 +2106,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="1">
         <v>70002</v>
       </c>
@@ -2736,7 +2126,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="1">
         <v>70003</v>
       </c>
@@ -2756,7 +2146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="1">
         <v>70004</v>
       </c>
@@ -2776,7 +2166,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="1">
         <v>70005</v>
       </c>
@@ -2796,7 +2186,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="1">
         <v>70006</v>
       </c>
@@ -2816,7 +2206,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="1">
         <v>70007</v>
       </c>
@@ -2836,7 +2226,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="1">
         <v>70008</v>
       </c>
@@ -2856,7 +2246,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A93" s="1">
         <v>70009</v>
       </c>
@@ -2876,7 +2266,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A94" s="1">
         <v>70010</v>
       </c>
@@ -2896,7 +2286,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="1">
         <v>70011</v>
       </c>
@@ -2916,7 +2306,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="1">
         <v>70012</v>
       </c>
@@ -2936,7 +2326,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A97" s="1">
         <v>70013</v>
       </c>
@@ -2956,7 +2346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A98" s="1">
         <v>70014</v>
       </c>
@@ -2976,7 +2366,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:6">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A99" s="1">
         <v>70015</v>
       </c>
@@ -2996,7 +2386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A100" s="1">
         <v>70016</v>
       </c>
@@ -3016,7 +2406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A101" s="1">
         <v>70017</v>
       </c>
@@ -3036,7 +2426,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A102" s="1">
         <v>70018</v>
       </c>
@@ -3056,7 +2446,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A103" s="1">
         <v>70019</v>
       </c>
@@ -3076,7 +2466,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A104" s="1">
         <v>70020</v>
       </c>
@@ -3096,7 +2486,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A105" s="1">
         <v>1000001</v>
       </c>
@@ -3116,7 +2506,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A106" s="1">
         <v>1000002</v>
       </c>
@@ -3136,7 +2526,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A107" s="1">
         <v>1000003</v>
       </c>
@@ -3156,7 +2546,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="108" spans="1:6">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A108" s="1">
         <v>1000004</v>
       </c>
@@ -3176,7 +2566,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A109" s="1">
         <v>1000005</v>
       </c>
@@ -3196,7 +2586,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A110" s="1">
         <v>1000006</v>
       </c>
@@ -3216,7 +2606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A111" s="1">
         <v>1000007</v>
       </c>
@@ -3236,7 +2626,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A112" s="1">
         <v>1000008</v>
       </c>
@@ -3256,7 +2646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A113" s="1">
         <v>1000009</v>
       </c>
@@ -3276,7 +2666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A114" s="1">
         <v>1000010</v>
       </c>
@@ -3296,7 +2686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A115" s="1">
         <v>1000011</v>
       </c>
@@ -3316,7 +2706,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A116" s="1">
         <v>1000012</v>
       </c>
@@ -3336,7 +2726,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A117" s="1">
         <v>1000013</v>
       </c>
@@ -3356,7 +2746,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A118" s="1">
         <v>1000014</v>
       </c>
@@ -3376,7 +2766,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A119" s="1">
         <v>1000015</v>
       </c>
@@ -3396,7 +2786,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A120" s="1">
         <v>1000016</v>
       </c>
@@ -3416,7 +2806,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A121" s="1">
         <v>1000017</v>
       </c>
@@ -3436,7 +2826,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A122" s="1">
         <v>1000018</v>
       </c>
@@ -3456,7 +2846,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="123" spans="1:6">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A123" s="1">
         <v>1000019</v>
       </c>
@@ -3476,7 +2866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A124" s="1">
         <v>1000020</v>
       </c>
@@ -3496,7 +2886,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A125" s="1">
         <v>1000021</v>
       </c>
@@ -3516,7 +2906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A126" s="1">
         <v>1000022</v>
       </c>
@@ -3536,7 +2926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A127" s="1">
         <v>1000023</v>
       </c>
@@ -3556,7 +2946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A128" s="1">
         <v>1000024</v>
       </c>
@@ -3576,7 +2966,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A129" s="1">
         <v>1000025</v>
       </c>
@@ -3596,7 +2986,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A130" s="1">
         <v>1000026</v>
       </c>
@@ -3616,7 +3006,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:6">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A131" s="1">
         <v>1000027</v>
       </c>
@@ -3636,7 +3026,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A132" s="1">
         <v>1000028</v>
       </c>
@@ -3656,7 +3046,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="133" spans="1:6">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A133" s="1">
         <v>1000029</v>
       </c>
@@ -3676,7 +3066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="134" spans="1:6">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A134" s="1">
         <v>1000030</v>
       </c>
@@ -3696,7 +3086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A135" s="1">
         <v>1000031</v>
       </c>
@@ -3716,7 +3106,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A136" s="1">
         <v>1000032</v>
       </c>
@@ -3736,7 +3126,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="137" spans="1:6">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A137" s="1">
         <v>1000033</v>
       </c>
@@ -3756,7 +3146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A138" s="1">
         <v>1000034</v>
       </c>
@@ -3776,7 +3166,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A139" s="1">
         <v>1000035</v>
       </c>
@@ -3796,7 +3186,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A140" s="1">
         <v>1000036</v>
       </c>
@@ -3816,7 +3206,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A141" s="1">
         <v>1000037</v>
       </c>
@@ -3836,7 +3226,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A142" s="1">
         <v>1000038</v>
       </c>
@@ -3856,7 +3246,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A143" s="1">
         <v>1000039</v>
       </c>
@@ -3876,7 +3266,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A144" s="1">
         <v>1000040</v>
       </c>
@@ -3896,7 +3286,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A145" s="1">
         <v>1000041</v>
       </c>
@@ -3916,7 +3306,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="146" spans="1:6">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A146" s="1">
         <v>1000042</v>
       </c>
@@ -3936,7 +3326,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:6">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A147" s="1">
         <v>1000043</v>
       </c>
@@ -3956,7 +3346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="148" spans="1:6">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A148" s="1">
         <v>1000044</v>
       </c>
@@ -3976,7 +3366,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="149" spans="1:6">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A149" s="1">
         <v>1000045</v>
       </c>
@@ -3996,7 +3386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:6">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A150" s="1">
         <v>1000046</v>
       </c>
@@ -4016,7 +3406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="151" spans="1:6">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A151" s="1">
         <v>1000047</v>
       </c>
@@ -4036,7 +3426,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A152" s="1">
         <v>1000048</v>
       </c>
@@ -4056,7 +3446,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A153" s="1">
         <v>1000049</v>
       </c>
@@ -4076,7 +3466,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A154" s="1">
         <v>1000050</v>
       </c>
@@ -4096,7 +3486,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A155" s="1">
         <v>1000051</v>
       </c>
@@ -4116,7 +3506,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="156" spans="1:6">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A156" s="1">
         <v>1000052</v>
       </c>
@@ -4136,7 +3526,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A157" s="1">
         <v>1000053</v>
       </c>
@@ -4156,7 +3546,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="158" spans="1:6">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A158" s="1">
         <v>1000054</v>
       </c>
@@ -4176,7 +3566,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="159" spans="1:6">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A159" s="1">
         <v>1000055</v>
       </c>
@@ -4196,7 +3586,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A160" s="1">
         <v>1000056</v>
       </c>
@@ -4216,7 +3606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A161" s="1">
         <v>1000057</v>
       </c>
@@ -4236,7 +3626,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A162" s="1">
         <v>1000058</v>
       </c>
@@ -4256,7 +3646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A163" s="1">
         <v>1000059</v>
       </c>
@@ -4276,7 +3666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="164" spans="1:6">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A164" s="1">
         <v>1000060</v>
       </c>
@@ -4296,7 +3686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A165" s="1">
         <v>11010001</v>
       </c>
@@ -4316,7 +3706,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A166" s="1">
         <v>11010002</v>
       </c>
@@ -4336,7 +3726,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A167" s="1">
         <v>11010003</v>
       </c>
@@ -4356,7 +3746,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A168" s="1">
         <v>11010004</v>
       </c>
@@ -4376,7 +3766,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A169" s="1">
         <v>11010005</v>
       </c>
@@ -4396,7 +3786,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A170" s="1">
         <v>11010006</v>
       </c>
@@ -4416,7 +3806,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A171" s="1">
         <v>11010007</v>
       </c>
@@ -4436,7 +3826,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A172" s="1">
         <v>11010008</v>
       </c>
@@ -4456,7 +3846,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A173" s="1">
         <v>11010009</v>
       </c>
@@ -4476,7 +3866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A174" s="1">
         <v>11010010</v>
       </c>
@@ -4496,7 +3886,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A175" s="1">
         <v>11010011</v>
       </c>
@@ -4516,7 +3906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A176" s="1">
         <v>11010012</v>
       </c>
@@ -4536,7 +3926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A177" s="1">
         <v>11010013</v>
       </c>
@@ -4556,7 +3946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A178" s="1">
         <v>11010014</v>
       </c>
@@ -4576,7 +3966,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A179" s="1">
         <v>11010015</v>
       </c>
@@ -4596,7 +3986,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A180" s="1">
         <v>11010016</v>
       </c>
@@ -4616,7 +4006,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A181" s="1">
         <v>11010017</v>
       </c>
@@ -4636,7 +4026,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A182" s="1">
         <v>11010018</v>
       </c>
@@ -4656,7 +4046,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A183" s="1">
         <v>11010019</v>
       </c>
@@ -4676,7 +4066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A184" s="1">
         <v>11010020</v>
       </c>
@@ -4696,7 +4086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A185" s="1">
         <v>11010021</v>
       </c>
@@ -4716,7 +4106,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A186" s="1">
         <v>11010022</v>
       </c>
@@ -4736,7 +4126,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A187" s="1">
         <v>11010023</v>
       </c>
@@ -4756,7 +4146,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A188" s="1">
         <v>11010024</v>
       </c>
@@ -4776,7 +4166,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A189" s="1">
         <v>11010025</v>
       </c>
@@ -4796,7 +4186,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A190" s="1">
         <v>11010026</v>
       </c>
@@ -4816,7 +4206,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A191" s="1">
         <v>11010027</v>
       </c>
@@ -4836,7 +4226,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A192" s="1">
         <v>11010028</v>
       </c>
@@ -4856,7 +4246,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A193" s="1">
         <v>11010029</v>
       </c>
@@ -4876,7 +4266,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A194" s="1">
         <v>11010030</v>
       </c>
@@ -4896,7 +4286,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A195" s="1">
         <v>11010031</v>
       </c>
@@ -4916,7 +4306,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A196" s="1">
         <v>11010032</v>
       </c>
@@ -4936,7 +4326,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A197" s="1">
         <v>11010033</v>
       </c>
@@ -4956,7 +4346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A198" s="1">
         <v>11010034</v>
       </c>
@@ -4976,7 +4366,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A199" s="1">
         <v>11010035</v>
       </c>
@@ -4996,7 +4386,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A200" s="1">
         <v>11010036</v>
       </c>
@@ -5016,7 +4406,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A201" s="1">
         <v>11010037</v>
       </c>
@@ -5036,7 +4426,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="1:6">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A202" s="1">
         <v>11010038</v>
       </c>
@@ -5056,7 +4446,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:6">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A203" s="1">
         <v>11010039</v>
       </c>
@@ -5076,7 +4466,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="204" spans="1:6">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A204" s="1">
         <v>11010040</v>
       </c>
@@ -5096,7 +4486,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="205" spans="1:6">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A205" s="1">
         <v>11020001</v>
       </c>
@@ -5116,7 +4506,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="206" spans="1:6">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A206" s="1">
         <v>11020002</v>
       </c>
@@ -5136,7 +4526,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="207" spans="1:6">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A207" s="1">
         <v>11020003</v>
       </c>
@@ -5156,7 +4546,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="208" spans="1:6">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A208" s="1">
         <v>11020004</v>
       </c>
@@ -5176,7 +4566,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="209" spans="1:6">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A209" s="1">
         <v>11020005</v>
       </c>
@@ -5196,7 +4586,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="210" spans="1:6">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A210" s="1">
         <v>11020006</v>
       </c>
@@ -5216,7 +4606,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="211" spans="1:6">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A211" s="1">
         <v>11020007</v>
       </c>
@@ -5236,7 +4626,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="212" spans="1:6">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A212" s="1">
         <v>11020008</v>
       </c>
@@ -5256,7 +4646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="213" spans="1:6">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A213" s="1">
         <v>11020009</v>
       </c>
@@ -5276,7 +4666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="1:6">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A214" s="1">
         <v>11020010</v>
       </c>
@@ -5296,7 +4686,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:6">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A215" s="1">
         <v>11020011</v>
       </c>
@@ -5316,7 +4706,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A216" s="1">
         <v>11020012</v>
       </c>
@@ -5336,7 +4726,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A217" s="1">
         <v>11020013</v>
       </c>
@@ -5356,7 +4746,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A218" s="1">
         <v>11020014</v>
       </c>
@@ -5376,7 +4766,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="219" spans="1:6">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A219" s="1">
         <v>11020015</v>
       </c>
@@ -5396,7 +4786,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A220" s="1">
         <v>11020016</v>
       </c>
@@ -5416,7 +4806,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:6">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A221" s="1">
         <v>11020017</v>
       </c>
@@ -5436,7 +4826,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A222" s="1">
         <v>11020018</v>
       </c>
@@ -5456,7 +4846,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="223" spans="1:6">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A223" s="1">
         <v>11020019</v>
       </c>
@@ -5476,7 +4866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="224" spans="1:6">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A224" s="1">
         <v>11020020</v>
       </c>
@@ -5496,7 +4886,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="225" spans="1:6">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A225" s="1">
         <v>11020021</v>
       </c>
@@ -5516,7 +4906,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="226" spans="1:6">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A226" s="1">
         <v>11020022</v>
       </c>
@@ -5536,7 +4926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="227" spans="1:6">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A227" s="1">
         <v>11020023</v>
       </c>
@@ -5556,7 +4946,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="228" spans="1:6">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A228" s="1">
         <v>11020024</v>
       </c>
@@ -5576,7 +4966,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="229" spans="1:6">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A229" s="1">
         <v>11020025</v>
       </c>
@@ -5596,7 +4986,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="230" spans="1:6">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A230" s="1">
         <v>11020026</v>
       </c>
@@ -5616,7 +5006,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="231" spans="1:6">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A231" s="1">
         <v>11020027</v>
       </c>
@@ -5636,7 +5026,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="232" spans="1:6">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A232" s="1">
         <v>11020028</v>
       </c>
@@ -5656,7 +5046,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="233" spans="1:6">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A233" s="1">
         <v>11020029</v>
       </c>
@@ -5676,7 +5066,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="234" spans="1:6">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A234" s="1">
         <v>11020030</v>
       </c>
@@ -5696,8 +5086,208 @@
         <v>100</v>
       </c>
     </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A235" s="1">
+        <v>11030001</v>
+      </c>
+      <c r="B235" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C235" s="1">
+        <v>1</v>
+      </c>
+      <c r="D235" s="1">
+        <v>6</v>
+      </c>
+      <c r="E235" s="1">
+        <v>0</v>
+      </c>
+      <c r="F235" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A236" s="1">
+        <v>11030002</v>
+      </c>
+      <c r="B236" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C236" s="1">
+        <v>2</v>
+      </c>
+      <c r="D236" s="1">
+        <v>12</v>
+      </c>
+      <c r="E236" s="1">
+        <v>1</v>
+      </c>
+      <c r="F236" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A237" s="1">
+        <v>11030003</v>
+      </c>
+      <c r="B237" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C237" s="1">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1">
+        <v>18</v>
+      </c>
+      <c r="E237" s="1">
+        <v>1</v>
+      </c>
+      <c r="F237" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A238" s="1">
+        <v>11030004</v>
+      </c>
+      <c r="B238" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C238" s="1">
+        <v>4</v>
+      </c>
+      <c r="D238" s="1">
+        <v>24</v>
+      </c>
+      <c r="E238" s="1">
+        <v>1</v>
+      </c>
+      <c r="F238" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A239" s="1">
+        <v>11030005</v>
+      </c>
+      <c r="B239" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C239" s="1">
+        <v>5</v>
+      </c>
+      <c r="D239" s="1">
+        <v>30</v>
+      </c>
+      <c r="E239" s="1">
+        <v>1</v>
+      </c>
+      <c r="F239" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A240" s="1">
+        <v>11030006</v>
+      </c>
+      <c r="B240" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C240" s="1">
+        <v>6</v>
+      </c>
+      <c r="D240" s="1">
+        <v>36</v>
+      </c>
+      <c r="E240" s="1">
+        <v>1</v>
+      </c>
+      <c r="F240" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A241" s="1">
+        <v>11030007</v>
+      </c>
+      <c r="B241" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C241" s="1">
+        <v>7</v>
+      </c>
+      <c r="D241" s="1">
+        <v>42</v>
+      </c>
+      <c r="E241" s="1">
+        <v>1</v>
+      </c>
+      <c r="F241" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A242" s="1">
+        <v>11030008</v>
+      </c>
+      <c r="B242" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C242" s="1">
+        <v>8</v>
+      </c>
+      <c r="D242" s="1">
+        <v>48</v>
+      </c>
+      <c r="E242" s="1">
+        <v>1</v>
+      </c>
+      <c r="F242" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A243" s="1">
+        <v>11030009</v>
+      </c>
+      <c r="B243" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C243" s="1">
+        <v>9</v>
+      </c>
+      <c r="D243" s="1">
+        <v>54</v>
+      </c>
+      <c r="E243" s="1">
+        <v>1</v>
+      </c>
+      <c r="F243" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A244" s="1">
+        <v>11030010</v>
+      </c>
+      <c r="B244" s="1">
+        <v>1103</v>
+      </c>
+      <c r="C244" s="1">
+        <v>10</v>
+      </c>
+      <c r="D244" s="1">
+        <v>-1</v>
+      </c>
+      <c r="E244" s="1">
+        <v>1</v>
+      </c>
+      <c r="F244" s="1">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>